--- a/Result/checksun_type/期貨業.xlsx
+++ b/Result/checksun_type/期貨業.xlsx
@@ -878,42 +878,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>-0.9</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>280.155</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>49.55</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>190.635</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-13.79</t>
+          <t>-19.61</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,285 +1009,285 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>33.33</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>-0.84</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>49.97000000000001</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>49.73</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>49.16</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>49.17</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>-10.99</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-83.14</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/10/09</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>26678443.79479769</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>13917892.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>12989513.2</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>16157581.3</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>11144720.98</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>-3168068</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>601138.5201360579</t>
+        </is>
+      </c>
+      <c r="BC2" t="n">
+        <v>164721.92</v>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>49.4</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>2025/10/30</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>0.30</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>群益期</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>群益期</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>金融保險</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>群益期-金融保險-上市</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>金融保險平上市</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>62.5</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>-0.12</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0.71</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>50.06</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>49.71</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>49.16</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>49.16</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>4.26</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0.28</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-82.68</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/10/09</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>26686839.75108539</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>9536973.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>13494796.6</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>15653412.6</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>11004239.68</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>-2158616</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>680486.9921846419</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>123679.1</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>49.4</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>2025/10/30</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>群益期</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>群益期</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>金融保險</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>-10.066362907277</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>-32.65401076400691</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>12.56247973252524</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>5.66</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>2.94</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>10.44</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>51.90%</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>-1.13%</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>17.01</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>12497</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>經紀手續費72.99%、期貨佣金12.11%、衍生工具淨損益-櫃檯3.93%、營業證券出售損益2.93%、衍生性金融商品利益(損失)-期2.52%、借券及附賣回債券融券回補利1.62%、營業證券透過損益按公允價值1.13%、證券佣金0.93%、顧問0.45%、股利收入0.39%、其他營業收入0.36%、經理費0.34%、借券及附賣回債券融券透過損0.29% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>群益期-金融保險-上市</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>金融保險平上市</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>** 金融 - 期貨業</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>216.851</t>
+          <t>190.635</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-9.51</t>
+          <t>-13.79</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>7.20</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,270 +1455,270 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>71.76</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
+          <t>50.06</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>49.71</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>49.16</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>49.16</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>4.26</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.27</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-82.68</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/10/09</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>26678443.79479769</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>9536973.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>13494796.6</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>15653412.6</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>11004239.68</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>-2158616</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>680486.9921846419</t>
+        </is>
+      </c>
+      <c r="BC3" t="n">
+        <v>123679.1</v>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>49.4</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>2025/10/30</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>群益期</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>群益期</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>金融保險</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>群益期-金融保險-上市</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>金融保險平上市</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>50.2</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>49.67</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>49.13</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>49.16</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>9.33</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>0.29</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-82.86</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>2025/10/09</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>26686839.75108539</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>10866728.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>14079770.6</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>15558958.7</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>11059068.34</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>-1479188</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>781724.7904853937</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>530013.5699999999</v>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>49.4</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>2025/10/30</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>群益期</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>群益期</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>金融保險</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>-10.066362907277</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>-32.65401076400691</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>12.56247973252524</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>5.66</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>2.94</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>10.44</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>51.90%</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>-1.13%</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>17.01</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>12497</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>經紀手續費72.99%、期貨佣金12.11%、衍生工具淨損益-櫃檯3.93%、營業證券出售損益2.93%、衍生性金融商品利益(損失)-期2.52%、借券及附賣回債券融券回補利1.62%、營業證券透過損益按公允價值1.13%、證券佣金0.93%、顧問0.45%、股利收入0.39%、其他營業收入0.36%、經理費0.34%、借券及附賣回債券融券透過損0.29% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>群益期-金融保險-上市</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>金融保險平上市</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>50.4</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>** 金融 - 期貨業</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>316.682</t>
+          <t>216.851</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-9.51</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,32 +1871,32 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>77.31</t>
+          <t>71.76</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1916,32 +1916,32 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>49.67</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>49.12</t>
+          <t>49.13</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>49.16</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-83.26</t>
+          <t>-82.86</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,45 +1961,45 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>26686839.75108539</t>
+          <t>26678443.79479769</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>15895155.0</t>
+          <t>10866728.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>14764043.0</t>
+          <t>14079770.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>15136546.0</t>
+          <t>15558958.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>10951152.16</t>
+          <t>11059068.34</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-372503</t>
+          <t>-1479188</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>827490.4676659188</t>
+          <t>781724.7904853937</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>949088.5699999999</v>
+        <v>530013.5699999999</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,77 +2039,77 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-10.066362907277</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-32.65401076400691</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>12.56247973252524</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>10.44</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>51.90%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>12497</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>經紀手續費72.99%、期貨佣金12.11%、衍生工具淨損益-櫃檯3.93%、營業證券出售損益2.93%、衍生性金融商品利益(損失)-期2.52%、借券及附賣回債券融券回補利1.62%、營業證券透過損益按公允價值1.13%、證券佣金0.93%、顧問0.45%、股利收入0.39%、其他營業收入0.36%、經理費0.34%、借券及附賣回債券融券透過損0.29% (2024年)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>50.4</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>49.95</t>
-        </is>
-      </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>** 金融 - 期貨業</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>293.714</t>
+          <t>316.682</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,27 +2302,27 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>59.26</t>
+          <t>77.31</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -2332,47 +2332,47 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>49.92</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>49.57</t>
+          <t>49.65</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.12</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>49.14</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>14.90</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-83.91</t>
+          <t>-83.26</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,45 +2392,45 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>26686839.75108539</t>
+          <t>26678443.79479769</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>14730818.0</t>
+          <t>15895155.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>13578593.4</t>
+          <t>14764043.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>14039374.8</t>
+          <t>15136546.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>10823334.4</t>
+          <t>10951152.16</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-460781</t>
+          <t>-372503</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>805381.7224345424</t>
+          <t>827490.4676659188</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>975111.08</v>
+        <v>949088.5699999999</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,27 +2470,27 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-10.066362907277</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-32.65401076400691</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>12.56247973252524</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2500,47 +2500,47 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>10.44</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>51.90%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>12497</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>經紀手續費72.99%、期貨佣金12.11%、衍生工具淨損益-櫃檯3.93%、營業證券出售損益2.93%、衍生性金融商品利益(損失)-期2.52%、借券及附賣回債券融券回補利1.62%、營業證券透過損益按公允價值1.13%、證券佣金0.93%、顧問0.45%、股利收入0.39%、其他營業收入0.36%、經理費0.34%、借券及附賣回債券融券透過損0.29% (2024年)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2565,22 +2565,22 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>** 金融 - 期貨業</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>328.706</t>
+          <t>293.714</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10.92</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,57 +2733,57 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>59.26</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>49.96</t>
+          <t>49.92</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.57</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>49.09</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -2793,17 +2793,17 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>14.93</t>
+          <t>14.90</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-84.51</t>
+          <t>-83.91</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,45 +2823,45 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>26686839.75108539</t>
+          <t>26678443.79479769</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>16444309.0</t>
+          <t>14730818.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>19325649.4</t>
+          <t>13578593.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>13160448.7</t>
+          <t>14039374.8</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>10778049.42</t>
+          <t>10823334.4</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>6165200</t>
+          <t>-460781</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>774521.8387753789</t>
+          <t>805381.7224345424</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>1102211.1</v>
+        <v>975111.08</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,77 +2901,77 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-10.066362907277</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-32.65401076400691</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>12.56247973252524</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>10.44</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>51.90%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>12497</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>經紀手續費72.99%、期貨佣金12.11%、衍生工具淨損益-櫃檯3.93%、營業證券出售損益2.93%、衍生性金融商品利益(損失)-期2.52%、借券及附賣回債券融券回補利1.62%、營業證券透過損益按公允價值1.13%、證券佣金0.93%、顧問0.45%、股利收入0.39%、其他營業收入0.36%、經理費0.34%、借券及附賣回債券融券透過損0.29% (2024年)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3001,17 +3001,17 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>** 金融 - 期貨業</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>249.901</t>
+          <t>328.706</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,74 +3048,74 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>46.85</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-02-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-02-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>49.7</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>35.26</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-11-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-02-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-02-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>49.55</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>49.7</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
       <c r="T7" t="inlineStr">
         <is>
           <t>58.3</t>
@@ -3128,12 +3128,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>8.30</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,285 +3164,285 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
+          <t>49.96</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>49.5</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>49.09</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>49.14</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>14.93</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>-84.51</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2025/10/09</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>26678443.79479769</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>16444309.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>19325649.4</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>13160448.7</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>10778049.42</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>6165200</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>774521.8387753789</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
+        <v>1102211.1</v>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>49.4</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>2025/10/30</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>群益期</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>群益期</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>金融保險</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>群益期-金融保險-上市</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>金融保險平上市</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>50.4</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>50.4</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
           <t>49.9</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>49.45</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>49.07</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>49.13</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>16.19</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>0.23</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>-85.09</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>2025/10/09</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>26686839.75108539</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>12461843.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>17812028.6</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>13168761.5</t>
-        </is>
-      </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>10570089.02</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>4643267</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>714941.9726178073</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
-        <v>1060829.56</v>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>49.4</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>2025/10/30</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>0.61</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>群益期</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>群益期</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>金融保險</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>-10.066362907277</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
-        <is>
-          <t>-32.65401076400691</t>
-        </is>
-      </c>
-      <c r="BO7" t="inlineStr">
-        <is>
-          <t>12.56247973252524</t>
-        </is>
-      </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>價-量縮</t>
-        </is>
-      </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>5.66</t>
-        </is>
-      </c>
-      <c r="BT7" t="inlineStr">
-        <is>
-          <t>2.94</t>
-        </is>
-      </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>10.44</t>
-        </is>
-      </c>
-      <c r="BV7" t="inlineStr">
-        <is>
-          <t>51.90%</t>
-        </is>
-      </c>
-      <c r="BW7" t="inlineStr">
-        <is>
-          <t>-1.13%</t>
-        </is>
-      </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>17.01</t>
-        </is>
-      </c>
-      <c r="BY7" t="inlineStr">
-        <is>
-          <t>12497</t>
-        </is>
-      </c>
-      <c r="BZ7" t="inlineStr">
-        <is>
-          <t>經紀手續費72.99%、期貨佣金12.11%、衍生工具淨損益-櫃檯3.93%、營業證券出售損益2.93%、衍生性金融商品利益(損失)-期2.52%、借券及附賣回債券融券回補利1.62%、營業證券透過損益按公允價值1.13%、證券佣金0.93%、顧問0.45%、股利收入0.39%、其他營業收入0.36%、經理費0.34%、借券及附賣回債券融券透過損0.29% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA7" t="inlineStr">
-        <is>
-          <t>群益期-金融保險-上市</t>
-        </is>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>金融保險平上市</t>
-        </is>
-      </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>49.75</t>
-        </is>
-      </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>50.1</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>49.65</t>
-        </is>
-      </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>** 金融 - 期貨業</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>285.892</t>
+          <t>249.901</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>23.50</t>
+          <t>35.26</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3539,7 +3539,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,57 +3595,57 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>70.37</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>49.39</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>49.07</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -3655,17 +3655,17 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>28.88</t>
+          <t>16.19</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-85.69</t>
+          <t>-85.09</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,45 +3685,45 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>26686839.75108539</t>
+          <t>26678443.79479769</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>14288090.0</t>
+          <t>12461843.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>17038146.8</t>
+          <t>17812028.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>13796400.7</t>
+          <t>13168761.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>10521886.92</t>
+          <t>10570089.02</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>3241746</t>
+          <t>4643267</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>652053.3210508002</t>
+          <t>714941.9726178073</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>1390519.08</v>
+        <v>1060829.56</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,77 +3763,77 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-10.066362907277</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-32.65401076400691</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>12.56247973252524</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>10.44</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>51.90%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>12497</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>經紀手續費72.99%、期貨佣金12.11%、衍生工具淨損益-櫃檯3.93%、營業證券出售損益2.93%、衍生性金融商品利益(損失)-期2.52%、借券及附賣回債券融券回補利1.62%、營業證券透過損益按公允價值1.13%、證券佣金0.93%、顧問0.45%、股利收入0.39%、其他營業收入0.36%、經理費0.34%、借券及附賣回債券融券透過損0.29% (2024年)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -3858,22 +3858,22 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
+          <t>49.65</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>49.7</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>** 金融 - 期貨業</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>200.482</t>
+          <t>285.892</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>19.43</t>
+          <t>23.50</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -3990,12 +3990,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>75.93</t>
+          <t>70.37</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>49.73999999999999</t>
+          <t>49.86</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>49.31</t>
+          <t>49.39</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>49.04</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>49.12</t>
+          <t>49.13</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>32.74</t>
+          <t>28.88</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-86.72</t>
+          <t>-85.69</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,45 +4116,45 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>26686839.75108539</t>
+          <t>26678443.79479769</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>9967907.0</t>
+          <t>14288090.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>15509049.0</t>
+          <t>17038146.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>12985442.2</t>
+          <t>13796400.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>10326825.4</t>
+          <t>10521886.92</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>2523606</t>
+          <t>3241746</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>517786.819929163</t>
+          <t>652053.3210508002</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>1616173.39</v>
+        <v>1390519.08</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,27 +4194,27 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-10.066362907277</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-32.65401076400691</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>12.56247973252524</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,47 +4224,47 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>10.44</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>51.90%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>12497</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>經紀手續費72.99%、期貨佣金12.11%、衍生工具淨損益-櫃檯3.93%、營業證券出售損益2.93%、衍生性金融商品利益(損失)-期2.52%、借券及附賣回債券融券回補利1.62%、營業證券透過損益按公允價值1.13%、證券佣金0.93%、顧問0.45%、股利收入0.39%、其他營業收入0.36%、經理費0.34%、借券及附賣回債券融券透過損0.29% (2024年)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4279,32 +4279,32 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
+          <t>49.8</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>50.1</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>49.5</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>49.8</t>
-        </is>
-      </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>** 金融 - 期貨業</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>868.674</t>
+          <t>200.482</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>13.83</t>
+          <t>19.43</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -4421,12 +4421,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,37 +4457,37 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>80.16</t>
+          <t>75.93</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -4497,17 +4497,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>49.69</t>
+          <t>49.73999999999999</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.31</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>49.03</t>
+          <t>49.04</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -4517,7 +4517,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>44.67</t>
+          <t>32.74</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-87.81</t>
+          <t>-86.72</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,45 +4547,45 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>26686839.75108539</t>
+          <t>26678443.79479769</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>43466098.0</t>
+          <t>9967907.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>14500156.2</t>
+          <t>15509049.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>12738580.5</t>
+          <t>12985442.2</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>10254268.68</t>
+          <t>10326825.4</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>1761575</t>
+          <t>2523606</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>318080.1707976277</t>
+          <t>517786.819929163</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>2343692.97</v>
+        <v>1616173.39</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,77 +4625,77 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-10.066362907277</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-32.65401076400691</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>12.56247973252524</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>10.44</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>51.90%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>12497</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>經紀手續費72.99%、期貨佣金12.11%、衍生工具淨損益-櫃檯3.93%、營業證券出售損益2.93%、衍生性金融商品利益(損失)-期2.52%、借券及附賣回債券融券回補利1.62%、營業證券透過損益按公允價值1.13%、證券佣金0.93%、顧問0.45%、股利收入0.39%、其他營業收入0.36%、經理費0.34%、借券及附賣回債券融券透過損0.29% (2024年)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4710,32 +4710,32 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>** 金融 - 期貨業</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>178.648</t>
+          <t>868.674</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,74 +4772,74 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>13.83</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-02-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-02-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>49.7</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>-21.95</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-11-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-02-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-02-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>49.55</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
         <is>
           <t>49.7</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
       <c r="T11" t="inlineStr">
         <is>
           <t>58.3</t>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,98 +4867,98 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>61.11</t>
+          <t>80.16</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>-0.17</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>49.69</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>49.24</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>49.03</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>49.12</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>44.67</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
           <t>0.27</t>
         </is>
       </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>-0.19</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>49.55</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>49.14</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>49.01</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>49.1</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>30.29</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>0.22</t>
-        </is>
-      </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-89.17</t>
+          <t>-87.81</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,45 +4978,45 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>26686839.75108539</t>
+          <t>26678443.79479769</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>8876205.0</t>
+          <t>43466098.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>6995248.0</t>
+          <t>14500156.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>8962264.3</t>
+          <t>12738580.5</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>9651407.64</t>
+          <t>10254268.68</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-1967016</t>
+          <t>1761575</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-50213.06471600111</t>
+          <t>318080.1707976277</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-289788.57</v>
+        <v>2343692.97</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,27 +5056,27 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-10.066362907277</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-32.65401076400691</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>12.56247973252524</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,47 +5086,47 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>10.44</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>51.90%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>12497</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>經紀手續費72.99%、期貨佣金12.11%、衍生工具淨損益-櫃檯3.93%、營業證券出售損益2.93%、衍生性金融商品利益(損失)-期2.52%、借券及附賣回債券融券回補利1.62%、營業證券透過損益按公允價值1.13%、證券佣金0.93%、顧問0.45%、股利收入0.39%、其他營業收入0.36%、經理費0.34%、借券及附賣回債券融券透過損0.29% (2024年)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5141,32 +5141,32 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>** 金融 - 期貨業</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>173.414</t>
+          <t>178.648</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-21.95</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-17 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5263,12 +5263,12 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,63 +5298,63 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>54.76</t>
+          <t>61.11</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -5364,32 +5364,32 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>49.07</t>
+          <t>49.14</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.01</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>49.09</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>33.34</t>
+          <t>30.29</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-89.99</t>
+          <t>-89.17</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,45 +5409,45 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>26686839.75108539</t>
+          <t>26678443.79479769</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>8592434.0</t>
+          <t>8876205.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>8525494.4</t>
+          <t>6995248.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>8650468.1</t>
+          <t>8962264.3</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>9624290.5</t>
+          <t>9651407.64</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-124973</t>
+          <t>-1967016</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-6653.882483255285</t>
+          <t>-50213.06471600111</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-335495.49</v>
+        <v>-289788.57</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,27 +5487,27 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-10.066362907277</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-32.65401076400691</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>12.56247973252524</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,47 +5517,47 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>10.44</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>51.90%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>12497</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>經紀手續費72.99%、期貨佣金12.11%、衍生工具淨損益-櫃檯3.93%、營業證券出售損益2.93%、衍生性金融商品利益(損失)-期2.52%、借券及附賣回債券融券回補利1.62%、營業證券透過損益按公允價值1.13%、證券佣金0.93%、顧問0.45%、股利收入0.39%、其他營業收入0.36%、經理費0.34%、借券及附賣回債券融券透過損0.29% (2024年)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
+          <t>49.85</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>49.55</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
           <t>49.7</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>49.4</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>49.5</t>
-        </is>
-      </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>** 金融 - 期貨業</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>187.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>11.03</t>
+          <t>21.90</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>7.55</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>8.63</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,12 +5750,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>187</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5770,57 +5770,57 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>92.82</t>
+          <t>93.47999999999999</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>89.98</t>
+          <t>90.35</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>88.09</t>
+          <t>88.23</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>86.66</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>30.52</t>
+          <t>29.27</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-66.27</t>
+          <t>-63.61</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,45 +5840,45 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>19235.31837916064</t>
+          <t>19245.7651734104</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>14355.0</t>
+          <t>17643.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>17808.0</t>
+          <t>19485.8</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>16039.2</t>
+          <t>15984.8</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>10954.0</t>
+          <t>11103.86</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>1768</t>
+          <t>3501</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>1075.831681715461</t>
+          <t>995.53747787437</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>562.4</v>
+        <v>553.92</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5923,22 +5923,22 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>7.0674220703959</t>
+          <t>0.586310700095985</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>-31.40940154657053</t>
+          <t>8.007619922843494</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>-16.67133187484817</t>
+          <t>-12.34648294771329</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
@@ -5948,12 +5948,12 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>11.63</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>29918</t>
+          <t>30238</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-13.59</t>
+          <t>11.03</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>7.55</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>8.80</t>
+          <t>8.63</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>187</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6201,57 +6201,57 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>92.82</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>89.98</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>88.09</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>86.66</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>30.52</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
           <t>1.65</t>
         </is>
       </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>92.16</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>89.63</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>87.95</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>86.52</t>
-        </is>
-      </c>
-      <c r="AP14" t="inlineStr">
-        <is>
-          <t>31.22</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-68.84</t>
+          <t>-66.27</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,45 +6271,45 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>19235.31837916064</t>
+          <t>19245.7651734104</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>14562.0</t>
+          <t>14355.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>16832.6</t>
+          <t>17808.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>19479.0</t>
+          <t>16039.2</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>10822.66</t>
+          <t>10954.0</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-2646</t>
+          <t>1768</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>1169.182269182587</t>
+          <t>1075.831681715461</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>906.72</v>
+        <v>562.4</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6354,37 +6354,37 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>7.0674220703959</t>
+          <t>0.586310700095985</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>-31.40940154657053</t>
+          <t>8.007619922843494</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>-16.67133187484817</t>
+          <t>-12.34648294771329</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>11.63</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>29918</t>
+          <t>30238</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>227.0</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-9.61</t>
+          <t>-13.59</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12.80</t>
+          <t>8.80</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6612,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>187</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6632,57 +6632,57 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>92.16</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.63</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>87.81</t>
+          <t>87.95</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>86.52</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>31.22</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-71.27</t>
+          <t>-68.84</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,45 +6702,45 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>19235.31837916064</t>
+          <t>19245.7651734104</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>21173.0</t>
+          <t>14562.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>17689.4</t>
+          <t>16832.6</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>19569.4</t>
+          <t>19479.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>10628.18</t>
+          <t>10822.66</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-1880</t>
+          <t>-2646</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>1216.902052388735</t>
+          <t>1169.182269182587</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>1344.05</v>
+        <v>906.72</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6785,22 +6785,22 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>7.0674220703959</t>
+          <t>0.586310700095985</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-31.40940154657053</t>
+          <t>8.007619922843494</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>-16.67133187484817</t>
+          <t>-12.34648294771329</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>11.63</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>29918</t>
+          <t>30238</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
+          <t>93.6</t>
+        </is>
+      </c>
+      <c r="CE15" t="inlineStr">
+        <is>
+          <t>92.4</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
           <t>93.5</t>
-        </is>
-      </c>
-      <c r="CE15" t="inlineStr">
-        <is>
-          <t>92.1</t>
-        </is>
-      </c>
-      <c r="CF15" t="inlineStr">
-        <is>
-          <t>93.3</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>323.0</t>
+          <t>227.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-16.07</t>
+          <t>-9.61</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18.22</t>
+          <t>12.80</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,12 +7043,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>187</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7058,62 +7058,62 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>93.59</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>91.05999999999999</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>88.97</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>87.68</t>
+          <t>87.81</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>86.26</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>26.40</t>
+          <t>31.03</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-73.50</t>
+          <t>-71.27</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,45 +7133,45 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>19235.31837916064</t>
+          <t>19245.7651734104</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>29696.0</t>
+          <t>21173.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>15482.8</t>
+          <t>17689.4</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>18447.5</t>
+          <t>19569.4</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>10500.28</t>
+          <t>10628.18</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-2964</t>
+          <t>-1880</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>1193.78467296645</t>
+          <t>1216.902052388735</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>1212.47</v>
+        <v>1344.05</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7216,22 +7216,22 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>7.0674220703959</t>
+          <t>0.586310700095985</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>-31.40940154657053</t>
+          <t>8.007619922843494</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>-16.67133187484817</t>
+          <t>-12.34648294771329</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>11.63</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>29918</t>
+          <t>30238</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>92.6</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>323.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-22.04</t>
+          <t>-16.07</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>18.22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,12 +7474,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>187</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7494,57 +7494,57 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>91.05999999999999</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>88.97</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>87.68</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>86.26</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>26.40</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
           <t>1.26</t>
         </is>
       </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>90.68</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>88.68</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>87.57</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>86.15</t>
-        </is>
-      </c>
-      <c r="AP17" t="inlineStr">
-        <is>
-          <t>25.13</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-75.25</t>
+          <t>-73.50</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,45 +7564,45 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>19235.31837916064</t>
+          <t>19245.7651734104</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>9254.0</t>
+          <t>29696.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>12483.8</t>
+          <t>15482.8</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>16013.5</t>
+          <t>18447.5</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>10287.7</t>
+          <t>10500.28</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-3529</t>
+          <t>-2964</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>1190.386734510955</t>
+          <t>1193.78467296645</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>68.03</v>
+        <v>1212.47</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7647,37 +7647,37 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>7.0674220703959</t>
+          <t>0.586310700095985</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>-31.40940154657053</t>
+          <t>8.007619922843494</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>-16.67133187484817</t>
+          <t>-12.34648294771329</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>11.63</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>29918</t>
+          <t>30238</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>92.6</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,7 +7799,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-12.62</t>
+          <t>-22.04</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,77 +7905,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>187</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>80.77</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>91.51</t>
+          <t>93.59</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>90.68</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>88.44</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>87.49</t>
+          <t>87.57</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>86.05</t>
+          <t>86.15</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>25.13</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-76.81</t>
+          <t>-75.25</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,45 +7995,45 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>19235.31837916064</t>
+          <t>19245.7651734104</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>9478.0</t>
+          <t>9254.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>14270.4</t>
+          <t>12483.8</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>16330.8</t>
+          <t>16013.5</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>10507.96</t>
+          <t>10287.7</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-2060</t>
+          <t>-3529</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>1394.451804154832</t>
+          <t>1190.386734510955</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>620.89</v>
+        <v>68.03</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8078,22 +8078,22 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>7.0674220703959</t>
+          <t>0.586310700095985</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>-31.40940154657053</t>
+          <t>8.007619922843494</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>-16.67133187484817</t>
+          <t>-12.34648294771329</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>11.63</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>29918</t>
+          <t>30238</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>207.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -8240,7 +8240,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>18.06</t>
+          <t>-12.62</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11.68</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,77 +8336,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>187</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.77</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>97.92</t>
+          <t>91.51</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>90.34</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>88.23</t>
+          <t>88.44</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>87.36</t>
+          <t>87.49</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>85.95</t>
+          <t>86.05</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>34.95</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-78.44</t>
+          <t>-76.81</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,45 +8426,45 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>19235.31837916064</t>
+          <t>19245.7651734104</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>18846.0</t>
+          <t>9478.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>22125.4</t>
+          <t>14270.4</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>18741.1</t>
+          <t>16330.8</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>10427.96</t>
+          <t>10507.96</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>3384</t>
+          <t>-2060</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>1535.0988875752</t>
+          <t>1394.451804154832</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>1364.52</v>
+        <v>620.89</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8509,17 +8509,17 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>7.0674220703959</t>
+          <t>0.586310700095985</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>-31.40940154657053</t>
+          <t>8.007619922843494</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>-16.67133187484817</t>
+          <t>-12.34648294771329</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>11.63</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>29918</t>
+          <t>30238</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>207.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>19.97</t>
+          <t>18.06</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>6.37</t>
+          <t>11.68</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,17 +8767,17 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>187</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>93.75</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -8787,57 +8787,57 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>89.96000000000001</t>
+          <t>90.34</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>87.98</t>
+          <t>88.23</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>87.23</t>
+          <t>87.36</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>85.86</t>
+          <t>85.95</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>34.64</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-80.33</t>
+          <t>-78.44</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,45 +8857,45 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>19235.31837916064</t>
+          <t>19245.7651734104</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>10140.0</t>
+          <t>18846.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>21449.4</t>
+          <t>22125.4</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>17879.4</t>
+          <t>18741.1</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>10159.88</t>
+          <t>10427.96</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>3570</t>
+          <t>3384</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>1566.112538698074</t>
+          <t>1535.0988875752</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>1374.41</v>
+        <v>1364.52</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8940,37 +8940,37 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>7.0674220703959</t>
+          <t>0.586310700095985</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>-31.40940154657053</t>
+          <t>8.007619922843494</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>-16.67133187484817</t>
+          <t>-12.34648294771329</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>11.63</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>29918</t>
+          <t>30238</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,42 +9067,42 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>-0.11</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>90.1</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>4.66</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>163.0</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>90.2</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>3.53</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>21.61</t>
+          <t>19.97</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -9162,7 +9162,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>6.37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,77 +9198,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>187</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.75</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.92</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>89.96000000000001</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>87.98</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>87.12</t>
+          <t>87.23</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>85.76</t>
+          <t>85.86</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>43.38</t>
+          <t>34.64</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-82.03</t>
+          <t>-80.33</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,45 +9288,45 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>19235.31837916064</t>
+          <t>19245.7651734104</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>14701.0</t>
+          <t>10140.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>21412.2</t>
+          <t>21449.4</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>17607.4</t>
+          <t>17879.4</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>10049.5</t>
+          <t>10159.88</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>3804</t>
+          <t>3570</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>1600.968187194823</t>
+          <t>1566.112538698074</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>2272.22</v>
+        <v>1374.41</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9371,22 +9371,22 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>7.0674220703959</t>
+          <t>0.586310700095985</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>-31.40940154657053</t>
+          <t>8.007619922843494</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>-16.67133187484817</t>
+          <t>-12.34648294771329</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>11.63</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>29918</t>
+          <t>30238</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>91.1</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>203.0</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9523,7 +9523,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9533,7 +9533,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>21.61</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9553,7 +9553,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11.45</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,12 +9629,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>187</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9649,57 +9649,57 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>89.38</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>87.49</t>
+          <t>87.74</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.12</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>85.65</t>
+          <t>85.76</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>51.03</t>
+          <t>43.38</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-83.98</t>
+          <t>-82.03</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,45 +9719,45 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>19235.31837916064</t>
+          <t>19245.7651734104</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>18187.0</t>
+          <t>14701.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>19543.2</t>
+          <t>21412.2</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>16412.2</t>
+          <t>17607.4</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>9864.5</t>
+          <t>10049.5</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>3131</t>
+          <t>3804</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>1478.921614959184</t>
+          <t>1600.968187194823</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>2984.99</v>
+        <v>2272.22</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9802,22 +9802,22 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>7.0674220703959</t>
+          <t>0.586310700095985</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>-31.40940154657053</t>
+          <t>8.007619922843494</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>-16.67133187484817</t>
+          <t>-12.34648294771329</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9832,7 +9832,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>11.63</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>29918</t>
+          <t>30238</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,17 +9882,17 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>91.1</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>541.0</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,39 +9944,39 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>90.2</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>4.55</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>19.08</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t>90.0</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>3.74</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>21.99</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
       <c r="M23" t="inlineStr">
         <is>
           <t>2025-10-15 00:00:00</t>
@@ -9984,7 +9984,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>30.51</t>
+          <t>11.45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,12 +10060,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>187</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10075,7 +10075,7 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>94.87</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
@@ -10085,52 +10085,52 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>89.17999999999999</t>
+          <t>89.38</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>87.27</t>
+          <t>87.49</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>86.88</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>85.54</t>
+          <t>85.65</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>56.27</t>
+          <t>51.03</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-86.02</t>
+          <t>-83.98</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,45 +10150,45 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>19235.31837916064</t>
+          <t>19245.7651734104</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>48753.0</t>
+          <t>18187.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>18391.2</t>
+          <t>19543.2</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>15076.5</t>
+          <t>16412.2</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>9633.12</t>
+          <t>9864.5</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>1205.090664872232</t>
+          <t>1478.921614959184</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>3523.12</v>
+        <v>2984.99</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10233,22 +10233,22 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>7.0674220703959</t>
+          <t>0.586310700095985</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>-31.40940154657053</t>
+          <t>8.007619922843494</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>-16.67133187484817</t>
+          <t>-12.34648294771329</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10263,7 +10263,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>11.63</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>29918</t>
+          <t>30238</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/期貨業.xlsx
+++ b/Result/checksun_type/期貨業.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>505.389</t>
+          <t>124.255</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,37 +1009,37 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -1049,37 +1049,37 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>49.71</t>
+          <t>49.69</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>49.16</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>49.16</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-45.07</t>
+          <t>-74.56</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-84.85</t>
+          <t>-87.23</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>26693458.4047619</t>
+          <t>26668108.88904899</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>24722379.0</t>
+          <t>6067263.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>14987825.4</t>
+          <t>13022247.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>14283209.4</t>
+          <t>13893145.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>11515168.36</t>
+          <t>11517867.76</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>704616</t>
+          <t>-870898</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>662451.1134088128</t>
+          <t>585152.301157737</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>999670.38</v>
+        <v>160008.83</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>16.79</t>
+          <t>16.75</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>12184</t>
+          <t>12197</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>48.95</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>280.155</t>
+          <t>505.389</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,74 +1324,74 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>48.75</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>4.93</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-02-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-02-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>49.55</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-1.64</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-19.61</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-02-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-02-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>49.55</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
       <c r="T3" t="inlineStr">
         <is>
           <t>58.3</t>
@@ -1404,12 +1404,12 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>9.30</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,37 +1455,37 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>49.97000000000001</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>49.73</t>
+          <t>49.71</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1495,24 +1495,24 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>49.17</t>
+          <t>49.16</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-10.99</t>
+          <t>-45.07</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
           <t>0.23</t>
         </is>
       </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.26</t>
-        </is>
-      </c>
       <c r="AS3" t="inlineStr">
         <is>
           <t>1.55</t>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-83.14</t>
+          <t>-84.85</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,45 +1530,45 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>26693458.4047619</t>
+          <t>26668108.88904899</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>13917892.0</t>
+          <t>24722379.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>12989513.2</t>
+          <t>14987825.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>16157581.3</t>
+          <t>14283209.4</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>11144720.98</t>
+          <t>11515168.36</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-3168068</t>
+          <t>704616</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>601138.5201360579</t>
+          <t>662451.1134088128</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>164721.92</v>
+        <v>999670.38</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>16.79</t>
+          <t>16.75</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>12184</t>
+          <t>12197</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,42 +1740,42 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>-0.9</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>280.155</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>49.55</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-1.54</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>190.635</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-2.56</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-13.79</t>
+          <t>-19.61</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>9.30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,275 +1871,275 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>33.33</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>-0.84</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>49.97000000000001</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>49.73</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>49.16</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>49.17</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>-10.99</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-83.14</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2025/10/09</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>26668108.88904899</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>13917892.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>12989513.2</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>16157581.3</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>11144720.98</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>-3168068</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>601138.5201360579</t>
+        </is>
+      </c>
+      <c r="BC4" t="n">
+        <v>164721.92</v>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>49.4</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>2025/10/30</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>0.30</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>群益期</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>群益期</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>金融保險</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>-27.83005134720237</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>2.962791641689599</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>13.57296192649591</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>2.94</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>10.19</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>51.90%</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>-1.13%</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>16.75</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>12197</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>經紀手續費72.99%、期貨佣金12.11%、衍生工具淨損益-櫃檯3.93%、營業證券出售損益2.93%、衍生性金融商品利益(損失)-期2.52%、借券及附賣回債券融券回補利1.62%、營業證券透過損益按公允價值1.13%、證券佣金0.93%、顧問0.45%、股利收入0.39%、其他營業收入0.36%、經理費0.34%、借券及附賣回債券融券透過損0.29% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>群益期-金融保險-上市</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>金融保險平上市</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>62.5</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>-0.12</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0.71</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>50.06</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>49.71</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>49.16</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>49.16</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>4.26</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>0.28</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>-82.68</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>2025/10/09</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>26693458.4047619</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>9536973.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>13494796.6</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>15653412.6</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>11004239.68</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>-2158616</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>680486.9921846419</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>123679.1</v>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>49.4</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>2025/10/30</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>群益期</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>群益期</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>金融保險</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>-27.83005134720237</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>2.962791641689599</t>
-        </is>
-      </c>
-      <c r="BO4" t="inlineStr">
-        <is>
-          <t>13.57296192649591</t>
-        </is>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>5.81</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>2.94</t>
-        </is>
-      </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>10.18</t>
-        </is>
-      </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>51.90%</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
-        <is>
-          <t>-1.13%</t>
-        </is>
-      </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>16.79</t>
-        </is>
-      </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>12184</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>經紀手續費72.99%、期貨佣金12.11%、衍生工具淨損益-櫃檯3.93%、營業證券出售損益2.93%、衍生性金融商品利益(損失)-期2.52%、借券及附賣回債券融券回補利1.62%、營業證券透過損益按公允價值1.13%、證券佣金0.93%、顧問0.45%、股利收入0.39%、其他營業收入0.36%、經理費0.34%、借券及附賣回債券融券透過損0.29% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA4" t="inlineStr">
-        <is>
-          <t>群益期-金融保險-上市</t>
-        </is>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>金融保險平上市</t>
-        </is>
-      </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>216.851</t>
+          <t>190.635</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-9.51</t>
+          <t>-13.79</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.20</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2302,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2317,42 +2317,42 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>71.76</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>50.06</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>49.67</t>
+          <t>49.71</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>49.13</t>
+          <t>49.16</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-82.86</t>
+          <t>-82.68</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>26693458.4047619</t>
+          <t>26668108.88904899</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>10866728.0</t>
+          <t>9536973.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>14079770.6</t>
+          <t>13494796.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>15558958.7</t>
+          <t>15653412.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>11059068.34</t>
+          <t>11004239.68</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-1479188</t>
+          <t>-2158616</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>781724.7904853937</t>
+          <t>680486.9921846419</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>530013.5699999999</v>
+        <v>123679.1</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>16.79</t>
+          <t>16.75</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>12184</t>
+          <t>12197</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,17 +2555,17 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>316.682</t>
+          <t>216.851</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-9.51</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>7.20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,32 +2733,32 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>77.31</t>
+          <t>71.76</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -2778,32 +2778,32 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>49.67</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>49.12</t>
+          <t>49.13</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>49.16</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-83.26</t>
+          <t>-82.86</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>26693458.4047619</t>
+          <t>26668108.88904899</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>15895155.0</t>
+          <t>10866728.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>14764043.0</t>
+          <t>14079770.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>15136546.0</t>
+          <t>15558958.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>10951152.16</t>
+          <t>11059068.34</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-372503</t>
+          <t>-1479188</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>827490.4676659188</t>
+          <t>781724.7904853937</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>949088.5699999999</v>
+        <v>530013.5699999999</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>16.79</t>
+          <t>16.75</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>12184</t>
+          <t>12197</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>50.4</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>49.95</t>
-        </is>
-      </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>293.714</t>
+          <t>316.682</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,27 +3164,27 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>59.26</t>
+          <t>77.31</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
@@ -3194,47 +3194,47 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>49.92</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>49.57</t>
+          <t>49.65</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.12</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>49.14</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>14.90</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-83.91</t>
+          <t>-83.26</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>26693458.4047619</t>
+          <t>26668108.88904899</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>14730818.0</t>
+          <t>15895155.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>13578593.4</t>
+          <t>14764043.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>14039374.8</t>
+          <t>15136546.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>10823334.4</t>
+          <t>10951152.16</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-460781</t>
+          <t>-372503</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>805381.7224345424</t>
+          <t>827490.4676659188</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>975111.08</v>
+        <v>949088.5699999999</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>16.79</t>
+          <t>16.75</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>12184</t>
+          <t>12197</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>328.706</t>
+          <t>293.714</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10.92</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,57 +3595,57 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>59.26</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>49.96</t>
+          <t>49.92</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.57</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>49.09</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -3655,17 +3655,17 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>14.93</t>
+          <t>14.90</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-84.51</t>
+          <t>-83.91</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>26693458.4047619</t>
+          <t>26668108.88904899</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>16444309.0</t>
+          <t>14730818.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>19325649.4</t>
+          <t>13578593.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>13160448.7</t>
+          <t>14039374.8</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>10778049.42</t>
+          <t>10823334.4</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>6165200</t>
+          <t>-460781</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>774521.8387753789</t>
+          <t>805381.7224345424</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>1102211.1</v>
+        <v>975111.08</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,12 +3783,12 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>16.79</t>
+          <t>16.75</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>12184</t>
+          <t>12197</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>249.901</t>
+          <t>328.706</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,74 +3910,74 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-2.46</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>46.85</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-02-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-02-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>49.7</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-1.95</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>35.26</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-02-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-02-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>49.55</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>49.7</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>49.55</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
       <c r="T9" t="inlineStr">
         <is>
           <t>58.3</t>
@@ -3990,12 +3990,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>8.30</t>
+          <t>10.92</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,275 +4026,275 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
+          <t>49.96</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>49.5</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>49.09</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>49.14</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>14.93</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-84.51</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/10/09</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>26668108.88904899</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>16444309.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>19325649.4</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>13160448.7</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>10778049.42</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>6165200</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>774521.8387753789</t>
+        </is>
+      </c>
+      <c r="BC9" t="n">
+        <v>1102211.1</v>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>49.4</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>2025/10/30</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>群益期</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>群益期</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>金融保險</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>-27.83005134720237</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>2.962791641689599</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>13.57296192649591</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>2.94</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>10.19</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>51.90%</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>-1.13%</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>16.75</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>12197</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>經紀手續費72.99%、期貨佣金12.11%、衍生工具淨損益-櫃檯3.93%、營業證券出售損益2.93%、衍生性金融商品利益(損失)-期2.52%、借券及附賣回債券融券回補利1.62%、營業證券透過損益按公允價值1.13%、證券佣金0.93%、顧問0.45%、股利收入0.39%、其他營業收入0.36%、經理費0.34%、借券及附賣回債券融券透過損0.29% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>群益期-金融保險-上市</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>金融保險平上市</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>50.4</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>50.4</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
           <t>49.9</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>49.45</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>49.07</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>49.13</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>16.19</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>0.23</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>-85.09</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>2025/10/09</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>26693458.4047619</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>12461843.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>17812028.6</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>13168761.5</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>10570089.02</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>4643267</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>714941.9726178073</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>1060829.56</v>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>49.4</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>2025/10/30</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>0.61</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>群益期</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>群益期</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>金融保險</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>-27.83005134720237</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>2.962791641689599</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>13.57296192649591</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>價-量縮</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>5.81</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>2.94</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>10.18</t>
-        </is>
-      </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>51.90%</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>-1.13%</t>
-        </is>
-      </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>16.79</t>
-        </is>
-      </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>12184</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>經紀手續費72.99%、期貨佣金12.11%、衍生工具淨損益-櫃檯3.93%、營業證券出售損益2.93%、衍生性金融商品利益(損失)-期2.52%、借券及附賣回債券融券回補利1.62%、營業證券透過損益按公允價值1.13%、證券佣金0.93%、顧問0.45%、股利收入0.39%、其他營業收入0.36%、經理費0.34%、借券及附賣回債券融券透過損0.29% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr">
-        <is>
-          <t>群益期-金融保險-上市</t>
-        </is>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>金融保險平上市</t>
-        </is>
-      </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>49.75</t>
-        </is>
-      </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>50.1</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>49.65</t>
-        </is>
-      </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>285.892</t>
+          <t>249.901</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>23.50</t>
+          <t>35.26</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4421,12 +4421,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>8.30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,57 +4457,57 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>70.37</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>49.39</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>49.07</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -4517,17 +4517,17 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>28.88</t>
+          <t>16.19</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-85.69</t>
+          <t>-85.09</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>26693458.4047619</t>
+          <t>26668108.88904899</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>14288090.0</t>
+          <t>12461843.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>17038146.8</t>
+          <t>17812028.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>13796400.7</t>
+          <t>13168761.5</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>10521886.92</t>
+          <t>10570089.02</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>3241746</t>
+          <t>4643267</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>652053.3210508002</t>
+          <t>714941.9726178073</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>1390519.08</v>
+        <v>1060829.56</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>16.79</t>
+          <t>16.75</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>12184</t>
+          <t>12197</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -4720,12 +4720,12 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
+          <t>49.65</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
           <t>49.7</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>50.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>200.482</t>
+          <t>285.892</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>19.43</t>
+          <t>23.50</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4852,12 +4852,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>9.49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,177 +4888,177 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>75.93</t>
+          <t>70.37</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>-0.14</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>49.86</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>49.39</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>49.06</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>49.13</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>28.88</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>0.29</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>-85.69</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2025/10/09</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>26668108.88904899</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>14288090.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>17038146.8</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>13796400.7</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>10521886.92</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>3241746</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>652053.3210508002</t>
+        </is>
+      </c>
+      <c r="BC11" t="n">
+        <v>1390519.08</v>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>49.4</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>2025/10/30</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>群益期</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>群益期</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>金融保險</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
           <t>0.55</t>
         </is>
       </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>-0.17</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>49.73999999999999</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>49.31</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>49.04</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>49.12</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>32.74</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>0.21</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>-86.72</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>2025/10/09</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>26693458.4047619</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>9967907.0</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>15509049.0</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>12985442.2</t>
-        </is>
-      </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>10326825.4</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>2523606</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>517786.819929163</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>1616173.39</v>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>49.4</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>2025/10/30</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>0.81</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>群益期</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>群益期</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>金融保險</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
       <c r="BM11" t="inlineStr">
         <is>
           <t>-27.83005134720237</t>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>16.79</t>
+          <t>16.75</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>12184</t>
+          <t>12197</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
+          <t>49.8</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>50.1</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
           <t>50.0</t>
-        </is>
-      </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>49.5</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>49.8</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>868.674</t>
+          <t>200.482</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>13.83</t>
+          <t>19.43</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,37 +5319,37 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>80.16</t>
+          <t>75.93</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -5359,17 +5359,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>49.69</t>
+          <t>49.73999999999999</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.31</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>49.03</t>
+          <t>49.04</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>44.67</t>
+          <t>32.74</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-87.81</t>
+          <t>-86.72</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>26693458.4047619</t>
+          <t>26668108.88904899</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>43466098.0</t>
+          <t>9967907.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>14500156.2</t>
+          <t>15509049.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>12738580.5</t>
+          <t>12985442.2</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>10254268.68</t>
+          <t>10326825.4</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>1761575</t>
+          <t>2523606</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>318080.1707976277</t>
+          <t>517786.819929163</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>2343692.97</v>
+        <v>1616173.39</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>16.79</t>
+          <t>16.75</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>12184</t>
+          <t>12197</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>8.04</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,77 +5750,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>180</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>81.58</t>
+          <t>92.11</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>93.86</t>
+          <t>91.23</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>93.82</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>90.71</t>
+          <t>91.08</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>88.33</t>
+          <t>88.45</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>86.93</t>
+          <t>87.06</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>22.80</t>
+          <t>18.54</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-61.41</t>
+          <t>-59.53</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,45 +5840,45 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>19268.25541125541</t>
+          <t>19276.96037463977</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>23221.0</t>
+          <t>16873.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>18190.8</t>
+          <t>17330.8</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>16836.8</t>
+          <t>17510.1</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>11205.54</t>
+          <t>11244.72</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>-179</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>988.9136362169477</t>
+          <t>949.3214844405758</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>952.48</v>
+        <v>731.5599999999999</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>11.67</t>
+          <t>11.72</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>25.67</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>30014</t>
+          <t>30142</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
+          <t>93.9</t>
+        </is>
+      </c>
+      <c r="CD13" t="inlineStr">
+        <is>
           <t>94.7</t>
         </is>
       </c>
-      <c r="CD13" t="inlineStr">
-        <is>
-          <t>94.7</t>
-        </is>
-      </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>187.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>21.90</t>
+          <t>8.04</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10.55</t>
+          <t>13.99</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,77 +6181,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>180</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>81.58</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.86</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>93.47999999999999</t>
+          <t>93.82</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>90.35</t>
+          <t>90.71</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>88.23</t>
+          <t>88.33</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.93</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>22.80</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-63.61</t>
+          <t>-61.41</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,45 +6271,45 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>19268.25541125541</t>
+          <t>19276.96037463977</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>17643.0</t>
+          <t>23221.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>19485.8</t>
+          <t>18190.8</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>15984.8</t>
+          <t>16836.8</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>11103.86</t>
+          <t>11205.54</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>3501</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>995.53747787437</t>
+          <t>988.9136362169477</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>553.92</v>
+        <v>952.48</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>5.16</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -6369,22 +6369,22 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>11.67</t>
+          <t>11.72</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>25.67</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>30014</t>
+          <t>30142</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>187.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>11.03</t>
+          <t>21.90</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>7.55</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>8.63</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6612,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>180</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6632,57 +6632,57 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>92.82</t>
+          <t>93.47999999999999</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>89.98</t>
+          <t>90.35</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>88.09</t>
+          <t>88.23</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>86.66</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>30.52</t>
+          <t>29.27</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-66.27</t>
+          <t>-63.61</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,45 +6702,45 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>19268.25541125541</t>
+          <t>19276.96037463977</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>14355.0</t>
+          <t>17643.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>17808.0</t>
+          <t>19485.8</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>16039.2</t>
+          <t>15984.8</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>10954.0</t>
+          <t>11103.86</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>1768</t>
+          <t>3501</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>1075.831681715461</t>
+          <t>995.53747787437</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>562.4</v>
+        <v>553.92</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>11.67</t>
+          <t>11.72</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>25.67</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>30014</t>
+          <t>30142</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,109 +6912,109 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>0.21</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>156.0</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>11.03</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2025-10-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2025-11-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>87.4</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>93.5</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>87.4</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>87.3</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>87.6</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>7.55</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0.32</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>-13.59</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2025-10-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2025-11-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2025-08-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>87.4</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>87.4</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>87.3</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>87.6</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>6.98</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="X16" t="inlineStr">
         <is>
           <t>-0.23</t>
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>8.80</t>
+          <t>8.63</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,12 +7043,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>180</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7063,57 +7063,57 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>92.82</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>89.98</t>
+        </is>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>88.09</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>86.66</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>30.52</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
           <t>1.65</t>
         </is>
       </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>92.16</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>89.63</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>87.95</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>86.52</t>
-        </is>
-      </c>
-      <c r="AP16" t="inlineStr">
-        <is>
-          <t>31.22</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-68.84</t>
+          <t>-66.27</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,45 +7133,45 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>19268.25541125541</t>
+          <t>19276.96037463977</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>14562.0</t>
+          <t>14355.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>16832.6</t>
+          <t>17808.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>19479.0</t>
+          <t>16039.2</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>10822.66</t>
+          <t>10954.0</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-2646</t>
+          <t>1768</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>1169.182269182587</t>
+          <t>1075.831681715461</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>906.72</v>
+        <v>562.4</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -7231,22 +7231,22 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>11.67</t>
+          <t>11.72</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>25.67</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>30014</t>
+          <t>30142</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>227.0</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-9.61</t>
+          <t>-13.59</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12.80</t>
+          <t>8.80</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,12 +7474,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>180</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7494,57 +7494,57 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>92.16</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.63</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>87.81</t>
+          <t>87.95</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>86.52</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>31.22</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-71.27</t>
+          <t>-68.84</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,45 +7564,45 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>19268.25541125541</t>
+          <t>19276.96037463977</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>21173.0</t>
+          <t>14562.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>17689.4</t>
+          <t>16832.6</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>19569.4</t>
+          <t>19479.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>10628.18</t>
+          <t>10822.66</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-1880</t>
+          <t>-2646</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>1216.902052388735</t>
+          <t>1169.182269182587</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>1344.05</v>
+        <v>906.72</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
@@ -7677,7 +7677,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>11.67</t>
+          <t>11.72</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>25.67</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>30014</t>
+          <t>30142</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
+          <t>93.6</t>
+        </is>
+      </c>
+      <c r="CE17" t="inlineStr">
+        <is>
+          <t>92.4</t>
+        </is>
+      </c>
+      <c r="CF17" t="inlineStr">
+        <is>
           <t>93.5</t>
-        </is>
-      </c>
-      <c r="CE17" t="inlineStr">
-        <is>
-          <t>92.1</t>
-        </is>
-      </c>
-      <c r="CF17" t="inlineStr">
-        <is>
-          <t>93.3</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>323.0</t>
+          <t>227.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,7 +7799,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-16.07</t>
+          <t>-9.61</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18.22</t>
+          <t>12.80</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,12 +7905,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>180</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7920,62 +7920,62 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>93.59</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>91.05999999999999</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>88.97</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>87.68</t>
+          <t>87.81</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>86.26</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>26.40</t>
+          <t>31.03</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-73.50</t>
+          <t>-71.27</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,45 +7995,45 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>19268.25541125541</t>
+          <t>19276.96037463977</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>29696.0</t>
+          <t>21173.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>15482.8</t>
+          <t>17689.4</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>18447.5</t>
+          <t>19569.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>10500.28</t>
+          <t>10628.18</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-2964</t>
+          <t>-1880</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>1193.78467296645</t>
+          <t>1216.902052388735</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>1212.47</v>
+        <v>1344.05</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>11.67</t>
+          <t>11.72</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>25.67</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>30014</t>
+          <t>30142</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>92.6</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>323.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -8240,7 +8240,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-22.04</t>
+          <t>-16.07</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>18.22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,12 +8336,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>180</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8356,57 +8356,57 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>91.05999999999999</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>88.97</t>
+        </is>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>87.68</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>86.26</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>26.40</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
           <t>1.26</t>
         </is>
       </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>90.68</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>88.68</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>87.57</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>86.15</t>
-        </is>
-      </c>
-      <c r="AP19" t="inlineStr">
-        <is>
-          <t>25.13</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-75.25</t>
+          <t>-73.50</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,45 +8426,45 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>19268.25541125541</t>
+          <t>19276.96037463977</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>9254.0</t>
+          <t>29696.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>12483.8</t>
+          <t>15482.8</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>16013.5</t>
+          <t>18447.5</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>10287.7</t>
+          <t>10500.28</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-3529</t>
+          <t>-2964</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>1190.386734510955</t>
+          <t>1193.78467296645</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>68.03</v>
+        <v>1212.47</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -8524,22 +8524,22 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>11.67</t>
+          <t>11.72</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>25.67</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>30014</t>
+          <t>30142</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>92.6</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-12.62</t>
+          <t>-22.04</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,77 +8767,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>180</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>80.77</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>91.51</t>
+          <t>93.59</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>90.68</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>88.44</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>87.49</t>
+          <t>87.57</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>86.05</t>
+          <t>86.15</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>25.13</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-76.81</t>
+          <t>-75.25</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,45 +8857,45 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>19268.25541125541</t>
+          <t>19276.96037463977</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>9478.0</t>
+          <t>9254.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>14270.4</t>
+          <t>12483.8</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>16330.8</t>
+          <t>16013.5</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>10507.96</t>
+          <t>10287.7</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-2060</t>
+          <t>-3529</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>1394.451804154832</t>
+          <t>1190.386734510955</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>620.89</v>
+        <v>68.03</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>11.67</t>
+          <t>11.72</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>25.67</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>30014</t>
+          <t>30142</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>207.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,7 +9092,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>18.06</t>
+          <t>-12.62</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -9162,7 +9162,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11.68</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,77 +9198,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>180</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.77</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>97.92</t>
+          <t>91.51</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>90.34</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>88.23</t>
+          <t>88.44</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>87.36</t>
+          <t>87.49</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>85.95</t>
+          <t>86.05</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>34.95</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-78.44</t>
+          <t>-76.81</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,45 +9288,45 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>19268.25541125541</t>
+          <t>19276.96037463977</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>18846.0</t>
+          <t>9478.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>22125.4</t>
+          <t>14270.4</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>18741.1</t>
+          <t>16330.8</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>10427.96</t>
+          <t>10507.96</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>3384</t>
+          <t>-2060</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>1535.0988875752</t>
+          <t>1394.451804154832</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>1364.52</v>
+        <v>620.89</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>11.67</t>
+          <t>11.72</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>25.67</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>30014</t>
+          <t>30142</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>207.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,7 +9523,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9533,7 +9533,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>19.97</t>
+          <t>18.06</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9553,7 +9553,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -9593,7 +9593,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>6.37</t>
+          <t>11.68</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,17 +9629,17 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>180</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>93.75</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -9649,57 +9649,57 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>89.96000000000001</t>
+          <t>90.34</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>87.98</t>
+          <t>88.23</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>87.23</t>
+          <t>87.36</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>85.86</t>
+          <t>85.95</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>34.64</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-80.33</t>
+          <t>-78.44</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,45 +9719,45 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>19268.25541125541</t>
+          <t>19276.96037463977</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>10140.0</t>
+          <t>18846.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>21449.4</t>
+          <t>22125.4</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>17879.4</t>
+          <t>18741.1</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>10159.88</t>
+          <t>10427.96</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>3570</t>
+          <t>3384</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>1566.112538698074</t>
+          <t>1535.0988875752</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>1374.41</v>
+        <v>1364.52</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>11.67</t>
+          <t>11.72</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>25.67</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>30014</t>
+          <t>30142</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,109 +9929,109 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>-0.11</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>90.1</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>4.35</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>163.0</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>19.97</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2025-10-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2025-11-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>87.4</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>90.2</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>87.4</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>87.3</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>87.6</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>3.84</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>21.61</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>2025-10-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>2025-11-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>2025-08-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>87.4</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>87.4</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>87.3</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>87.6</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="X23" t="inlineStr">
         <is>
           <t>-0.23</t>
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>6.37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,77 +10060,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>180</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.75</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.92</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>89.96000000000001</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>87.98</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>87.12</t>
+          <t>87.23</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>85.76</t>
+          <t>85.86</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>43.38</t>
+          <t>34.64</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-82.03</t>
+          <t>-80.33</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,45 +10150,45 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>19268.25541125541</t>
+          <t>19276.96037463977</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>14701.0</t>
+          <t>10140.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>21412.2</t>
+          <t>21449.4</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>17607.4</t>
+          <t>17879.4</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>10049.5</t>
+          <t>10159.88</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>3804</t>
+          <t>3570</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>1600.968187194823</t>
+          <t>1566.112538698074</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>2272.22</v>
+        <v>1374.41</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10263,7 +10263,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>11.67</t>
+          <t>11.72</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>25.67</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>30014</t>
+          <t>30142</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>91.1</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/期貨業.xlsx
+++ b/Result/checksun_type/期貨業.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>346.337</t>
+          <t>437.14</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11.50</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>437</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>11.49</t>
+          <t>16.09</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>49.01000000000001</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>49.63</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
+          <t>49.14</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
           <t>49.15</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>49.15</t>
-        </is>
-      </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-132.60</t>
+          <t>-178.57</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-92.13</t>
+          <t>-94.56</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>26639933.96336207</t>
+          <t>26647648.4010043</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>16889257.0</t>
+          <t>21344598.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>13438369.4</t>
+          <t>14923710.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>13466583.0</t>
+          <t>13956611.9</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>11395162.18</t>
+          <t>11357891.38</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-28213</t>
+          <t>967098</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>350840.0393233188</t>
+          <t>386355.3261668038</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-47450.8450931944</t>
+          <t>581689.4038059711</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>16889257</v>
+        <v>21344598</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>17.08</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>12184</t>
+          <t>12247</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>113.787</t>
+          <t>346.337</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-8.11</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>11.50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>437</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1470,17 +1470,17 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1490,12 +1490,12 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>49.26000000000001</t>
+          <t>49.01000000000001</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>49.68</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1510,17 +1510,17 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-87.62</t>
+          <t>-132.60</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-89.52</t>
+          <t>-92.13</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>26639933.96336207</t>
+          <t>26647648.4010043</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>5595056.0</t>
+          <t>16889257.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>11967912.6</t>
+          <t>13438369.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>13023841.6</t>
+          <t>13466583.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>11508277.46</t>
+          <t>11395162.18</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-1055929</t>
+          <t>-28213</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>423256.5637626849</t>
+          <t>350840.0393233188</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-467169.9919101018</t>
+          <t>-47450.8450931944</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>5595056</v>
+        <v>16889257</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>17.08</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>12184</t>
+          <t>12247</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>124.255</t>
+          <t>113.787</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-8.11</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,37 +1886,37 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>437</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>31.03</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>11.49</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1926,12 +1926,12 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>49.26000000000001</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>49.69</t>
+          <t>49.68</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -1946,17 +1946,17 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-74.56</t>
+          <t>-87.62</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-87.23</t>
+          <t>-89.52</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>26639933.96336207</t>
+          <t>26647648.4010043</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>6067263.0</t>
+          <t>5595056.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>13022247.0</t>
+          <t>11967912.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>13893145.0</t>
+          <t>13023841.6</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>11517867.76</t>
+          <t>11508277.46</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-870898</t>
+          <t>-1055929</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>585152.301157737</t>
+          <t>423256.5637626849</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>160008.8337768205</t>
+          <t>-467169.9919101018</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>6067263</v>
+        <v>5595056</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>17.08</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>12184</t>
+          <t>12247</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>48.95</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>505.389</t>
+          <t>124.255</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>0.41</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,37 +2322,37 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>437</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -2362,37 +2362,37 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>49.71</t>
+          <t>49.69</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>49.16</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>49.16</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-45.07</t>
+          <t>-74.56</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-84.85</t>
+          <t>-87.23</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>26639933.96336207</t>
+          <t>26647648.4010043</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>24722379.0</t>
+          <t>6067263.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>14987825.4</t>
+          <t>13022247.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>14283209.4</t>
+          <t>13893145.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>11515168.36</t>
+          <t>11517867.76</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>704616</t>
+          <t>-870898</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>662451.1134088128</t>
+          <t>585152.301157737</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>999670.3764089644</t>
+          <t>160008.8337768205</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>24722379</v>
+        <v>6067263</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>17.08</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>12184</t>
+          <t>12247</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,12 +2580,12 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>48.95</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>280.155</t>
+          <t>505.389</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,72 +2642,72 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>48.75</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>4.93</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-02-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-02-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
           <t>49.55</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-1.64</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-19.61</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-02-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-02-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>49.55</t>
-        </is>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>9.30</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>437</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2773,37 +2773,37 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>49.97000000000001</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>49.73</t>
+          <t>49.71</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -2813,24 +2813,24 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>49.17</t>
+          <t>49.16</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-10.99</t>
+          <t>-45.07</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
           <t>0.23</t>
         </is>
       </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>0.26</t>
-        </is>
-      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>1.55</t>
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-83.14</t>
+          <t>-84.85</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,50 +2848,50 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>26639933.96336207</t>
+          <t>26647648.4010043</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>13917892.0</t>
+          <t>24722379.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>12989513.2</t>
+          <t>14987825.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>16157581.3</t>
+          <t>14283209.4</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>11144720.98</t>
+          <t>11515168.36</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-3168068</t>
+          <t>704616</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>601138.5201360579</t>
+          <t>662451.1134088128</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>164721.9238688461</t>
+          <t>999670.3764089644</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>13917892</v>
+        <v>24722379</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>17.08</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>12184</t>
+          <t>12247</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,42 +3063,42 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>-0.9</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>280.155</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>49.55</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-1.12</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>190.635</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-2.56</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-13.79</t>
+          <t>-19.61</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>9.30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,280 +3194,280 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>437</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>33.33</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>-0.84</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>49.97000000000001</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>49.73</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>49.16</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>49.17</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>-10.99</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>-83.14</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2025/10/09</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>26647648.4010043</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>13917892.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>12989513.2</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>16157581.3</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>11144720.98</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>-3168068</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>601138.5201360579</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>164721.9238688461</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>13917892</v>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>49.4</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>2025/10/30</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>0.30</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>群益期</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>群益期</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>金融保險</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>-27.83005134720237</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>2.962791641689599</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>13.57296192649591</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>5.78</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>2.94</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>10.23</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>51.90%</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>-1.13%</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>17.08</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>12247</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>經紀手續費72.99%、期貨佣金12.11%、衍生工具淨損益-櫃檯3.93%、營業證券出售損益2.93%、衍生性金融商品利益(損失)-期2.52%、借券及附賣回債券融券回補利1.62%、營業證券透過損益按公允價值1.13%、證券佣金0.93%、顧問0.45%、股利收入0.39%、其他營業收入0.36%、經理費0.34%、借券及附賣回債券融券透過損0.29% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>群益期-金融保險-上市</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>金融保險平上市</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>62.5</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>-0.12</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>0.71</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>50.06</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>49.71</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>49.16</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>49.16</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>4.26</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>0.28</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>-82.68</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>2025/10/09</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>26639933.96336207</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>9536973.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>13494796.6</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>15653412.6</t>
-        </is>
-      </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>11004239.68</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>-2158616</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>680486.9921846419</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>123679.1015305072</t>
-        </is>
-      </c>
-      <c r="BD7" t="n">
-        <v>9536973</v>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>49.4</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>2025/10/30</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>群益期</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>群益期</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>金融保險</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
-        <is>
-          <t>-27.83005134720237</t>
-        </is>
-      </c>
-      <c r="BO7" t="inlineStr">
-        <is>
-          <t>2.962791641689599</t>
-        </is>
-      </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>13.57296192649591</t>
-        </is>
-      </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="BT7" t="inlineStr">
-        <is>
-          <t>5.81</t>
-        </is>
-      </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>2.94</t>
-        </is>
-      </c>
-      <c r="BV7" t="inlineStr">
-        <is>
-          <t>10.18</t>
-        </is>
-      </c>
-      <c r="BW7" t="inlineStr">
-        <is>
-          <t>51.90%</t>
-        </is>
-      </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>-1.13%</t>
-        </is>
-      </c>
-      <c r="BY7" t="inlineStr">
-        <is>
-          <t>16.86</t>
-        </is>
-      </c>
-      <c r="BZ7" t="inlineStr">
-        <is>
-          <t>12184</t>
-        </is>
-      </c>
-      <c r="CA7" t="inlineStr">
-        <is>
-          <t>經紀手續費72.99%、期貨佣金12.11%、衍生工具淨損益-櫃檯3.93%、營業證券出售損益2.93%、衍生性金融商品利益(損失)-期2.52%、借券及附賣回債券融券回補利1.62%、營業證券透過損益按公允價值1.13%、證券佣金0.93%、顧問0.45%、股利收入0.39%、其他營業收入0.36%、經理費0.34%、借券及附賣回債券融券透過損0.29% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>群益期-金融保險-上市</t>
-        </is>
-      </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>金融保險平上市</t>
-        </is>
-      </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>216.851</t>
+          <t>190.635</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-9.51</t>
+          <t>-13.79</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7.20</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>437</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3645,42 +3645,42 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>71.76</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>50.06</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>49.67</t>
+          <t>49.71</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>49.13</t>
+          <t>49.16</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -3690,12 +3690,12 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-82.86</t>
+          <t>-82.68</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>26639933.96336207</t>
+          <t>26647648.4010043</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>10866728.0</t>
+          <t>9536973.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>14079770.6</t>
+          <t>13494796.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>15558958.7</t>
+          <t>15653412.6</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>11059068.34</t>
+          <t>11004239.68</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-1479188</t>
+          <t>-2158616</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>781724.7904853937</t>
+          <t>680486.9921846419</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>530013.5659925062</t>
+          <t>123679.1015305072</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>10866728</v>
+        <v>9536973</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>17.08</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>12184</t>
+          <t>12247</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,17 +3888,17 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>316.682</t>
+          <t>216.851</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-9.51</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4030,12 +4030,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>7.20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,32 +4066,32 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>437</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>77.31</t>
+          <t>71.76</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -4111,32 +4111,32 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>49.67</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>49.12</t>
+          <t>49.13</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>49.16</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-83.26</t>
+          <t>-82.86</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>26639933.96336207</t>
+          <t>26647648.4010043</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>15895155.0</t>
+          <t>10866728.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>14764043.0</t>
+          <t>14079770.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>15136546.0</t>
+          <t>15558958.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>10951152.16</t>
+          <t>11059068.34</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-372503</t>
+          <t>-1479188</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>827490.4676659188</t>
+          <t>781724.7904853937</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>949088.5664384887</t>
+          <t>530013.5659925062</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>15895155</v>
+        <v>10866728</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>17.08</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>12184</t>
+          <t>12247</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>50.4</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>49.95</t>
-        </is>
-      </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>293.714</t>
+          <t>316.682</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,27 +4502,27 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>437</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>59.26</t>
+          <t>77.31</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -4532,47 +4532,47 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>49.92</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>49.57</t>
+          <t>49.65</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.12</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>49.14</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>14.90</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-83.91</t>
+          <t>-83.26</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>26639933.96336207</t>
+          <t>26647648.4010043</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>14730818.0</t>
+          <t>15895155.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>13578593.4</t>
+          <t>14764043.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>14039374.8</t>
+          <t>15136546.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>10823334.4</t>
+          <t>10951152.16</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-460781</t>
+          <t>-372503</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>805381.7224345424</t>
+          <t>827490.4676659188</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>975111.0825599413</t>
+          <t>949088.5664384887</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>14730818</v>
+        <v>15895155</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>17.08</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>12184</t>
+          <t>12247</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -4770,12 +4770,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>328.706</t>
+          <t>293.714</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10.92</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,57 +4938,57 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>437</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>59.26</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>49.96</t>
+          <t>49.92</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.57</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>49.09</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -4998,17 +4998,17 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>14.93</t>
+          <t>14.90</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-84.51</t>
+          <t>-83.91</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>26639933.96336207</t>
+          <t>26647648.4010043</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>16444309.0</t>
+          <t>14730818.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>19325649.4</t>
+          <t>13578593.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>13160448.7</t>
+          <t>14039374.8</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>10778049.42</t>
+          <t>10823334.4</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>6165200</t>
+          <t>-460781</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>774521.8387753789</t>
+          <t>805381.7224345424</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>1102211.102642022</t>
+          <t>975111.0825599413</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>16444309</v>
+        <v>14730818</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>17.08</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>12184</t>
+          <t>12247</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>249.901</t>
+          <t>328.706</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,74 +5258,74 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-2.04</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>46.85</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-02-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-02-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>49.7</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-1.95</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>35.26</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-02-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-02-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>49.55</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
         <is>
           <t>49.7</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>49.55</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
       <c r="T12" t="inlineStr">
         <is>
           <t>58.3</t>
@@ -5338,12 +5338,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>8.30</t>
+          <t>10.92</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,280 +5374,280 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>437</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
+          <t>49.96</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>49.5</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>49.09</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>49.14</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>14.93</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>-84.51</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2025/10/09</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>26647648.4010043</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>16444309.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>19325649.4</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>13160448.7</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>10778049.42</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>6165200</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>774521.8387753789</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>1102211.102642022</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>16444309</v>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>49.4</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>2025/10/30</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>群益期</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>群益期</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>金融保險</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>-27.83005134720237</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>2.962791641689599</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>13.57296192649591</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>5.78</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>2.94</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>10.23</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
+          <t>51.90%</t>
+        </is>
+      </c>
+      <c r="BX12" t="inlineStr">
+        <is>
+          <t>-1.13%</t>
+        </is>
+      </c>
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>17.08</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>12247</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>經紀手續費72.99%、期貨佣金12.11%、衍生工具淨損益-櫃檯3.93%、營業證券出售損益2.93%、衍生性金融商品利益(損失)-期2.52%、借券及附賣回債券融券回補利1.62%、營業證券透過損益按公允價值1.13%、證券佣金0.93%、顧問0.45%、股利收入0.39%、其他營業收入0.36%、經理費0.34%、借券及附賣回債券融券透過損0.29% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>群益期-金融保險-上市</t>
+        </is>
+      </c>
+      <c r="CC12" t="inlineStr">
+        <is>
+          <t>金融保險平上市</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>50.4</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>50.4</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
           <t>49.9</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>49.45</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>49.07</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>49.13</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>16.19</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>0.23</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>-85.09</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>2025/10/09</t>
-        </is>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>26639933.96336207</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>12461843.0</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>17812028.6</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>13168761.5</t>
-        </is>
-      </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>10570089.02</t>
-        </is>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>4643267</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>714941.9726178073</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>1060829.556236347</t>
-        </is>
-      </c>
-      <c r="BD12" t="n">
-        <v>12461843</v>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>49.4</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>2025/10/30</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>0.61</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>群益期</t>
-        </is>
-      </c>
-      <c r="BJ12" t="inlineStr">
-        <is>
-          <t>群益期</t>
-        </is>
-      </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>金融保險</t>
-        </is>
-      </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
-        <is>
-          <t>-27.83005134720237</t>
-        </is>
-      </c>
-      <c r="BO12" t="inlineStr">
-        <is>
-          <t>2.962791641689599</t>
-        </is>
-      </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>13.57296192649591</t>
-        </is>
-      </c>
-      <c r="BQ12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="BT12" t="inlineStr">
-        <is>
-          <t>5.81</t>
-        </is>
-      </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>2.94</t>
-        </is>
-      </c>
-      <c r="BV12" t="inlineStr">
-        <is>
-          <t>10.18</t>
-        </is>
-      </c>
-      <c r="BW12" t="inlineStr">
-        <is>
-          <t>51.90%</t>
-        </is>
-      </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>-1.13%</t>
-        </is>
-      </c>
-      <c r="BY12" t="inlineStr">
-        <is>
-          <t>16.86</t>
-        </is>
-      </c>
-      <c r="BZ12" t="inlineStr">
-        <is>
-          <t>12184</t>
-        </is>
-      </c>
-      <c r="CA12" t="inlineStr">
-        <is>
-          <t>經紀手續費72.99%、期貨佣金12.11%、衍生工具淨損益-櫃檯3.93%、營業證券出售損益2.93%、衍生性金融商品利益(損失)-期2.52%、借券及附賣回債券融券回補利1.62%、營業證券透過損益按公允價值1.13%、證券佣金0.93%、顧問0.45%、股利收入0.39%、其他營業收入0.36%、經理費0.34%、借券及附賣回債券融券透過損0.29% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>群益期-金融保險-上市</t>
-        </is>
-      </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>金融保險平上市</t>
-        </is>
-      </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>49.75</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>50.1</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>49.65</t>
-        </is>
-      </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>334.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18.84</t>
+          <t>6.99</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,215 +5810,215 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>88.02</t>
+          <t>87.88</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>94.16</t>
+          <t>94.14000000000001</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>91.66</t>
+          <t>91.92</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>88.69</t>
+          <t>88.82</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>87.34</t>
+          <t>87.49</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>-56.30</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>2025/10/15</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>19325.11979913917</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>11803.0</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>20205.2</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>19845.5</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>12067.32</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>954.5399998971137</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>698.9549726006335</t>
+        </is>
+      </c>
+      <c r="BD13" t="n">
+        <v>11803</v>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>2025/10/23</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>5.83</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>元大期貨</t>
+        </is>
+      </c>
+      <c r="BJ13" t="inlineStr">
+        <is>
+          <t>元大期貨</t>
+        </is>
+      </c>
+      <c r="BK13" t="inlineStr">
+        <is>
+          <t>金融業</t>
+        </is>
+      </c>
+      <c r="BL13" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM13" t="inlineStr">
+        <is>
+          <t>0.27</t>
+        </is>
+      </c>
+      <c r="BN13" t="inlineStr">
+        <is>
+          <t>0.586310700095985</t>
+        </is>
+      </c>
+      <c r="BO13" t="inlineStr">
+        <is>
+          <t>8.007619922843494</t>
+        </is>
+      </c>
+      <c r="BP13" t="inlineStr">
+        <is>
+          <t>-12.34648294771329</t>
+        </is>
+      </c>
+      <c r="BQ13" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR13" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS13" t="inlineStr">
+        <is>
           <t>1.61</t>
         </is>
       </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="AT13" t="inlineStr">
-        <is>
-          <t>-56.98</t>
-        </is>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>2025/10/15</t>
-        </is>
-      </c>
-      <c r="AV13" t="inlineStr">
-        <is>
-          <t>19327.44827586207</t>
-        </is>
-      </c>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>31270.0</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>21373.2</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>19590.6</t>
-        </is>
-      </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>11958.24</t>
-        </is>
-      </c>
-      <c r="BA13" t="inlineStr">
-        <is>
-          <t>1782</t>
-        </is>
-      </c>
-      <c r="BB13" t="inlineStr">
-        <is>
-          <t>1001.01000486011</t>
-        </is>
-      </c>
-      <c r="BC13" t="inlineStr">
-        <is>
-          <t>1553.306325886435</t>
-        </is>
-      </c>
-      <c r="BD13" t="n">
-        <v>31270</v>
-      </c>
-      <c r="BE13" t="inlineStr">
-        <is>
-          <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="BF13" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr">
-        <is>
-          <t>2025/10/23</t>
-        </is>
-      </c>
-      <c r="BH13" t="inlineStr">
-        <is>
-          <t>5.27</t>
-        </is>
-      </c>
-      <c r="BI13" t="inlineStr">
-        <is>
-          <t>元大期貨</t>
-        </is>
-      </c>
-      <c r="BJ13" t="inlineStr">
-        <is>
-          <t>元大期貨</t>
-        </is>
-      </c>
-      <c r="BK13" t="inlineStr">
-        <is>
-          <t>金融業</t>
-        </is>
-      </c>
-      <c r="BL13" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM13" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="BN13" t="inlineStr">
-        <is>
-          <t>0.586310700095985</t>
-        </is>
-      </c>
-      <c r="BO13" t="inlineStr">
-        <is>
-          <t>8.007619922843494</t>
-        </is>
-      </c>
-      <c r="BP13" t="inlineStr">
-        <is>
-          <t>-12.34648294771329</t>
-        </is>
-      </c>
-      <c r="BQ13" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
-        </is>
-      </c>
-      <c r="BR13" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS13" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>11.68</t>
+          <t>11.74</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>30046</t>
+          <t>30206</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>188.0</t>
+          <t>334.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>93.9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10.60</t>
+          <t>18.84</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,77 +6246,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>96.97</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>90.22</t>
+          <t>88.02</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>94.18</t>
+          <t>94.16</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>91.66</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>88.57</t>
+          <t>88.69</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.34</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>14.91</t>
+          <t>9.14</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-57.96</t>
+          <t>-56.98</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,50 +6336,50 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>19327.44827586207</t>
+          <t>19325.11979913917</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>17859.0</t>
+          <t>31270.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>17990.2</t>
+          <t>21373.2</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>17411.4</t>
+          <t>19590.6</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>11472.62</t>
+          <t>11958.24</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>900.5924919462329</t>
+          <t>1001.01000486011</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>632.5830332273472</t>
+          <t>1553.306325886435</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>17859</v>
+        <v>31270</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6439,22 +6439,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>11.68</t>
+          <t>11.74</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>30046</t>
+          <t>30206</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>93.9</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>188.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.60</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,77 +6682,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>92.11</t>
+          <t>96.97</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>91.23</t>
+          <t>90.22</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>94.18</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>91.08</t>
+          <t>91.42</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>88.45</t>
+          <t>88.57</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>87.06</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>18.54</t>
+          <t>14.91</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-59.53</t>
+          <t>-57.96</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,50 +6772,50 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>19327.44827586207</t>
+          <t>19325.11979913917</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>16873.0</t>
+          <t>17859.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>17330.8</t>
+          <t>17990.2</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>17510.1</t>
+          <t>17411.4</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>11244.72</t>
+          <t>11472.62</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-179</t>
+          <t>578</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>949.3214844405758</t>
+          <t>900.5924919462329</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>731.5646496705303</t>
+          <t>632.5830332273472</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>16873</v>
+        <v>17859</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6875,7 +6875,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>11.68</t>
+          <t>11.74</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>30046</t>
+          <t>30206</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>8.04</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7042,7 +7042,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,77 +7118,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>81.58</t>
+          <t>92.11</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>93.86</t>
+          <t>91.23</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>93.82</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>90.71</t>
+          <t>91.08</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>88.33</t>
+          <t>88.45</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>86.93</t>
+          <t>87.06</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>22.80</t>
+          <t>18.54</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-61.41</t>
+          <t>-59.53</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,50 +7208,50 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>19327.44827586207</t>
+          <t>19325.11979913917</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>23221.0</t>
+          <t>16873.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>18190.8</t>
+          <t>17330.8</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>16836.8</t>
+          <t>17510.1</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>11205.54</t>
+          <t>11244.72</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>-179</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>988.9136362169477</t>
+          <t>949.3214844405758</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>952.4825071011255</t>
+          <t>731.5646496705303</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>23221</v>
+        <v>16873</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>11.68</t>
+          <t>11.74</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>30046</t>
+          <t>30206</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
+          <t>93.9</t>
+        </is>
+      </c>
+      <c r="CE16" t="inlineStr">
+        <is>
           <t>94.7</t>
         </is>
       </c>
-      <c r="CE16" t="inlineStr">
-        <is>
-          <t>94.7</t>
-        </is>
-      </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>187.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -7458,7 +7458,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>21.90</t>
+          <t>8.04</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10.55</t>
+          <t>13.99</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,77 +7554,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>81.58</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.86</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>93.47999999999999</t>
+          <t>93.82</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>90.35</t>
+          <t>90.71</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>88.23</t>
+          <t>88.33</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.93</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>22.80</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-63.61</t>
+          <t>-61.41</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,50 +7644,50 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>19327.44827586207</t>
+          <t>19325.11979913917</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>17643.0</t>
+          <t>23221.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>19485.8</t>
+          <t>18190.8</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>15984.8</t>
+          <t>16836.8</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>11103.86</t>
+          <t>11205.54</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>3501</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>995.53747787437</t>
+          <t>988.9136362169477</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>553.9193567483671</t>
+          <t>952.4825071011255</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>17643</v>
+        <v>23221</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>5.16</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7747,22 +7747,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>11.68</t>
+          <t>11.74</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>30046</t>
+          <t>30206</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>187.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7894,7 +7894,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>11.03</t>
+          <t>21.90</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -7954,7 +7954,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>7.55</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>8.63</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,12 +7990,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -8010,57 +8010,57 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>92.82</t>
+          <t>93.47999999999999</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>89.98</t>
+          <t>90.35</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>88.09</t>
+          <t>88.23</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>86.66</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>30.52</t>
+          <t>29.27</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-66.27</t>
+          <t>-63.61</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,50 +8080,50 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>19327.44827586207</t>
+          <t>19325.11979913917</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>14355.0</t>
+          <t>17643.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>17808.0</t>
+          <t>19485.8</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>16039.2</t>
+          <t>15984.8</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>10954.0</t>
+          <t>11103.86</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>1768</t>
+          <t>3501</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>1075.831681715461</t>
+          <t>995.53747787437</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>562.4034506462722</t>
+          <t>553.9193567483671</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>14355</v>
+        <v>17643</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>11.68</t>
+          <t>11.74</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>30046</t>
+          <t>30206</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,7 +8320,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-13.59</t>
+          <t>11.03</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8350,7 +8350,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>7.55</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>8.80</t>
+          <t>8.63</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,12 +8426,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8446,57 +8446,57 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>92.82</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>89.98</t>
+        </is>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>88.09</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>86.66</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>30.52</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
           <t>1.65</t>
         </is>
       </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>92.16</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>89.63</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>87.95</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>86.52</t>
-        </is>
-      </c>
-      <c r="AP19" t="inlineStr">
-        <is>
-          <t>31.22</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-68.84</t>
+          <t>-66.27</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,50 +8516,50 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>19327.44827586207</t>
+          <t>19325.11979913917</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>14562.0</t>
+          <t>14355.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>16832.6</t>
+          <t>17808.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>19479.0</t>
+          <t>16039.2</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>10822.66</t>
+          <t>10954.0</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-2646</t>
+          <t>1768</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>1169.182269182587</t>
+          <t>1075.831681715461</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>906.7234615487687</t>
+          <t>562.4034506462722</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>14562</v>
+        <v>14355</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,22 +8619,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>11.68</t>
+          <t>11.74</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>30046</t>
+          <t>30206</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>227.0</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-9.61</t>
+          <t>-13.59</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12.80</t>
+          <t>8.80</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,12 +8862,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8882,57 +8882,57 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>92.16</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.63</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>87.81</t>
+          <t>87.95</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>86.52</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>31.22</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-71.27</t>
+          <t>-68.84</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,50 +8952,50 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>19327.44827586207</t>
+          <t>19325.11979913917</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>21173.0</t>
+          <t>14562.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>17689.4</t>
+          <t>16832.6</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>19569.4</t>
+          <t>19479.0</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>10628.18</t>
+          <t>10822.66</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-1880</t>
+          <t>-2646</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>1216.902052388735</t>
+          <t>1169.182269182587</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>1344.047639211305</t>
+          <t>906.7234615487687</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>21173</v>
+        <v>14562</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>11.68</t>
+          <t>11.74</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>30046</t>
+          <t>30206</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
+          <t>93.6</t>
+        </is>
+      </c>
+      <c r="CF20" t="inlineStr">
+        <is>
+          <t>92.4</t>
+        </is>
+      </c>
+      <c r="CG20" t="inlineStr">
+        <is>
           <t>93.5</t>
-        </is>
-      </c>
-      <c r="CF20" t="inlineStr">
-        <is>
-          <t>92.1</t>
-        </is>
-      </c>
-      <c r="CG20" t="inlineStr">
-        <is>
-          <t>93.3</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>323.0</t>
+          <t>227.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,7 +9192,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-16.07</t>
+          <t>-9.61</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -9262,7 +9262,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18.22</t>
+          <t>12.80</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,12 +9298,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9313,62 +9313,62 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>93.59</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>91.05999999999999</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>88.97</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>87.68</t>
+          <t>87.81</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>86.26</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>26.40</t>
+          <t>31.03</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-73.50</t>
+          <t>-71.27</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,50 +9388,50 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>19327.44827586207</t>
+          <t>19325.11979913917</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>29696.0</t>
+          <t>21173.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>15482.8</t>
+          <t>17689.4</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>18447.5</t>
+          <t>19569.4</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>10500.28</t>
+          <t>10628.18</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-2964</t>
+          <t>-1880</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>1193.78467296645</t>
+          <t>1216.902052388735</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>1212.47333447167</t>
+          <t>1344.047639211305</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>29696</v>
+        <v>21173</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>11.68</t>
+          <t>11.74</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>30046</t>
+          <t>30206</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>92.6</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>323.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-22.04</t>
+          <t>-16.07</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -9698,7 +9698,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>18.22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,12 +9734,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9754,57 +9754,57 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>91.05999999999999</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>88.97</t>
+        </is>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>87.68</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>86.26</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>26.40</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
           <t>1.26</t>
         </is>
       </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>90.68</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>88.68</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>87.57</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>86.15</t>
-        </is>
-      </c>
-      <c r="AP22" t="inlineStr">
-        <is>
-          <t>25.13</t>
-        </is>
-      </c>
-      <c r="AQ22" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-75.25</t>
+          <t>-73.50</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,50 +9824,50 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>19327.44827586207</t>
+          <t>19325.11979913917</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>9254.0</t>
+          <t>29696.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>12483.8</t>
+          <t>15482.8</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>16013.5</t>
+          <t>18447.5</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>10287.7</t>
+          <t>10500.28</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-3529</t>
+          <t>-2964</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>1190.386734510955</t>
+          <t>1193.78467296645</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>68.02885146963308</t>
+          <t>1212.47333447167</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>9254</v>
+        <v>29696</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>11.68</t>
+          <t>11.74</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>30046</t>
+          <t>30206</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>92.6</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-12.62</t>
+          <t>-22.04</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,77 +10170,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>80.77</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>91.51</t>
+          <t>93.59</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>90.68</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>88.44</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>87.49</t>
+          <t>87.57</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>86.05</t>
+          <t>86.15</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>25.13</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-76.81</t>
+          <t>-75.25</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,50 +10260,50 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>19327.44827586207</t>
+          <t>19325.11979913917</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>9478.0</t>
+          <t>9254.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>14270.4</t>
+          <t>12483.8</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>16330.8</t>
+          <t>16013.5</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>10507.96</t>
+          <t>10287.7</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-2060</t>
+          <t>-3529</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>1394.451804154832</t>
+          <t>1190.386734510955</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>620.8928453428107</t>
+          <t>68.02885146963308</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>9478</v>
+        <v>9254</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF23" t="inlineStr">
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>11.68</t>
+          <t>11.74</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>30046</t>
+          <t>30206</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/期貨業.xlsx
+++ b/Result/checksun_type/期貨業.xlsx
@@ -888,7 +888,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>437.14</t>
+          <t>164.837</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>-12.76</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14.52</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,37 +1014,37 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>165</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -1054,240 +1054,240 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
+          <t>49.0</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>49.58</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>49.14</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>49.16</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>-222.32</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-96.50</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/10/09</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>26626847.5487106</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>8085769.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>11596388.6</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>13292107.0</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>11264689.06</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>-1695718</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>328936.5325934861</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>13133.16794023849</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
+        <v>8085769</v>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>49.4</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>2025/10/30</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>-0.30</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>群益期</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>群益期</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>金融保險</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>-27.83005134720237</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>2.962791641689599</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>13.57296192649591</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>2.94</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>10.28</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>51.90%</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>-1.13%</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>16.99</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>12309</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>經紀手續費72.99%、期貨佣金12.11%、衍生工具淨損益-櫃檯3.93%、營業證券出售損益2.93%、衍生性金融商品利益(損失)-期2.52%、借券及附賣回債券融券回補利1.62%、營業證券透過損益按公允價值1.13%、證券佣金0.93%、顧問0.45%、股利收入0.39%、其他營業收入0.36%、經理費0.34%、借券及附賣回債券融券透過損0.29% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>群益期-金融保險-上市</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>金融保險平上市</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>49.0</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>49.25</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>48.9</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>49.6</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>49.14</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>49.15</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>-178.57</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.08</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-94.56</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/10/09</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>26647648.4010043</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>21344598.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>14923710.6</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>13956611.9</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>11357891.38</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>967098</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>386355.3261668038</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>581689.4038059711</t>
-        </is>
-      </c>
-      <c r="BD2" t="n">
-        <v>21344598</v>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>49.4</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>2025/10/30</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>-0.81</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>群益期</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>群益期</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>金融保險</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>-27.83005134720237</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>2.962791641689599</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>13.57296192649591</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>5.78</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>2.94</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>10.23</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>51.90%</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>-1.13%</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>17.08</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>12247</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>經紀手續費72.99%、期貨佣金12.11%、衍生工具淨損益-櫃檯3.93%、營業證券出售損益2.93%、衍生性金融商品利益(損失)-期2.52%、借券及附賣回債券融券回補利1.62%、營業證券透過損益按公允價值1.13%、證券佣金0.93%、顧問0.45%、股利收入0.39%、其他營業收入0.36%、經理費0.34%、借券及附賣回債券融券透過損0.29% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>群益期-金融保險-上市</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>金融保險平上市</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>49.0</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>49.3</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>48.5</t>
-        </is>
-      </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>346.337</t>
+          <t>437.14</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11.50</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>165</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>11.49</t>
+          <t>16.09</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>49.01000000000001</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>49.63</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
+          <t>49.14</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
           <t>49.15</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>49.15</t>
-        </is>
-      </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-132.60</t>
+          <t>-178.57</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-92.13</t>
+          <t>-94.56</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>26647648.4010043</t>
+          <t>26626847.5487106</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>16889257.0</t>
+          <t>21344598.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>13438369.4</t>
+          <t>14923710.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>13466583.0</t>
+          <t>13956611.9</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>11395162.18</t>
+          <t>11357891.38</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-28213</t>
+          <t>967098</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>350840.0393233188</t>
+          <t>386355.3261668038</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-47450.8450931944</t>
+          <t>581689.4038059711</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>16889257</v>
+        <v>21344598</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>17.08</t>
+          <t>16.99</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>12247</t>
+          <t>12309</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>113.787</t>
+          <t>346.337</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-8.11</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>11.50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,17 +1886,17 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>165</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1906,17 +1906,17 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1926,12 +1926,12 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>49.26000000000001</t>
+          <t>49.01000000000001</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>49.68</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -1946,17 +1946,17 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-87.62</t>
+          <t>-132.60</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-89.52</t>
+          <t>-92.13</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>26647648.4010043</t>
+          <t>26626847.5487106</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>5595056.0</t>
+          <t>16889257.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>11967912.6</t>
+          <t>13438369.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>13023841.6</t>
+          <t>13466583.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>11508277.46</t>
+          <t>11395162.18</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-1055929</t>
+          <t>-28213</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>423256.5637626849</t>
+          <t>350840.0393233188</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-467169.9919101018</t>
+          <t>-47450.8450931944</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>5595056</v>
+        <v>16889257</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>17.08</t>
+          <t>16.99</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>12247</t>
+          <t>12309</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,34 +2191,34 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>113.787</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>49.2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>124.255</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>48.8</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.41</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-8.11</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,37 +2322,37 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>165</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>31.03</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>11.49</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>49.26000000000001</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>49.69</t>
+          <t>49.68</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2382,17 +2382,17 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-74.56</t>
+          <t>-87.62</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-87.23</t>
+          <t>-89.52</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>26647648.4010043</t>
+          <t>26626847.5487106</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>6067263.0</t>
+          <t>5595056.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>13022247.0</t>
+          <t>11967912.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>13893145.0</t>
+          <t>13023841.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>11517867.76</t>
+          <t>11508277.46</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-870898</t>
+          <t>-1055929</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>585152.301157737</t>
+          <t>423256.5637626849</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>160008.8337768205</t>
+          <t>-467169.9919101018</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>6067263</v>
+        <v>5595056</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>17.08</t>
+          <t>16.99</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>12247</t>
+          <t>12309</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>48.95</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>505.389</t>
+          <t>124.255</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,37 +2758,37 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>165</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2798,37 +2798,37 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>49.71</t>
+          <t>49.69</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>49.16</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>49.16</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-45.07</t>
+          <t>-74.56</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-84.85</t>
+          <t>-87.23</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>26647648.4010043</t>
+          <t>26626847.5487106</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>24722379.0</t>
+          <t>6067263.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>14987825.4</t>
+          <t>13022247.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>14283209.4</t>
+          <t>13893145.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>11515168.36</t>
+          <t>11517867.76</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>704616</t>
+          <t>-870898</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>662451.1134088128</t>
+          <t>585152.301157737</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>999670.3764089644</t>
+          <t>160008.8337768205</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>24722379</v>
+        <v>6067263</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>17.08</t>
+          <t>16.99</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>12247</t>
+          <t>12309</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,12 +3016,12 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>48.95</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>280.155</t>
+          <t>505.389</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,72 +3078,72 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>48.75</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>4.93</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-02-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-02-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
           <t>49.55</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-1.12</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>-19.61</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-02-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-02-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>49.55</t>
-        </is>
-      </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>9.30</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>165</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3209,37 +3209,37 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>49.97000000000001</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>49.73</t>
+          <t>49.71</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3249,24 +3249,24 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>49.17</t>
+          <t>49.16</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-10.99</t>
+          <t>-45.07</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
           <t>0.23</t>
         </is>
       </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>0.26</t>
-        </is>
-      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>1.55</t>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-83.14</t>
+          <t>-84.85</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,50 +3284,50 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>26647648.4010043</t>
+          <t>26626847.5487106</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>13917892.0</t>
+          <t>24722379.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>12989513.2</t>
+          <t>14987825.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>16157581.3</t>
+          <t>14283209.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>11144720.98</t>
+          <t>11515168.36</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-3168068</t>
+          <t>704616</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>601138.5201360579</t>
+          <t>662451.1134088128</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>164721.9238688461</t>
+          <t>999670.3764089644</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>13917892</v>
+        <v>24722379</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>17.08</t>
+          <t>16.99</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>12247</t>
+          <t>12309</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,42 +3499,42 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>-0.9</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>280.155</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>49.55</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-0.61</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>190.635</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-2.04</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-13.79</t>
+          <t>-19.61</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>9.30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,280 +3630,280 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>165</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>33.33</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>-0.84</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>49.97000000000001</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>49.73</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>49.16</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>49.17</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>-10.99</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-83.14</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/10/09</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>26626847.5487106</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>13917892.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>12989513.2</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>16157581.3</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>11144720.98</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>-3168068</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>601138.5201360579</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>164721.9238688461</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>13917892</v>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>49.4</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>2025/10/30</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>0.30</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>群益期</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>群益期</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>金融保險</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>-27.83005134720237</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>2.962791641689599</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>13.57296192649591</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>2.94</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>10.28</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>51.90%</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>-1.13%</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>16.99</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>12309</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>經紀手續費72.99%、期貨佣金12.11%、衍生工具淨損益-櫃檯3.93%、營業證券出售損益2.93%、衍生性金融商品利益(損失)-期2.52%、借券及附賣回債券融券回補利1.62%、營業證券透過損益按公允價值1.13%、證券佣金0.93%、顧問0.45%、股利收入0.39%、其他營業收入0.36%、經理費0.34%、借券及附賣回債券融券透過損0.29% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>群益期-金融保險-上市</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>金融保險平上市</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>62.5</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>-0.12</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>0.71</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>50.06</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>49.71</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>49.16</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>49.16</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>4.26</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>0.28</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>-82.68</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>2025/10/09</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>26647648.4010043</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>9536973.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>13494796.6</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>15653412.6</t>
-        </is>
-      </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>11004239.68</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>-2158616</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>680486.9921846419</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>123679.1015305072</t>
-        </is>
-      </c>
-      <c r="BD8" t="n">
-        <v>9536973</v>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>49.4</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>2025/10/30</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>群益期</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>群益期</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>金融保險</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
-        <is>
-          <t>-27.83005134720237</t>
-        </is>
-      </c>
-      <c r="BO8" t="inlineStr">
-        <is>
-          <t>2.962791641689599</t>
-        </is>
-      </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>13.57296192649591</t>
-        </is>
-      </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>5.78</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>2.94</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>10.23</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>51.90%</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>-1.13%</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>17.08</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>12247</t>
-        </is>
-      </c>
-      <c r="CA8" t="inlineStr">
-        <is>
-          <t>經紀手續費72.99%、期貨佣金12.11%、衍生工具淨損益-櫃檯3.93%、營業證券出售損益2.93%、衍生性金融商品利益(損失)-期2.52%、借券及附賣回債券融券回補利1.62%、營業證券透過損益按公允價值1.13%、證券佣金0.93%、顧問0.45%、股利收入0.39%、其他營業收入0.36%、經理費0.34%、借券及附賣回債券融券透過損0.29% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>群益期-金融保險-上市</t>
-        </is>
-      </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>金融保險平上市</t>
-        </is>
-      </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>216.851</t>
+          <t>190.635</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-9.51</t>
+          <t>-13.79</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>7.20</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>165</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4081,42 +4081,42 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>71.76</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>50.06</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>49.67</t>
+          <t>49.71</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>49.13</t>
+          <t>49.16</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-82.86</t>
+          <t>-82.68</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>26647648.4010043</t>
+          <t>26626847.5487106</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>10866728.0</t>
+          <t>9536973.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>14079770.6</t>
+          <t>13494796.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>15558958.7</t>
+          <t>15653412.6</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>11059068.34</t>
+          <t>11004239.68</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-1479188</t>
+          <t>-2158616</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>781724.7904853937</t>
+          <t>680486.9921846419</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>530013.5659925062</t>
+          <t>123679.1015305072</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>10866728</v>
+        <v>9536973</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>17.08</t>
+          <t>16.99</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>12247</t>
+          <t>12309</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,17 +4324,17 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>316.682</t>
+          <t>216.851</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-9.51</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>7.20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,32 +4502,32 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>165</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>77.31</t>
+          <t>71.76</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -4547,32 +4547,32 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>49.67</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>49.12</t>
+          <t>49.13</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>49.16</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-83.26</t>
+          <t>-82.86</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>26647648.4010043</t>
+          <t>26626847.5487106</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>15895155.0</t>
+          <t>10866728.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>14764043.0</t>
+          <t>14079770.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>15136546.0</t>
+          <t>15558958.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>10951152.16</t>
+          <t>11059068.34</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-372503</t>
+          <t>-1479188</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>827490.4676659188</t>
+          <t>781724.7904853937</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>949088.5664384887</t>
+          <t>530013.5659925062</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>15895155</v>
+        <v>10866728</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>17.08</t>
+          <t>16.99</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>12247</t>
+          <t>12309</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>50.4</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>49.95</t>
-        </is>
-      </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>293.714</t>
+          <t>316.682</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,27 +4938,27 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>165</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>59.26</t>
+          <t>77.31</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -4968,47 +4968,47 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>49.92</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>49.57</t>
+          <t>49.65</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.12</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>49.14</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>14.90</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-83.91</t>
+          <t>-83.26</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>26647648.4010043</t>
+          <t>26626847.5487106</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>14730818.0</t>
+          <t>15895155.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>13578593.4</t>
+          <t>14764043.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>14039374.8</t>
+          <t>15136546.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>10823334.4</t>
+          <t>10951152.16</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-460781</t>
+          <t>-372503</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>805381.7224345424</t>
+          <t>827490.4676659188</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>975111.0825599413</t>
+          <t>949088.5664384887</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>14730818</v>
+        <v>15895155</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>17.08</t>
+          <t>16.99</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>12247</t>
+          <t>12309</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5206,12 +5206,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>328.706</t>
+          <t>293.714</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10.92</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,57 +5374,57 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>165</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>59.26</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>49.96</t>
+          <t>49.92</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.57</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>49.09</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -5434,17 +5434,17 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>14.93</t>
+          <t>14.90</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-84.51</t>
+          <t>-83.91</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>26647648.4010043</t>
+          <t>26626847.5487106</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>16444309.0</t>
+          <t>14730818.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>19325649.4</t>
+          <t>13578593.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>13160448.7</t>
+          <t>14039374.8</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>10778049.42</t>
+          <t>10823334.4</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>6165200</t>
+          <t>-460781</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>774521.8387753789</t>
+          <t>805381.7224345424</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>1102211.102642022</t>
+          <t>975111.0825599413</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>16444309</v>
+        <v>14730818</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>17.08</t>
+          <t>16.99</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>12247</t>
+          <t>12309</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>8.58</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>6.99</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,77 +5810,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>88.89</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>94.14000000000001</t>
+          <t>94.36</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>91.92</t>
+          <t>92.24</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>88.82</t>
+          <t>88.95</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>87.49</t>
+          <t>87.64</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-56.30</t>
+          <t>-55.73</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,50 +5900,50 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>19325.11979913917</t>
+          <t>19313.43051575931</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>11803.0</t>
+          <t>7444.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>20205.2</t>
+          <t>17049.8</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>19845.5</t>
+          <t>17620.3</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>12067.32</t>
+          <t>12079.36</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>-570</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>954.5399998971137</t>
+          <t>770.2277154491823</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>698.9549726006335</t>
+          <t>-243.4898490144406</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>11803</v>
+        <v>7444</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>11.74</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>30206</t>
+          <t>30366</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>334.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18.84</t>
+          <t>6.99</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,215 +6246,215 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>88.02</t>
+          <t>87.88</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>94.16</t>
+          <t>94.14000000000001</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>91.66</t>
+          <t>91.92</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>88.69</t>
+          <t>88.82</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>87.34</t>
+          <t>87.49</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>-56.30</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>2025/10/15</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>19313.43051575931</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>11803.0</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>20205.2</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>19845.5</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>12067.32</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>954.5399998971137</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>698.9549726006335</t>
+        </is>
+      </c>
+      <c r="BD14" t="n">
+        <v>11803</v>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>2025/10/23</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>5.83</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>元大期貨</t>
+        </is>
+      </c>
+      <c r="BJ14" t="inlineStr">
+        <is>
+          <t>元大期貨</t>
+        </is>
+      </c>
+      <c r="BK14" t="inlineStr">
+        <is>
+          <t>金融業</t>
+        </is>
+      </c>
+      <c r="BL14" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>0.27</t>
+        </is>
+      </c>
+      <c r="BN14" t="inlineStr">
+        <is>
+          <t>0.586310700095985</t>
+        </is>
+      </c>
+      <c r="BO14" t="inlineStr">
+        <is>
+          <t>8.007619922843494</t>
+        </is>
+      </c>
+      <c r="BP14" t="inlineStr">
+        <is>
+          <t>-12.34648294771329</t>
+        </is>
+      </c>
+      <c r="BQ14" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS14" t="inlineStr">
+        <is>
           <t>1.61</t>
         </is>
       </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr">
-        <is>
-          <t>-56.98</t>
-        </is>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>2025/10/15</t>
-        </is>
-      </c>
-      <c r="AV14" t="inlineStr">
-        <is>
-          <t>19325.11979913917</t>
-        </is>
-      </c>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>31270.0</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>21373.2</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>19590.6</t>
-        </is>
-      </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>11958.24</t>
-        </is>
-      </c>
-      <c r="BA14" t="inlineStr">
-        <is>
-          <t>1782</t>
-        </is>
-      </c>
-      <c r="BB14" t="inlineStr">
-        <is>
-          <t>1001.01000486011</t>
-        </is>
-      </c>
-      <c r="BC14" t="inlineStr">
-        <is>
-          <t>1553.306325886435</t>
-        </is>
-      </c>
-      <c r="BD14" t="n">
-        <v>31270</v>
-      </c>
-      <c r="BE14" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="BF14" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr">
-        <is>
-          <t>2025/10/23</t>
-        </is>
-      </c>
-      <c r="BH14" t="inlineStr">
-        <is>
-          <t>5.27</t>
-        </is>
-      </c>
-      <c r="BI14" t="inlineStr">
-        <is>
-          <t>元大期貨</t>
-        </is>
-      </c>
-      <c r="BJ14" t="inlineStr">
-        <is>
-          <t>元大期貨</t>
-        </is>
-      </c>
-      <c r="BK14" t="inlineStr">
-        <is>
-          <t>金融業</t>
-        </is>
-      </c>
-      <c r="BL14" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM14" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="BN14" t="inlineStr">
-        <is>
-          <t>0.586310700095985</t>
-        </is>
-      </c>
-      <c r="BO14" t="inlineStr">
-        <is>
-          <t>8.007619922843494</t>
-        </is>
-      </c>
-      <c r="BP14" t="inlineStr">
-        <is>
-          <t>-12.34648294771329</t>
-        </is>
-      </c>
-      <c r="BQ14" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
-        </is>
-      </c>
-      <c r="BR14" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS14" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>11.74</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>30206</t>
+          <t>30366</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>188.0</t>
+          <t>334.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>93.9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10.60</t>
+          <t>18.84</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,77 +6682,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>96.97</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>90.22</t>
+          <t>88.02</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>94.18</t>
+          <t>94.16</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>91.66</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>88.57</t>
+          <t>88.69</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.34</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>14.91</t>
+          <t>9.14</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-57.96</t>
+          <t>-56.98</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,50 +6772,50 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>19325.11979913917</t>
+          <t>19313.43051575931</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>17859.0</t>
+          <t>31270.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>17990.2</t>
+          <t>21373.2</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>17411.4</t>
+          <t>19590.6</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>11472.62</t>
+          <t>11958.24</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>900.5924919462329</t>
+          <t>1001.01000486011</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>632.5830332273472</t>
+          <t>1553.306325886435</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>17859</v>
+        <v>31270</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6875,22 +6875,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>11.74</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>30206</t>
+          <t>30366</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>93.9</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>188.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7042,7 +7042,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.60</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,77 +7118,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>92.11</t>
+          <t>96.97</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>91.23</t>
+          <t>90.22</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>94.18</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>91.08</t>
+          <t>91.42</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>88.45</t>
+          <t>88.57</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>87.06</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>18.54</t>
+          <t>14.91</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-59.53</t>
+          <t>-57.96</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,50 +7208,50 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>19325.11979913917</t>
+          <t>19313.43051575931</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>16873.0</t>
+          <t>17859.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>17330.8</t>
+          <t>17990.2</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>17510.1</t>
+          <t>17411.4</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>11244.72</t>
+          <t>11472.62</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-179</t>
+          <t>578</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>949.3214844405758</t>
+          <t>900.5924919462329</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>731.5646496705303</t>
+          <t>632.5830332273472</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>16873</v>
+        <v>17859</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7321,12 +7321,12 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>11.74</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>30206</t>
+          <t>30366</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -7458,7 +7458,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>8.04</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,77 +7554,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>81.58</t>
+          <t>92.11</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>93.86</t>
+          <t>91.23</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>93.82</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>90.71</t>
+          <t>91.08</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>88.33</t>
+          <t>88.45</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>86.93</t>
+          <t>87.06</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>22.80</t>
+          <t>18.54</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-61.41</t>
+          <t>-59.53</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,50 +7644,50 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>19325.11979913917</t>
+          <t>19313.43051575931</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>23221.0</t>
+          <t>16873.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>18190.8</t>
+          <t>17330.8</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>16836.8</t>
+          <t>17510.1</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>11205.54</t>
+          <t>11244.72</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>-179</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>988.9136362169477</t>
+          <t>949.3214844405758</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>952.4825071011255</t>
+          <t>731.5646496705303</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>23221</v>
+        <v>16873</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7747,12 +7747,12 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>11.74</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>30206</t>
+          <t>30366</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
+          <t>93.9</t>
+        </is>
+      </c>
+      <c r="CE17" t="inlineStr">
+        <is>
           <t>94.7</t>
         </is>
       </c>
-      <c r="CE17" t="inlineStr">
-        <is>
-          <t>94.7</t>
-        </is>
-      </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>187.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -7894,7 +7894,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>21.90</t>
+          <t>8.04</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -7954,7 +7954,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10.55</t>
+          <t>13.99</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,77 +7990,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>81.58</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.86</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>93.47999999999999</t>
+          <t>93.82</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>90.35</t>
+          <t>90.71</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>88.23</t>
+          <t>88.33</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.93</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>22.80</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-63.61</t>
+          <t>-61.41</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,50 +8080,50 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>19325.11979913917</t>
+          <t>19313.43051575931</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>17643.0</t>
+          <t>23221.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>19485.8</t>
+          <t>18190.8</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>15984.8</t>
+          <t>16836.8</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>11103.86</t>
+          <t>11205.54</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>3501</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>995.53747787437</t>
+          <t>988.9136362169477</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>553.9193567483671</t>
+          <t>952.4825071011255</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>17643</v>
+        <v>23221</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>5.16</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8183,22 +8183,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>11.74</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>30206</t>
+          <t>30366</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>187.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>11.03</t>
+          <t>21.90</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8350,7 +8350,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>7.55</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>8.63</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,12 +8426,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8446,57 +8446,57 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>92.82</t>
+          <t>93.47999999999999</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>89.98</t>
+          <t>90.35</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>88.09</t>
+          <t>88.23</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>86.66</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>30.52</t>
+          <t>29.27</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-66.27</t>
+          <t>-63.61</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,50 +8516,50 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>19325.11979913917</t>
+          <t>19313.43051575931</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>14355.0</t>
+          <t>17643.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>17808.0</t>
+          <t>19485.8</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>16039.2</t>
+          <t>15984.8</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>10954.0</t>
+          <t>11103.86</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>1768</t>
+          <t>3501</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>1075.831681715461</t>
+          <t>995.53747787437</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>562.4034506462722</t>
+          <t>553.9193567483671</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>14355</v>
+        <v>17643</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>11.74</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>30206</t>
+          <t>30366</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-13.59</t>
+          <t>11.03</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>7.55</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>8.80</t>
+          <t>8.63</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,12 +8862,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8882,57 +8882,57 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>92.82</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>89.98</t>
+        </is>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>88.09</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>86.66</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>30.52</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
           <t>1.65</t>
         </is>
       </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>92.16</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>89.63</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>87.95</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>86.52</t>
-        </is>
-      </c>
-      <c r="AP20" t="inlineStr">
-        <is>
-          <t>31.22</t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-68.84</t>
+          <t>-66.27</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,50 +8952,50 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>19325.11979913917</t>
+          <t>19313.43051575931</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>14562.0</t>
+          <t>14355.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>16832.6</t>
+          <t>17808.0</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>19479.0</t>
+          <t>16039.2</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>10822.66</t>
+          <t>10954.0</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-2646</t>
+          <t>1768</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>1169.182269182587</t>
+          <t>1075.831681715461</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>906.7234615487687</t>
+          <t>562.4034506462722</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>14562</v>
+        <v>14355</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9055,22 +9055,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>11.74</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>30206</t>
+          <t>30366</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>227.0</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,7 +9192,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-9.61</t>
+          <t>-13.59</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -9262,7 +9262,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12.80</t>
+          <t>8.80</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,12 +9298,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9318,57 +9318,57 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>92.16</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.63</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>87.81</t>
+          <t>87.95</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>86.52</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>31.22</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-71.27</t>
+          <t>-68.84</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,50 +9388,50 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>19325.11979913917</t>
+          <t>19313.43051575931</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>21173.0</t>
+          <t>14562.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>17689.4</t>
+          <t>16832.6</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>19569.4</t>
+          <t>19479.0</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>10628.18</t>
+          <t>10822.66</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-1880</t>
+          <t>-2646</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>1216.902052388735</t>
+          <t>1169.182269182587</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>1344.047639211305</t>
+          <t>906.7234615487687</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>21173</v>
+        <v>14562</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9506,7 +9506,7 @@
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>11.74</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>30206</t>
+          <t>30366</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
+          <t>93.6</t>
+        </is>
+      </c>
+      <c r="CF21" t="inlineStr">
+        <is>
+          <t>92.4</t>
+        </is>
+      </c>
+      <c r="CG21" t="inlineStr">
+        <is>
           <t>93.5</t>
-        </is>
-      </c>
-      <c r="CF21" t="inlineStr">
-        <is>
-          <t>92.1</t>
-        </is>
-      </c>
-      <c r="CG21" t="inlineStr">
-        <is>
-          <t>93.3</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>323.0</t>
+          <t>227.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-16.07</t>
+          <t>-9.61</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -9698,7 +9698,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18.22</t>
+          <t>12.80</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,12 +9734,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9749,62 +9749,62 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>93.59</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>91.05999999999999</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>88.97</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>87.68</t>
+          <t>87.81</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>86.26</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>26.40</t>
+          <t>31.03</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-73.50</t>
+          <t>-71.27</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,50 +9824,50 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>19325.11979913917</t>
+          <t>19313.43051575931</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>29696.0</t>
+          <t>21173.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>15482.8</t>
+          <t>17689.4</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>18447.5</t>
+          <t>19569.4</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>10500.28</t>
+          <t>10628.18</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-2964</t>
+          <t>-1880</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>1193.78467296645</t>
+          <t>1216.902052388735</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>1212.47333447167</t>
+          <t>1344.047639211305</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>29696</v>
+        <v>21173</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>11.74</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>30206</t>
+          <t>30366</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>92.6</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>323.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-22.04</t>
+          <t>-16.07</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>18.22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,12 +10170,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10190,57 +10190,57 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>91.05999999999999</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>88.97</t>
+        </is>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>87.68</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>86.26</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>26.40</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
           <t>1.26</t>
         </is>
       </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>90.68</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>88.68</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>87.57</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>86.15</t>
-        </is>
-      </c>
-      <c r="AP23" t="inlineStr">
-        <is>
-          <t>25.13</t>
-        </is>
-      </c>
-      <c r="AQ23" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-75.25</t>
+          <t>-73.50</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,50 +10260,50 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>19325.11979913917</t>
+          <t>19313.43051575931</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>9254.0</t>
+          <t>29696.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>12483.8</t>
+          <t>15482.8</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>16013.5</t>
+          <t>18447.5</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>10287.7</t>
+          <t>10500.28</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-3529</t>
+          <t>-2964</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>1190.386734510955</t>
+          <t>1193.78467296645</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>68.02885146963308</t>
+          <t>1212.47333447167</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>9254</v>
+        <v>29696</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="BF23" t="inlineStr">
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>11.74</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>30206</t>
+          <t>30366</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>92.6</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/期貨業.xlsx
+++ b/Result/checksun_type/期貨業.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>164.837</t>
+          <t>220.404</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-12.76</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,37 +1014,37 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>44.41</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.18</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -1064,27 +1064,27 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>49.14</t>
+          <t>49.16</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>49.16</t>
+          <t>49.17</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-222.32</t>
+          <t>-179.21</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-96.50</t>
+          <t>-97.59</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>26626847.5487106</t>
+          <t>26612183.2167382</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>8085769.0</t>
+          <t>10917653.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>11596388.6</t>
+          <t>12566466.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>13292107.0</t>
+          <t>12794356.8</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>11264689.06</t>
+          <t>11192472.92</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-1695718</t>
+          <t>-227890</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>328936.5325934861</t>
+          <t>251747.3389076761</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>13133.16794023849</t>
+          <t>-172793.2263642792</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>8085769</v>
+        <v>10917653</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>10.38</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>16.99</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>12309</t>
+          <t>12422</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>437.14</t>
+          <t>164.837</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>-12.76</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14.52</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,37 +1450,37 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1490,240 +1490,240 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
+          <t>49.0</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>49.58</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>49.14</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>49.16</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>-222.32</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-96.50</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/10/09</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>26612183.2167382</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>8085769.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>11596388.6</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>13292107.0</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>11264689.06</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>-1695718</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>328936.5325934861</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>13133.16794023849</t>
+        </is>
+      </c>
+      <c r="BD3" t="n">
+        <v>8085769</v>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>49.4</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>2025/10/30</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>-0.30</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>群益期</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>群益期</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>金融保險</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>-27.83005134720237</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>2.962791641689599</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>13.57296192649591</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>5.69</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>2.94</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>10.38</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>51.90%</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>-1.13%</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>16.82</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>12422</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>經紀手續費72.99%、期貨佣金12.11%、衍生工具淨損益-櫃檯3.93%、營業證券出售損益2.93%、衍生性金融商品利益(損失)-期2.52%、借券及附賣回債券融券回補利1.62%、營業證券透過損益按公允價值1.13%、證券佣金0.93%、顧問0.45%、股利收入0.39%、其他營業收入0.36%、經理費0.34%、借券及附賣回債券融券透過損0.29% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>群益期-金融保險-上市</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>金融保險平上市</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>49.0</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>49.25</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>48.9</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>49.6</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>49.14</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>49.15</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>-178.57</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.08</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-94.56</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>2025/10/09</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>26626847.5487106</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>21344598.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>14923710.6</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>13956611.9</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>11357891.38</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>967098</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>386355.3261668038</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>581689.4038059711</t>
-        </is>
-      </c>
-      <c r="BD3" t="n">
-        <v>21344598</v>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>49.4</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>2025/10/30</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>-0.81</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>群益期</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>群益期</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>金融保險</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>-27.83005134720237</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>2.962791641689599</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>13.57296192649591</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>2.94</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>10.28</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>51.90%</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>-1.13%</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>16.99</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>12309</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>經紀手續費72.99%、期貨佣金12.11%、衍生工具淨損益-櫃檯3.93%、營業證券出售損益2.93%、衍生性金融商品利益(損失)-期2.52%、借券及附賣回債券融券回補利1.62%、營業證券透過損益按公允價值1.13%、證券佣金0.93%、顧問0.45%、股利收入0.39%、其他營業收入0.36%、經理費0.34%、借券及附賣回債券融券透過損0.29% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>群益期-金融保險-上市</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>金融保險平上市</t>
-        </is>
-      </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>49.0</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>49.3</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>48.5</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>346.337</t>
+          <t>437.14</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11.50</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>11.49</t>
+          <t>16.09</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>49.01000000000001</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>49.63</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
+          <t>49.14</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
           <t>49.15</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>49.15</t>
-        </is>
-      </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-132.60</t>
+          <t>-178.57</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-92.13</t>
+          <t>-94.56</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>26626847.5487106</t>
+          <t>26612183.2167382</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>16889257.0</t>
+          <t>21344598.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>13438369.4</t>
+          <t>14923710.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>13466583.0</t>
+          <t>13956611.9</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>11395162.18</t>
+          <t>11357891.38</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-28213</t>
+          <t>967098</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>350840.0393233188</t>
+          <t>386355.3261668038</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-47450.8450931944</t>
+          <t>581689.4038059711</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>16889257</v>
+        <v>21344598</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>10.38</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>16.99</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>12309</t>
+          <t>12422</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>113.787</t>
+          <t>346.337</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-8.11</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>11.50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,17 +2322,17 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -2342,17 +2342,17 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>49.26000000000001</t>
+          <t>49.01000000000001</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>49.68</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2382,17 +2382,17 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-87.62</t>
+          <t>-132.60</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-89.52</t>
+          <t>-92.13</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>26626847.5487106</t>
+          <t>26612183.2167382</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>5595056.0</t>
+          <t>16889257.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>11967912.6</t>
+          <t>13438369.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>13023841.6</t>
+          <t>13466583.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>11508277.46</t>
+          <t>11395162.18</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-1055929</t>
+          <t>-28213</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>423256.5637626849</t>
+          <t>350840.0393233188</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-467169.9919101018</t>
+          <t>-47450.8450931944</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>5595056</v>
+        <v>16889257</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>10.38</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>16.99</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>12309</t>
+          <t>12422</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>124.255</t>
+          <t>113.787</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-8.11</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,37 +2758,37 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>31.03</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>11.49</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>49.26000000000001</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>49.69</t>
+          <t>49.68</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -2818,17 +2818,17 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-74.56</t>
+          <t>-87.62</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-87.23</t>
+          <t>-89.52</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>26626847.5487106</t>
+          <t>26612183.2167382</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>6067263.0</t>
+          <t>5595056.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>13022247.0</t>
+          <t>11967912.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>13893145.0</t>
+          <t>13023841.6</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>11517867.76</t>
+          <t>11508277.46</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-870898</t>
+          <t>-1055929</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>585152.301157737</t>
+          <t>423256.5637626849</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>160008.8337768205</t>
+          <t>-467169.9919101018</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>6067263</v>
+        <v>5595056</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>10.38</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>16.99</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>12309</t>
+          <t>12422</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>48.95</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>505.389</t>
+          <t>124.255</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,37 +3194,37 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -3234,37 +3234,37 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>49.71</t>
+          <t>49.69</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>49.16</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>49.16</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-45.07</t>
+          <t>-74.56</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-84.85</t>
+          <t>-87.23</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>26626847.5487106</t>
+          <t>26612183.2167382</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>24722379.0</t>
+          <t>6067263.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>14987825.4</t>
+          <t>13022247.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>14283209.4</t>
+          <t>13893145.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>11515168.36</t>
+          <t>11517867.76</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>704616</t>
+          <t>-870898</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>662451.1134088128</t>
+          <t>585152.301157737</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>999670.3764089644</t>
+          <t>160008.8337768205</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>24722379</v>
+        <v>6067263</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>10.38</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>16.99</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>12309</t>
+          <t>12422</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>48.95</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>280.155</t>
+          <t>505.389</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,72 +3514,72 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>48.75</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>4.93</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-02-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-02-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
           <t>49.55</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-0.61</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>-19.61</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-02-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-02-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>49.55</t>
-        </is>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>9.30</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3645,37 +3645,37 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>49.97000000000001</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>49.73</t>
+          <t>49.71</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -3685,24 +3685,24 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>49.17</t>
+          <t>49.16</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-10.99</t>
+          <t>-45.07</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
           <t>0.23</t>
         </is>
       </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>0.26</t>
-        </is>
-      </c>
       <c r="AS8" t="inlineStr">
         <is>
           <t>1.55</t>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-83.14</t>
+          <t>-84.85</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,50 +3720,50 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>26626847.5487106</t>
+          <t>26612183.2167382</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>13917892.0</t>
+          <t>24722379.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>12989513.2</t>
+          <t>14987825.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>16157581.3</t>
+          <t>14283209.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>11144720.98</t>
+          <t>11515168.36</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-3168068</t>
+          <t>704616</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>601138.5201360579</t>
+          <t>662451.1134088128</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>164721.9238688461</t>
+          <t>999670.3764089644</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>13917892</v>
+        <v>24722379</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>10.38</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>16.99</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>12309</t>
+          <t>12422</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,42 +3935,42 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>-0.9</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>280.155</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>49.55</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>190.635</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-1.52</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-13.79</t>
+          <t>-19.61</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4030,12 +4030,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>9.30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,280 +4066,280 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>33.33</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>-0.84</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>49.97000000000001</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>49.73</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>49.16</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>49.17</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>-10.99</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-83.14</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/10/09</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>26612183.2167382</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>13917892.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>12989513.2</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>16157581.3</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>11144720.98</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>-3168068</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>601138.5201360579</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>164721.9238688461</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>13917892</v>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>49.4</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>2025/10/30</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>0.30</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>群益期</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>群益期</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>金融保險</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>-27.83005134720237</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>2.962791641689599</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>13.57296192649591</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>5.69</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>2.94</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>10.38</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>51.90%</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>-1.13%</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>16.82</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>12422</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>經紀手續費72.99%、期貨佣金12.11%、衍生工具淨損益-櫃檯3.93%、營業證券出售損益2.93%、衍生性金融商品利益(損失)-期2.52%、借券及附賣回債券融券回補利1.62%、營業證券透過損益按公允價值1.13%、證券佣金0.93%、顧問0.45%、股利收入0.39%、其他營業收入0.36%、經理費0.34%、借券及附賣回債券融券透過損0.29% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>群益期-金融保險-上市</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>金融保險平上市</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>62.5</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>-0.12</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0.71</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>50.06</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>49.71</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>49.16</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>49.16</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>4.26</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>0.28</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>-82.68</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>2025/10/09</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>26626847.5487106</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>9536973.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>13494796.6</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>15653412.6</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>11004239.68</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>-2158616</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>680486.9921846419</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>123679.1015305072</t>
-        </is>
-      </c>
-      <c r="BD9" t="n">
-        <v>9536973</v>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>49.4</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>2025/10/30</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>群益期</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>群益期</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>金融保險</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>-27.83005134720237</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>2.962791641689599</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>13.57296192649591</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>2.94</t>
-        </is>
-      </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>10.28</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>51.90%</t>
-        </is>
-      </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>-1.13%</t>
-        </is>
-      </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>16.99</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>12309</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr">
-        <is>
-          <t>經紀手續費72.99%、期貨佣金12.11%、衍生工具淨損益-櫃檯3.93%、營業證券出售損益2.93%、衍生性金融商品利益(損失)-期2.52%、借券及附賣回債券融券回補利1.62%、營業證券透過損益按公允價值1.13%、證券佣金0.93%、顧問0.45%、股利收入0.39%、其他營業收入0.36%、經理費0.34%、借券及附賣回債券融券透過損0.29% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>群益期-金融保險-上市</t>
-        </is>
-      </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>金融保險平上市</t>
-        </is>
-      </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>216.851</t>
+          <t>190.635</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-9.51</t>
+          <t>-13.79</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>7.20</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,12 +4502,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4517,42 +4517,42 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>71.76</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>50.06</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>49.67</t>
+          <t>49.71</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>49.13</t>
+          <t>49.16</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-82.86</t>
+          <t>-82.68</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>26626847.5487106</t>
+          <t>26612183.2167382</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>10866728.0</t>
+          <t>9536973.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>14079770.6</t>
+          <t>13494796.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>15558958.7</t>
+          <t>15653412.6</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>11059068.34</t>
+          <t>11004239.68</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-1479188</t>
+          <t>-2158616</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>781724.7904853937</t>
+          <t>680486.9921846419</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>530013.5659925062</t>
+          <t>123679.1015305072</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>10866728</v>
+        <v>9536973</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>10.38</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>16.99</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>12309</t>
+          <t>12422</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,17 +4760,17 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>316.682</t>
+          <t>216.851</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-9.51</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>7.20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,32 +4938,32 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>77.31</t>
+          <t>71.76</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -4983,32 +4983,32 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>49.67</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>49.12</t>
+          <t>49.13</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>49.16</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-83.26</t>
+          <t>-82.86</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>26626847.5487106</t>
+          <t>26612183.2167382</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>15895155.0</t>
+          <t>10866728.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>14764043.0</t>
+          <t>14079770.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>15136546.0</t>
+          <t>15558958.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>10951152.16</t>
+          <t>11059068.34</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-372503</t>
+          <t>-1479188</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>827490.4676659188</t>
+          <t>781724.7904853937</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>949088.5664384887</t>
+          <t>530013.5659925062</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>15895155</v>
+        <v>10866728</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>10.38</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>16.99</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>12309</t>
+          <t>12422</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>50.4</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>49.95</t>
-        </is>
-      </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>293.714</t>
+          <t>316.682</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,27 +5374,27 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>59.26</t>
+          <t>77.31</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
@@ -5404,47 +5404,47 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>49.92</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>49.57</t>
+          <t>49.65</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.12</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>49.14</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>14.90</t>
+          <t>15.48</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-83.91</t>
+          <t>-83.26</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>26626847.5487106</t>
+          <t>26612183.2167382</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>14730818.0</t>
+          <t>15895155.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>13578593.4</t>
+          <t>14764043.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>14039374.8</t>
+          <t>15136546.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>10823334.4</t>
+          <t>10951152.16</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-460781</t>
+          <t>-372503</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>805381.7224345424</t>
+          <t>827490.4676659188</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>975111.0825599413</t>
+          <t>949088.5664384887</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>14730818</v>
+        <v>15895155</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>10.38</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>16.99</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>12309</t>
+          <t>12422</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -5642,12 +5642,12 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>8.58</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,12 +5810,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5825,62 +5825,62 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>88.89</t>
+          <t>97.22</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>94.36</t>
+          <t>94.64000000000001</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>92.24</t>
+          <t>92.58</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>88.95</t>
+          <t>89.11</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>87.64</t>
+          <t>87.81</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-55.73</t>
+          <t>-55.07</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,50 +5900,50 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>19313.43051575931</t>
+          <t>19326.08369098713</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>7444.0</t>
+          <t>18772.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>17049.8</t>
+          <t>17429.6</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>17620.3</t>
+          <t>17380.2</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>12079.36</t>
+          <t>12316.72</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-570</t>
+          <t>49</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>770.2277154491823</t>
+          <t>644.4213010847493</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-243.4898490144406</t>
+          <t>-47.51397791963245</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>7444</v>
+        <v>18772</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>11.89</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>30366</t>
+          <t>30590</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>95.1</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>8.58</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>6.99</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,77 +6246,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>88.89</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>94.14000000000001</t>
+          <t>94.36</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>91.92</t>
+          <t>92.24</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>88.82</t>
+          <t>88.95</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>87.49</t>
+          <t>87.64</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-56.30</t>
+          <t>-55.73</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,50 +6336,50 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>19313.43051575931</t>
+          <t>19326.08369098713</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>11803.0</t>
+          <t>7444.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>20205.2</t>
+          <t>17049.8</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>19845.5</t>
+          <t>17620.3</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>12067.32</t>
+          <t>12079.36</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>-570</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>954.5399998971137</t>
+          <t>770.2277154491823</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>698.9549726006335</t>
+          <t>-243.4898490144406</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>11803</v>
+        <v>7444</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>11.89</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>30366</t>
+          <t>30590</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>334.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18.84</t>
+          <t>6.99</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,215 +6682,215 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>88.02</t>
+          <t>87.88</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>94.16</t>
+          <t>94.14000000000001</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>91.66</t>
+          <t>91.92</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>88.69</t>
+          <t>88.82</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>87.34</t>
+          <t>87.49</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>-56.30</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>2025/10/15</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>19326.08369098713</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>11803.0</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>20205.2</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>19845.5</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>12067.32</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>954.5399998971137</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>698.9549726006335</t>
+        </is>
+      </c>
+      <c r="BD15" t="n">
+        <v>11803</v>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>2025/10/23</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>5.83</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>元大期貨</t>
+        </is>
+      </c>
+      <c r="BJ15" t="inlineStr">
+        <is>
+          <t>元大期貨</t>
+        </is>
+      </c>
+      <c r="BK15" t="inlineStr">
+        <is>
+          <t>金融業</t>
+        </is>
+      </c>
+      <c r="BL15" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM15" t="inlineStr">
+        <is>
+          <t>0.27</t>
+        </is>
+      </c>
+      <c r="BN15" t="inlineStr">
+        <is>
+          <t>0.586310700095985</t>
+        </is>
+      </c>
+      <c r="BO15" t="inlineStr">
+        <is>
+          <t>8.007619922843494</t>
+        </is>
+      </c>
+      <c r="BP15" t="inlineStr">
+        <is>
+          <t>-12.34648294771329</t>
+        </is>
+      </c>
+      <c r="BQ15" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS15" t="inlineStr">
+        <is>
           <t>1.61</t>
         </is>
       </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr">
-        <is>
-          <t>-56.98</t>
-        </is>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>2025/10/15</t>
-        </is>
-      </c>
-      <c r="AV15" t="inlineStr">
-        <is>
-          <t>19313.43051575931</t>
-        </is>
-      </c>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>31270.0</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>21373.2</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>19590.6</t>
-        </is>
-      </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>11958.24</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr">
-        <is>
-          <t>1782</t>
-        </is>
-      </c>
-      <c r="BB15" t="inlineStr">
-        <is>
-          <t>1001.01000486011</t>
-        </is>
-      </c>
-      <c r="BC15" t="inlineStr">
-        <is>
-          <t>1553.306325886435</t>
-        </is>
-      </c>
-      <c r="BD15" t="n">
-        <v>31270</v>
-      </c>
-      <c r="BE15" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr">
-        <is>
-          <t>2025/10/23</t>
-        </is>
-      </c>
-      <c r="BH15" t="inlineStr">
-        <is>
-          <t>5.27</t>
-        </is>
-      </c>
-      <c r="BI15" t="inlineStr">
-        <is>
-          <t>元大期貨</t>
-        </is>
-      </c>
-      <c r="BJ15" t="inlineStr">
-        <is>
-          <t>元大期貨</t>
-        </is>
-      </c>
-      <c r="BK15" t="inlineStr">
-        <is>
-          <t>金融業</t>
-        </is>
-      </c>
-      <c r="BL15" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM15" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="BN15" t="inlineStr">
-        <is>
-          <t>0.586310700095985</t>
-        </is>
-      </c>
-      <c r="BO15" t="inlineStr">
-        <is>
-          <t>8.007619922843494</t>
-        </is>
-      </c>
-      <c r="BP15" t="inlineStr">
-        <is>
-          <t>-12.34648294771329</t>
-        </is>
-      </c>
-      <c r="BQ15" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
-        </is>
-      </c>
-      <c r="BR15" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS15" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>11.89</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>30366</t>
+          <t>30590</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>188.0</t>
+          <t>334.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>93.9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7042,7 +7042,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10.60</t>
+          <t>18.84</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,77 +7118,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>96.97</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>90.22</t>
+          <t>88.02</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>94.18</t>
+          <t>94.16</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>91.66</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>88.57</t>
+          <t>88.69</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.34</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>14.91</t>
+          <t>9.14</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-57.96</t>
+          <t>-56.98</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,50 +7208,50 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>19313.43051575931</t>
+          <t>19326.08369098713</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>17859.0</t>
+          <t>31270.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>17990.2</t>
+          <t>21373.2</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>17411.4</t>
+          <t>19590.6</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>11472.62</t>
+          <t>11958.24</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>900.5924919462329</t>
+          <t>1001.01000486011</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>632.5830332273472</t>
+          <t>1553.306325886435</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>17859</v>
+        <v>31270</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7311,22 +7311,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>11.89</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>30366</t>
+          <t>30590</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>93.9</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>188.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -7458,7 +7458,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.60</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,77 +7554,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>92.11</t>
+          <t>96.97</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>91.23</t>
+          <t>90.22</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>94.18</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>91.08</t>
+          <t>91.42</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>88.45</t>
+          <t>88.57</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>87.06</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>18.54</t>
+          <t>14.91</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-59.53</t>
+          <t>-57.96</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,50 +7644,50 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>19313.43051575931</t>
+          <t>19326.08369098713</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>16873.0</t>
+          <t>17859.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>17330.8</t>
+          <t>17990.2</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>17510.1</t>
+          <t>17411.4</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>11244.72</t>
+          <t>11472.62</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-179</t>
+          <t>578</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>949.3214844405758</t>
+          <t>900.5924919462329</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>731.5646496705303</t>
+          <t>632.5830332273472</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>16873</v>
+        <v>17859</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>11.89</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>30366</t>
+          <t>30590</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -7894,7 +7894,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>8.04</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -7954,7 +7954,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,77 +7990,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>81.58</t>
+          <t>92.11</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>93.86</t>
+          <t>91.23</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>93.82</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>90.71</t>
+          <t>91.08</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>88.33</t>
+          <t>88.45</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>86.93</t>
+          <t>87.06</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>22.80</t>
+          <t>18.54</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-61.41</t>
+          <t>-59.53</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,50 +8080,50 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>19313.43051575931</t>
+          <t>19326.08369098713</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>23221.0</t>
+          <t>16873.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>18190.8</t>
+          <t>17330.8</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>16836.8</t>
+          <t>17510.1</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>11205.54</t>
+          <t>11244.72</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>-179</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>988.9136362169477</t>
+          <t>949.3214844405758</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>952.4825071011255</t>
+          <t>731.5646496705303</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>23221</v>
+        <v>16873</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8183,12 +8183,12 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
@@ -8198,7 +8198,7 @@
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>11.89</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>30366</t>
+          <t>30590</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
+          <t>93.9</t>
+        </is>
+      </c>
+      <c r="CE18" t="inlineStr">
+        <is>
           <t>94.7</t>
         </is>
       </c>
-      <c r="CE18" t="inlineStr">
-        <is>
-          <t>94.7</t>
-        </is>
-      </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>187.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,7 +8320,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>21.90</t>
+          <t>8.04</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8350,7 +8350,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10.55</t>
+          <t>13.99</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,77 +8426,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>81.58</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.86</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>93.47999999999999</t>
+          <t>93.82</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>90.35</t>
+          <t>90.71</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>88.23</t>
+          <t>88.33</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.93</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>22.80</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-63.61</t>
+          <t>-61.41</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,50 +8516,50 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>19313.43051575931</t>
+          <t>19326.08369098713</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>17643.0</t>
+          <t>23221.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>19485.8</t>
+          <t>18190.8</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>15984.8</t>
+          <t>16836.8</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>11103.86</t>
+          <t>11205.54</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>3501</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>995.53747787437</t>
+          <t>988.9136362169477</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>553.9193567483671</t>
+          <t>952.4825071011255</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>17643</v>
+        <v>23221</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>5.16</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,22 +8619,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>11.89</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>30366</t>
+          <t>30590</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>187.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>11.03</t>
+          <t>21.90</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>7.55</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>8.63</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,12 +8862,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8882,57 +8882,57 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>92.82</t>
+          <t>93.47999999999999</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>89.98</t>
+          <t>90.35</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>88.09</t>
+          <t>88.23</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>86.66</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>30.52</t>
+          <t>29.27</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-66.27</t>
+          <t>-63.61</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,50 +8952,50 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>19313.43051575931</t>
+          <t>19326.08369098713</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>14355.0</t>
+          <t>17643.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>17808.0</t>
+          <t>19485.8</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>16039.2</t>
+          <t>15984.8</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>10954.0</t>
+          <t>11103.86</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>1768</t>
+          <t>3501</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>1075.831681715461</t>
+          <t>995.53747787437</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>562.4034506462722</t>
+          <t>553.9193567483671</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>14355</v>
+        <v>17643</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -9065,12 +9065,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>11.89</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>30366</t>
+          <t>30590</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,7 +9192,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-13.59</t>
+          <t>11.03</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -9262,7 +9262,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>7.55</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>8.80</t>
+          <t>8.63</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,12 +9298,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9318,57 +9318,57 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>92.82</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>89.98</t>
+        </is>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>88.09</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>86.66</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>30.52</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
           <t>1.65</t>
         </is>
       </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>92.16</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>89.63</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>87.95</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>86.52</t>
-        </is>
-      </c>
-      <c r="AP21" t="inlineStr">
-        <is>
-          <t>31.22</t>
-        </is>
-      </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-68.84</t>
+          <t>-66.27</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,50 +9388,50 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>19313.43051575931</t>
+          <t>19326.08369098713</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>14562.0</t>
+          <t>14355.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>16832.6</t>
+          <t>17808.0</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>19479.0</t>
+          <t>16039.2</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>10822.66</t>
+          <t>10954.0</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-2646</t>
+          <t>1768</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>1169.182269182587</t>
+          <t>1075.831681715461</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>906.7234615487687</t>
+          <t>562.4034506462722</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>14562</v>
+        <v>14355</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>11.89</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>30366</t>
+          <t>30590</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>227.0</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-9.61</t>
+          <t>-13.59</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -9698,7 +9698,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12.80</t>
+          <t>8.80</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,12 +9734,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9754,57 +9754,57 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>92.16</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.63</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>87.81</t>
+          <t>87.95</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>86.52</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>31.22</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-71.27</t>
+          <t>-68.84</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,50 +9824,50 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>19313.43051575931</t>
+          <t>19326.08369098713</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>21173.0</t>
+          <t>14562.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>17689.4</t>
+          <t>16832.6</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>19569.4</t>
+          <t>19479.0</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>10628.18</t>
+          <t>10822.66</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-1880</t>
+          <t>-2646</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>1216.902052388735</t>
+          <t>1169.182269182587</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>1344.047639211305</t>
+          <t>906.7234615487687</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>21173</v>
+        <v>14562</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>11.89</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>30366</t>
+          <t>30590</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
+          <t>93.6</t>
+        </is>
+      </c>
+      <c r="CF22" t="inlineStr">
+        <is>
+          <t>92.4</t>
+        </is>
+      </c>
+      <c r="CG22" t="inlineStr">
+        <is>
           <t>93.5</t>
-        </is>
-      </c>
-      <c r="CF22" t="inlineStr">
-        <is>
-          <t>92.1</t>
-        </is>
-      </c>
-      <c r="CG22" t="inlineStr">
-        <is>
-          <t>93.3</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>323.0</t>
+          <t>227.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-16.07</t>
+          <t>-9.61</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18.22</t>
+          <t>12.80</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,12 +10170,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10185,62 +10185,62 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>93.59</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>91.05999999999999</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>88.97</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>87.68</t>
+          <t>87.81</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>86.26</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>26.40</t>
+          <t>31.03</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-73.50</t>
+          <t>-71.27</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,50 +10260,50 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>19313.43051575931</t>
+          <t>19326.08369098713</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>29696.0</t>
+          <t>21173.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>15482.8</t>
+          <t>17689.4</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>18447.5</t>
+          <t>19569.4</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>10500.28</t>
+          <t>10628.18</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-2964</t>
+          <t>-1880</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>1193.78467296645</t>
+          <t>1216.902052388735</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>1212.47333447167</t>
+          <t>1344.047639211305</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>29696</v>
+        <v>21173</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="BF23" t="inlineStr">
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>11.89</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>30366</t>
+          <t>30590</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>92.6</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/期貨業.xlsx
+++ b/Result/checksun_type/期貨業.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>49.18</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>49.58</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>49.16</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>49.58</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>49.16</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>10917653.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>12566466.6</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>12566466.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>12794356.8</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>11192472.92</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>11192472.92</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-172793.2263642792</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>10917653</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>10917653.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>49.0</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>49.58</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>49.14</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>49.58</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>49.14</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>8085769.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>11596388.6</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>11596388.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>13292107.0</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>11264689.06</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>11264689.06</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>13133.16794023849</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>8085769</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>8085769.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>48.9</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>49.6</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>49.14</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>49.14</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>21344598.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>14923710.6</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>14923710.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>13956611.9</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>11357891.38</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>11357891.38</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>581689.4038059711</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>21344598</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>21344598.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,21 +2347,17 @@
           <t>49.01000000000001</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>49.63</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AM5" t="n">
+        <v>49.63</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>49.15</v>
+      </c>
+      <c r="AO5" t="inlineStr">
         <is>
           <t>49.15</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>49.15</t>
-        </is>
-      </c>
       <c r="AP5" t="inlineStr">
         <is>
           <t>-132.60</t>
@@ -2420,20 +2398,16 @@
           <t>16889257.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>13438369.4</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>13438369.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>13466583.0</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>11395162.18</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>11395162.18</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-47450.8450931944</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>16889257</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>16889257.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,21 +2777,17 @@
           <t>49.26000000000001</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>49.68</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
+      <c r="AM6" t="n">
+        <v>49.68</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>49.15</v>
+      </c>
+      <c r="AO6" t="inlineStr">
         <is>
           <t>49.15</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>49.15</t>
-        </is>
-      </c>
       <c r="AP6" t="inlineStr">
         <is>
           <t>-87.62</t>
@@ -2856,20 +2828,16 @@
           <t>5595056.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>11967912.6</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>11967912.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>13023841.6</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>11508277.46</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>11508277.46</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-467169.9919101018</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>5595056</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>5595056.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,21 +3207,17 @@
           <t>49.42</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>49.69</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AM7" t="n">
+        <v>49.69</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>49.15</v>
+      </c>
+      <c r="AO7" t="inlineStr">
         <is>
           <t>49.15</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>49.15</t>
-        </is>
-      </c>
       <c r="AP7" t="inlineStr">
         <is>
           <t>-74.56</t>
@@ -3292,20 +3258,16 @@
           <t>6067263.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>13022247.0</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>13022247</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>13893145.0</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>11517867.76</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>11517867.76</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>160008.8337768205</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>6067263</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>6067263.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,21 +3637,17 @@
           <t>49.7</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>49.71</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
+      <c r="AM8" t="n">
+        <v>49.71</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>49.16</v>
+      </c>
+      <c r="AO8" t="inlineStr">
         <is>
           <t>49.16</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>49.16</t>
-        </is>
-      </c>
       <c r="AP8" t="inlineStr">
         <is>
           <t>-45.07</t>
@@ -3728,20 +3688,16 @@
           <t>24722379.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>14987825.4</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>14987825.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>14283209.4</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>11515168.36</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>11515168.36</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>999670.3764089644</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>24722379</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>24722379.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>49.97000000000001</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>49.73</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>49.16</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>49.73</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>49.16</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>13917892.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>12989513.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>12989513.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>16157581.3</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>11144720.98</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>11144720.98</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>164721.9238688461</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>13917892</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>13917892.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,21 +4497,17 @@
           <t>50.06</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>49.71</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
+      <c r="AM10" t="n">
+        <v>49.71</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>49.16</v>
+      </c>
+      <c r="AO10" t="inlineStr">
         <is>
           <t>49.16</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>49.16</t>
-        </is>
-      </c>
       <c r="AP10" t="inlineStr">
         <is>
           <t>4.26</t>
@@ -4600,20 +4548,16 @@
           <t>9536973.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>13494796.6</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>13494796.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>15653412.6</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>11004239.68</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>11004239.68</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>123679.1015305072</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>9536973</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>9536973.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>50.0</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>49.67</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>49.13</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>49.67</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>49.13</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>10866728.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>14079770.6</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>14079770.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>15558958.7</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>11059068.34</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>11059068.34</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>530013.5659925062</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>10866728</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>10866728.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>50.0</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>49.65</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>49.12</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>49.65</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>49.12</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>15895155.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>14764043.0</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>14764043</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>15136546.0</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>10951152.16</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>10951152.16</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>949088.5664384887</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>15895155</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>15895155.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>94.64000000000001</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>92.58</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>89.11</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>92.58</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>89.11</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>18772.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>17429.6</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>17429.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>17380.2</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>12316.72</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>12316.72</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-47.51397791963245</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>18772</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>18772.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>94.36</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>92.24</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>88.95</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>92.23999999999999</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>88.95</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>7444.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>17049.8</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>17049.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>17620.3</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>12079.36</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>12079.36</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-243.4898490144406</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>7444</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>7444.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>94.14000000000001</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>91.92</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>88.82</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>91.92</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>88.81999999999999</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>11803.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>20205.2</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>20205.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>19845.5</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>12067.32</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>12067.32</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>698.9549726006335</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>11803</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>11803.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>94.16</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>91.66</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>88.69</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>91.66</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>88.69</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>31270.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>21373.2</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>21373.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>19590.6</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>11958.24</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>11958.24</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>1553.306325886435</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>31270</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>31270.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>94.18</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>91.42</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>88.57</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>91.42</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>88.56999999999999</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>17859.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>17990.2</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>17990.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>17411.4</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>11472.62</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>11472.62</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>632.5830332273472</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>17859</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>17859.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>94.0</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>91.08</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>88.45</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>91.08</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>88.45</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>16873.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>17330.8</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>17330.8</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>17510.1</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>11244.72</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>11244.72</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>731.5646496705303</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>16873</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>16873.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>93.82</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>90.71</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>88.33</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>90.70999999999999</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>88.33</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>23221.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>18190.8</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>18190.8</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>16836.8</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>11205.54</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>11205.54</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>952.4825071011255</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>23221</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>23221.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>93.47999999999999</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>90.35</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>88.23</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>90.34999999999999</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>88.23</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>17643.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>19485.8</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>19485.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>15984.8</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>11103.86</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>11103.86</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>553.9193567483671</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>17643</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>17643.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>92.82</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>89.98</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>88.09</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>89.98</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>88.09</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>14355.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>17808.0</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>17808</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>16039.2</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>10954.0</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>10954</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>562.4034506462722</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>14355</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>14355.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>92.16</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>89.63</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>87.95</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>89.63</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>87.95</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>14562.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>16832.6</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>16832.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>19479.0</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>10822.66</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>10822.66</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>906.7234615487687</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>14562</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>14562.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>91.7</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>89.32</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>87.81</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>89.31999999999999</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>87.81</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>21173.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>17689.4</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>17689.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>19569.4</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>10628.18</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>10628.18</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>1344.047639211305</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>21173</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>21173.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>

--- a/Result/checksun_type/期貨業.xlsx
+++ b/Result/checksun_type/期貨業.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>220.404</t>
+          <t>207.186</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,92 +898,92 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>49.95</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>6.05</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-02-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-02-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>49.7</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>49.55</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-1.78</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>58.3</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>57.5</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-02-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-02-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>49.55</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>58.3</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>57.5</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>207</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>44.41</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
+          <t>49.33</t>
+        </is>
+      </c>
+      <c r="AM2" t="n">
+        <v>49.61</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>49.18</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
           <t>49.18</t>
         </is>
       </c>
-      <c r="AM2" t="n">
-        <v>49.58</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>49.16</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>49.17</t>
-        </is>
-      </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-179.21</t>
+          <t>-42.74</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-97.59</t>
+          <t>-97.82</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>26612183.2167382</t>
+          <t>26596260.96428571</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>10917653.0</t>
+          <t>10311071.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>12566466.6</v>
+        <v>13509669.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>12794356.8</t>
+          <t>12738791.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>11192472.92</v>
+        <v>11218520</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-227890</t>
+          <t>770878</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>251747.3389076761</t>
+          <t>160076.1295805972</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-172793.2263642792</t>
+          <t>-344115.5217183363</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>10917653.0</t>
+          <t>10311071.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>10.38</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>16.84</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>12422</t>
+          <t>12484</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>164.837</t>
+          <t>220.404</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-12.76</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,37 +1444,37 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>207</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>44.41</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1484,33 +1484,33 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.18</t>
         </is>
       </c>
       <c r="AM3" t="n">
         <v>49.58</v>
       </c>
       <c r="AN3" t="n">
-        <v>49.14</v>
+        <v>49.16</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>49.16</t>
+          <t>49.17</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-222.32</t>
+          <t>-179.21</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-96.50</t>
+          <t>-97.59</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>26612183.2167382</t>
+          <t>26596260.96428571</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>8085769.0</t>
+          <t>10917653.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>11596388.6</v>
+        <v>12566466.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>13292107.0</t>
+          <t>12794356.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>11264689.06</v>
+        <v>11192472.92</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-1695718</t>
+          <t>-227890</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>328936.5325934861</t>
+          <t>251747.3389076761</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>13133.16794023849</t>
+          <t>-172793.2263642792</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>8085769.0</t>
+          <t>10917653.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>10.38</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>16.84</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>12422</t>
+          <t>12484</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>437.14</t>
+          <t>164.837</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>-12.76</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14.52</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,37 +1874,37 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>207</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1914,23 +1914,23 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>49.6</v>
+        <v>49.58</v>
       </c>
       <c r="AN4" t="n">
         <v>49.14</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>49.16</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-178.57</t>
+          <t>-222.32</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-94.56</t>
+          <t>-96.50</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>26612183.2167382</t>
+          <t>26596260.96428571</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>21344598.0</t>
+          <t>8085769.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>14923710.6</v>
+        <v>11596388.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>13956611.9</t>
+          <t>13292107.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>11357891.38</v>
+        <v>11264689.06</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>967098</t>
+          <t>-1695718</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>386355.3261668038</t>
+          <t>328936.5325934861</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>581689.4038059711</t>
+          <t>13133.16794023849</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>21344598.0</t>
+          <t>8085769.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>10.38</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>16.84</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>12422</t>
+          <t>12484</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>346.337</t>
+          <t>437.14</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11.50</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,54 +2304,54 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>207</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>11.49</t>
+          <t>16.09</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>49.01000000000001</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>49.63</v>
+        <v>49.6</v>
       </c>
       <c r="AN5" t="n">
-        <v>49.15</v>
+        <v>49.14</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2360,17 +2360,17 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-132.60</t>
+          <t>-178.57</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-92.13</t>
+          <t>-94.56</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>26612183.2167382</t>
+          <t>26596260.96428571</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>16889257.0</t>
+          <t>21344598.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>13438369.4</v>
+        <v>14923710.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>13466583.0</t>
+          <t>13956611.9</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>11395162.18</v>
+        <v>11357891.38</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-28213</t>
+          <t>967098</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>350840.0393233188</t>
+          <t>386355.3261668038</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-47450.8450931944</t>
+          <t>581689.4038059711</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>16889257.0</t>
+          <t>21344598.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>10.38</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>16.84</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>12422</t>
+          <t>12484</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,12 +2556,12 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>113.787</t>
+          <t>346.337</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-8.11</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>11.50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,17 +2734,17 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>207</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -2754,17 +2754,17 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2774,11 +2774,11 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>49.26000000000001</t>
+          <t>49.01000000000001</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>49.68</v>
+        <v>49.63</v>
       </c>
       <c r="AN6" t="n">
         <v>49.15</v>
@@ -2790,17 +2790,17 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-87.62</t>
+          <t>-132.60</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-89.52</t>
+          <t>-92.13</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>26612183.2167382</t>
+          <t>26596260.96428571</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>5595056.0</t>
+          <t>16889257.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>11967912.6</v>
+        <v>13438369.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>13023841.6</t>
+          <t>13466583.0</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>11508277.46</v>
+        <v>11395162.18</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-1055929</t>
+          <t>-28213</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>423256.5637626849</t>
+          <t>350840.0393233188</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-467169.9919101018</t>
+          <t>-47450.8450931944</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>5595056.0</t>
+          <t>16889257.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>10.38</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>16.84</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>12422</t>
+          <t>12484</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>124.255</t>
+          <t>113.787</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-8.11</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,37 +3164,37 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>207</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>31.03</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>11.49</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -3204,11 +3204,11 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>49.26000000000001</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>49.69</v>
+        <v>49.68</v>
       </c>
       <c r="AN7" t="n">
         <v>49.15</v>
@@ -3220,17 +3220,17 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-74.56</t>
+          <t>-87.62</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-87.23</t>
+          <t>-89.52</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>26612183.2167382</t>
+          <t>26596260.96428571</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>6067263.0</t>
+          <t>5595056.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>13022247</v>
+        <v>11967912.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>13893145.0</t>
+          <t>13023841.6</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>11517867.76</v>
+        <v>11508277.46</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-870898</t>
+          <t>-1055929</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>585152.301157737</t>
+          <t>423256.5637626849</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>160008.8337768205</t>
+          <t>-467169.9919101018</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>6067263.0</t>
+          <t>5595056.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>10.38</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>16.84</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>12422</t>
+          <t>12484</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>48.95</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>505.389</t>
+          <t>124.255</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,37 +3594,37 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>207</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -3634,33 +3634,33 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>49.71</v>
+        <v>49.69</v>
       </c>
       <c r="AN8" t="n">
-        <v>49.16</v>
+        <v>49.15</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>49.16</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-45.07</t>
+          <t>-74.56</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-84.85</t>
+          <t>-87.23</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>26612183.2167382</t>
+          <t>26596260.96428571</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>24722379.0</t>
+          <t>6067263.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>14987825.4</v>
+        <v>13022247</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>14283209.4</t>
+          <t>13893145.0</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>11515168.36</v>
+        <v>11517867.76</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>704616</t>
+          <t>-870898</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>662451.1134088128</t>
+          <t>585152.301157737</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>999670.3764089644</t>
+          <t>160008.8337768205</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>24722379.0</t>
+          <t>6067263.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>10.38</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>16.84</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>12422</t>
+          <t>12484</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>48.95</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>280.155</t>
+          <t>505.389</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,74 +3908,74 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>48.75</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>4.93</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-02-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-02-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
           <t>49.55</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>-19.61</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-02-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-02-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>49.55</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
       <c r="T9" t="inlineStr">
         <is>
           <t>58.3</t>
@@ -3988,12 +3988,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>9.30</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>207</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4039,60 +4039,60 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>49.97000000000001</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>49.73</v>
+        <v>49.71</v>
       </c>
       <c r="AN9" t="n">
         <v>49.16</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>49.17</t>
+          <t>49.16</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-10.99</t>
+          <t>-45.07</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
           <t>0.23</t>
         </is>
       </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>0.26</t>
-        </is>
-      </c>
       <c r="AS9" t="inlineStr">
         <is>
           <t>1.55</t>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-83.14</t>
+          <t>-84.85</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,48 +4110,48 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>26612183.2167382</t>
+          <t>26596260.96428571</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>13917892.0</t>
+          <t>24722379.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>12989513.2</v>
+        <v>14987825.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>16157581.3</t>
+          <t>14283209.4</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>11144720.98</v>
+        <v>11515168.36</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-3168068</t>
+          <t>704616</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>601138.5201360579</t>
+          <t>662451.1134088128</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>164721.9238688461</t>
+          <t>999670.3764089644</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>13917892.0</t>
+          <t>24722379.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>10.38</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>16.84</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>12422</t>
+          <t>12484</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4313,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4323,42 +4323,42 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>-0.9</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>280.155</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>49.55</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>190.635</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-0.6</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-13.79</t>
+          <t>-19.61</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>9.30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,37 +4454,37 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>207</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -4494,33 +4494,33 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>50.06</t>
+          <t>49.97000000000001</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>49.71</v>
+        <v>49.73</v>
       </c>
       <c r="AN10" t="n">
         <v>49.16</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>49.16</t>
+          <t>49.17</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>-10.99</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-82.68</t>
+          <t>-83.14</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>26612183.2167382</t>
+          <t>26596260.96428571</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>9536973.0</t>
+          <t>13917892.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>13494796.6</v>
+        <v>12989513.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>15653412.6</t>
+          <t>16157581.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>11004239.68</v>
+        <v>11144720.98</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-2158616</t>
+          <t>-3168068</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>680486.9921846419</t>
+          <t>601138.5201360579</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>123679.1015305072</t>
+          <t>164721.9238688461</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>9536973.0</t>
+          <t>13917892.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>10.38</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>16.84</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>12422</t>
+          <t>12484</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>216.851</t>
+          <t>190.635</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-9.51</t>
+          <t>-13.79</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>7.20</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>207</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,39 +4899,39 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>71.76</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>50.06</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>49.67</v>
+        <v>49.71</v>
       </c>
       <c r="AN11" t="n">
-        <v>49.13</v>
+        <v>49.16</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -4940,12 +4940,12 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-82.86</t>
+          <t>-82.68</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>26612183.2167382</t>
+          <t>26596260.96428571</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>10866728.0</t>
+          <t>9536973.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>14079770.6</v>
+        <v>13494796.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>15558958.7</t>
+          <t>15653412.6</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>11059068.34</v>
+        <v>11004239.68</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-1479188</t>
+          <t>-2158616</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>781724.7904853937</t>
+          <t>680486.9921846419</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>530013.5659925062</t>
+          <t>123679.1015305072</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>10866728.0</t>
+          <t>9536973.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>10.38</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>16.84</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>12422</t>
+          <t>12484</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,17 +5136,17 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>316.682</t>
+          <t>216.851</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-9.51</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5278,12 +5278,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>7.20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,32 +5314,32 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>207</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>77.31</t>
+          <t>71.76</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -5358,29 +5358,29 @@
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>49.65</v>
+        <v>49.67</v>
       </c>
       <c r="AN12" t="n">
-        <v>49.12</v>
+        <v>49.13</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>49.16</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-83.26</t>
+          <t>-82.86</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>26612183.2167382</t>
+          <t>26596260.96428571</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>15895155.0</t>
+          <t>10866728.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>14764043</v>
+        <v>14079770.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>15136546.0</t>
+          <t>15558958.7</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>10951152.16</v>
+        <v>11059068.34</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-372503</t>
+          <t>-1479188</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>827490.4676659188</t>
+          <t>781724.7904853937</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>949088.5664384887</t>
+          <t>530013.5659925062</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>15895155.0</t>
+          <t>10866728.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>10.38</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>16.84</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>12422</t>
+          <t>12484</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>50.4</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>49.95</t>
-        </is>
-      </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.27</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11.05</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,37 +5744,37 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>97.22</t>
+          <t>98.15</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -5784,23 +5784,23 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>94.64000000000001</t>
+          <t>94.86</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>92.58</v>
+        <v>92.88</v>
       </c>
       <c r="AN13" t="n">
-        <v>89.11</v>
+        <v>89.27</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>87.81</t>
+          <t>87.97</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-55.07</t>
+          <t>-54.52</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,48 +5830,48 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>19326.08369098713</t>
+          <t>19319.76214285714</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>18772.0</t>
+          <t>9934.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>17429.6</v>
+        <v>15844.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>17380.2</t>
+          <t>16917.4</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>12316.72</v>
+        <v>12366.42</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>-1072</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>644.4213010847493</t>
+          <t>457.2806365016687</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-47.51397791963245</t>
+          <t>-571.9930187052742</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>18772.0</t>
+          <t>9934.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>11.89</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>25.92</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>30590</t>
+          <t>30558</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>95.1</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>8.58</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,12 +6174,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6189,58 +6189,58 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>88.89</t>
+          <t>97.22</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>94.36</t>
+          <t>94.64000000000001</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>92.23999999999999</v>
+        <v>92.58</v>
       </c>
       <c r="AN14" t="n">
-        <v>88.95</v>
+        <v>89.11</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>87.64</t>
+          <t>87.81</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-55.73</t>
+          <t>-55.07</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,48 +6260,48 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>19326.08369098713</t>
+          <t>19319.76214285714</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>7444.0</t>
+          <t>18772.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>17049.8</v>
+        <v>17429.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>17620.3</t>
+          <t>17380.2</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>12079.36</v>
+        <v>12316.72</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-570</t>
+          <t>49</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>770.2277154491823</t>
+          <t>644.4213010847493</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-243.4898490144406</t>
+          <t>-47.51397791963245</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>7444.0</t>
+          <t>18772.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>11.89</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>25.92</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>30590</t>
+          <t>30558</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>95.1</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>8.58</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>6.99</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>88.89</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>94.14000000000001</t>
+          <t>94.36</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>91.92</v>
+        <v>92.23999999999999</v>
       </c>
       <c r="AN15" t="n">
-        <v>88.81999999999999</v>
+        <v>88.95</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>87.49</t>
+          <t>87.64</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-56.30</t>
+          <t>-55.73</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,48 +6690,48 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>19326.08369098713</t>
+          <t>19319.76214285714</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>11803.0</t>
+          <t>7444.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>20205.2</v>
+        <v>17049.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>19845.5</t>
+          <t>17620.3</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>12067.32</v>
+        <v>12079.36</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>-570</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>954.5399998971137</t>
+          <t>770.2277154491823</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>698.9549726006335</t>
+          <t>-243.4898490144406</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>11803.0</t>
+          <t>7444.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>11.89</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>25.92</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>30590</t>
+          <t>30558</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>334.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18.84</t>
+          <t>6.99</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,209 +7034,209 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>88.02</t>
+          <t>87.88</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>94.16</t>
+          <t>94.14000000000001</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>91.66</v>
+        <v>91.92</v>
       </c>
       <c r="AN16" t="n">
-        <v>88.69</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>87.34</t>
+          <t>87.49</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>-56.30</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>2025/10/15</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>19319.76214285714</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>11803.0</t>
+        </is>
+      </c>
+      <c r="AX16" t="n">
+        <v>20205.2</v>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>19845.5</t>
+        </is>
+      </c>
+      <c r="AZ16" t="n">
+        <v>12067.32</v>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>954.5399998971137</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>698.9549726006335</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>11803.0</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>2025/10/23</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>5.83</t>
+        </is>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>元大期貨</t>
+        </is>
+      </c>
+      <c r="BJ16" t="inlineStr">
+        <is>
+          <t>元大期貨</t>
+        </is>
+      </c>
+      <c r="BK16" t="inlineStr">
+        <is>
+          <t>金融業</t>
+        </is>
+      </c>
+      <c r="BL16" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM16" t="inlineStr">
+        <is>
+          <t>0.27</t>
+        </is>
+      </c>
+      <c r="BN16" t="inlineStr">
+        <is>
+          <t>0.586310700095985</t>
+        </is>
+      </c>
+      <c r="BO16" t="inlineStr">
+        <is>
+          <t>8.007619922843494</t>
+        </is>
+      </c>
+      <c r="BP16" t="inlineStr">
+        <is>
+          <t>-12.34648294771329</t>
+        </is>
+      </c>
+      <c r="BQ16" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR16" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS16" t="inlineStr">
+        <is>
           <t>1.61</t>
         </is>
       </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="AT16" t="inlineStr">
-        <is>
-          <t>-56.98</t>
-        </is>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>2025/10/15</t>
-        </is>
-      </c>
-      <c r="AV16" t="inlineStr">
-        <is>
-          <t>19326.08369098713</t>
-        </is>
-      </c>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>31270.0</t>
-        </is>
-      </c>
-      <c r="AX16" t="n">
-        <v>21373.2</v>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>19590.6</t>
-        </is>
-      </c>
-      <c r="AZ16" t="n">
-        <v>11958.24</v>
-      </c>
-      <c r="BA16" t="inlineStr">
-        <is>
-          <t>1782</t>
-        </is>
-      </c>
-      <c r="BB16" t="inlineStr">
-        <is>
-          <t>1001.01000486011</t>
-        </is>
-      </c>
-      <c r="BC16" t="inlineStr">
-        <is>
-          <t>1553.306325886435</t>
-        </is>
-      </c>
-      <c r="BD16" t="inlineStr">
-        <is>
-          <t>31270.0</t>
-        </is>
-      </c>
-      <c r="BE16" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="BF16" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr">
-        <is>
-          <t>2025/10/23</t>
-        </is>
-      </c>
-      <c r="BH16" t="inlineStr">
-        <is>
-          <t>5.27</t>
-        </is>
-      </c>
-      <c r="BI16" t="inlineStr">
-        <is>
-          <t>元大期貨</t>
-        </is>
-      </c>
-      <c r="BJ16" t="inlineStr">
-        <is>
-          <t>元大期貨</t>
-        </is>
-      </c>
-      <c r="BK16" t="inlineStr">
-        <is>
-          <t>金融業</t>
-        </is>
-      </c>
-      <c r="BL16" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM16" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="BN16" t="inlineStr">
-        <is>
-          <t>0.586310700095985</t>
-        </is>
-      </c>
-      <c r="BO16" t="inlineStr">
-        <is>
-          <t>8.007619922843494</t>
-        </is>
-      </c>
-      <c r="BP16" t="inlineStr">
-        <is>
-          <t>-12.34648294771329</t>
-        </is>
-      </c>
-      <c r="BQ16" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
-        </is>
-      </c>
-      <c r="BR16" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS16" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>11.89</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>25.92</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>30590</t>
+          <t>30558</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>188.0</t>
+          <t>334.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>93.9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10.60</t>
+          <t>18.84</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>96.97</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>90.22</t>
+          <t>88.02</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>94.18</t>
+          <t>94.16</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>91.42</v>
+        <v>91.66</v>
       </c>
       <c r="AN17" t="n">
-        <v>88.56999999999999</v>
+        <v>88.69</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.34</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>14.91</t>
+          <t>9.14</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-57.96</t>
+          <t>-56.98</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,48 +7550,48 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>19326.08369098713</t>
+          <t>19319.76214285714</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>17859.0</t>
+          <t>31270.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>17990.2</v>
+        <v>21373.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>17411.4</t>
+          <t>19590.6</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>11472.62</v>
+        <v>11958.24</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>900.5924919462329</t>
+          <t>1001.01000486011</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>632.5830332273472</t>
+          <t>1553.306325886435</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>17859.0</t>
+          <t>31270.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,22 +7651,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>11.89</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>25.92</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>30590</t>
+          <t>30558</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>93.9</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>188.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.60</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>92.11</t>
+          <t>96.97</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>91.23</t>
+          <t>90.22</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>94.18</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>91.08</v>
+        <v>91.42</v>
       </c>
       <c r="AN18" t="n">
-        <v>88.45</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>87.06</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>18.54</t>
+          <t>14.91</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-59.53</t>
+          <t>-57.96</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,48 +7980,48 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>19326.08369098713</t>
+          <t>19319.76214285714</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>16873.0</t>
+          <t>17859.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>17330.8</v>
+        <v>17990.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>17510.1</t>
+          <t>17411.4</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>11244.72</v>
+        <v>11472.62</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-179</t>
+          <t>578</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>949.3214844405758</t>
+          <t>900.5924919462329</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>731.5646496705303</t>
+          <t>632.5830332273472</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>16873.0</t>
+          <t>17859.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>11.89</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>25.92</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>30590</t>
+          <t>30558</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>8.04</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>81.58</t>
+          <t>92.11</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>93.86</t>
+          <t>91.23</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>93.82</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>90.70999999999999</v>
+        <v>91.08</v>
       </c>
       <c r="AN19" t="n">
-        <v>88.33</v>
+        <v>88.45</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>86.93</t>
+          <t>87.06</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>22.80</t>
+          <t>18.54</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-61.41</t>
+          <t>-59.53</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,48 +8410,48 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>19326.08369098713</t>
+          <t>19319.76214285714</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>23221.0</t>
+          <t>16873.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>18190.8</v>
+        <v>17330.8</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>16836.8</t>
+          <t>17510.1</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>11205.54</v>
+        <v>11244.72</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>-179</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>988.9136362169477</t>
+          <t>949.3214844405758</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>952.4825071011255</t>
+          <t>731.5646496705303</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>23221.0</t>
+          <t>16873.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>11.89</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>25.92</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>30590</t>
+          <t>30558</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
+          <t>93.9</t>
+        </is>
+      </c>
+      <c r="CE19" t="inlineStr">
+        <is>
           <t>94.7</t>
         </is>
       </c>
-      <c r="CE19" t="inlineStr">
-        <is>
-          <t>94.7</t>
-        </is>
-      </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>187.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>21.90</t>
+          <t>8.04</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10.55</t>
+          <t>13.99</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>81.58</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.86</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>93.47999999999999</t>
+          <t>93.82</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>90.34999999999999</v>
+        <v>90.70999999999999</v>
       </c>
       <c r="AN20" t="n">
-        <v>88.23</v>
+        <v>88.33</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.93</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>22.80</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-63.61</t>
+          <t>-61.41</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,48 +8840,48 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>19326.08369098713</t>
+          <t>19319.76214285714</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>17643.0</t>
+          <t>23221.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>19485.8</v>
+        <v>18190.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>15984.8</t>
+          <t>16836.8</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>11103.86</v>
+        <v>11205.54</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>3501</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>995.53747787437</t>
+          <t>988.9136362169477</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>553.9193567483671</t>
+          <t>952.4825071011255</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>17643.0</t>
+          <t>23221.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>5.16</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,22 +8941,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>11.89</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>25.92</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>30590</t>
+          <t>30558</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>187.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>11.03</t>
+          <t>21.90</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9108,7 +9108,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>7.55</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>8.63</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,12 +9184,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9204,53 +9204,53 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>92.82</t>
+          <t>93.47999999999999</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>89.98</v>
+        <v>90.34999999999999</v>
       </c>
       <c r="AN21" t="n">
-        <v>88.09</v>
+        <v>88.23</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>86.66</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>30.52</t>
+          <t>29.27</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-66.27</t>
+          <t>-63.61</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,48 +9270,48 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>19326.08369098713</t>
+          <t>19319.76214285714</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>14355.0</t>
+          <t>17643.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>17808</v>
+        <v>19485.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>16039.2</t>
+          <t>15984.8</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>10954</v>
+        <v>11103.86</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>1768</t>
+          <t>3501</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>1075.831681715461</t>
+          <t>995.53747787437</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>562.4034506462722</t>
+          <t>553.9193567483671</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>14355.0</t>
+          <t>17643.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>11.89</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>25.92</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>30590</t>
+          <t>30558</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9518,7 +9518,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-13.59</t>
+          <t>11.03</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9538,7 +9538,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -9578,7 +9578,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>7.55</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>8.80</t>
+          <t>8.63</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9634,53 +9634,53 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>92.82</t>
+        </is>
+      </c>
+      <c r="AM22" t="n">
+        <v>89.98</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>88.09</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>86.66</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>30.52</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
           <t>1.65</t>
         </is>
       </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>92.16</t>
-        </is>
-      </c>
-      <c r="AM22" t="n">
-        <v>89.63</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>87.95</v>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>86.52</t>
-        </is>
-      </c>
-      <c r="AP22" t="inlineStr">
-        <is>
-          <t>31.22</t>
-        </is>
-      </c>
-      <c r="AQ22" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-68.84</t>
+          <t>-66.27</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,48 +9700,48 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>19326.08369098713</t>
+          <t>19319.76214285714</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>14562.0</t>
+          <t>14355.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>16832.6</v>
+        <v>17808</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>19479.0</t>
+          <t>16039.2</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>10822.66</v>
+        <v>10954</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-2646</t>
+          <t>1768</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>1169.182269182587</t>
+          <t>1075.831681715461</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>906.7234615487687</t>
+          <t>562.4034506462722</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>14562.0</t>
+          <t>14355.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>11.89</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>25.92</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>30590</t>
+          <t>30558</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>227.0</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-9.61</t>
+          <t>-13.59</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9968,7 +9968,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12.80</t>
+          <t>8.80</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10064,53 +10064,53 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>92.16</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>89.31999999999999</v>
+        <v>89.63</v>
       </c>
       <c r="AN23" t="n">
-        <v>87.81</v>
+        <v>87.95</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>86.52</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>31.22</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-71.27</t>
+          <t>-68.84</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,48 +10130,48 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>19326.08369098713</t>
+          <t>19319.76214285714</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>21173.0</t>
+          <t>14562.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>17689.4</v>
+        <v>16832.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>19569.4</t>
+          <t>19479.0</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>10628.18</v>
+        <v>10822.66</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-1880</t>
+          <t>-2646</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>1216.902052388735</t>
+          <t>1169.182269182587</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>1344.047639211305</t>
+          <t>906.7234615487687</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>21173.0</t>
+          <t>14562.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="BF23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>11.89</t>
+          <t>11.88</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>25.92</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>30590</t>
+          <t>30558</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
+          <t>93.6</t>
+        </is>
+      </c>
+      <c r="CF23" t="inlineStr">
+        <is>
+          <t>92.4</t>
+        </is>
+      </c>
+      <c r="CG23" t="inlineStr">
+        <is>
           <t>93.5</t>
-        </is>
-      </c>
-      <c r="CF23" t="inlineStr">
-        <is>
-          <t>92.1</t>
-        </is>
-      </c>
-      <c r="CG23" t="inlineStr">
-        <is>
-          <t>93.3</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/期貨業.xlsx
+++ b/Result/checksun_type/期貨業.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>207.186</t>
+          <t>187.779</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>188</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.83</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>90.61</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.56</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>49.61</v>
+        <v>49.63</v>
       </c>
       <c r="AN2" t="n">
-        <v>49.18</v>
+        <v>49.2</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>49.18</t>
+          <t>49.19</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-42.74</t>
+          <t>41.80</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,53 +1090,53 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-97.82</t>
+          <t>-97.56</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2025/10/09</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>26596260.96428571</t>
+          <t>26578338.83238231</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>10311071.0</t>
+          <t>9355231.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>13509669.6</v>
+        <v>12002864.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>12738791.1</t>
+          <t>12720616.9</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>11218520</v>
+        <v>11280841.36</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>770878</t>
+          <t>-717752</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>160076.1295805972</t>
+          <t>54352.68804154852</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-344115.5217183363</t>
+          <t>-527126.2404232193</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>10311071.0</t>
+          <t>9355231.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>10.42</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>16.84</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>12484</t>
+          <t>12472</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>220.404</t>
+          <t>207.186</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,92 +1328,92 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>49.95</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-0.1</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>6.05</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-02-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-02-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>49.7</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>49.55</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-1.78</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>58.3</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>57.5</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-02-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-02-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>49.55</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>58.3</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>57.5</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>188</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>44.41</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
+          <t>49.33</t>
+        </is>
+      </c>
+      <c r="AM3" t="n">
+        <v>49.61</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>49.18</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
           <t>49.18</t>
         </is>
       </c>
-      <c r="AM3" t="n">
-        <v>49.58</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>49.16</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>49.17</t>
-        </is>
-      </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-179.21</t>
+          <t>-42.74</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,53 +1520,53 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-97.59</t>
+          <t>-97.82</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2025/10/09</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>26596260.96428571</t>
+          <t>26578338.83238231</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>10917653.0</t>
+          <t>10311071.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>12566466.6</v>
+        <v>13509669.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>12794356.8</t>
+          <t>12738791.1</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>11192472.92</v>
+        <v>11218520</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-227890</t>
+          <t>770878</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>251747.3389076761</t>
+          <t>160076.1295805972</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-172793.2263642792</t>
+          <t>-344115.5217183363</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>10917653.0</t>
+          <t>10311071.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>10.42</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>16.84</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>12484</t>
+          <t>12472</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>164.837</t>
+          <t>220.404</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-12.76</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,37 +1874,37 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>188</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>44.41</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1914,33 +1914,33 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.18</t>
         </is>
       </c>
       <c r="AM4" t="n">
         <v>49.58</v>
       </c>
       <c r="AN4" t="n">
-        <v>49.14</v>
+        <v>49.16</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>49.16</t>
+          <t>49.17</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-222.32</t>
+          <t>-179.21</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,53 +1950,53 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-96.50</t>
+          <t>-97.59</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2025/10/09</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>26596260.96428571</t>
+          <t>26578338.83238231</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>8085769.0</t>
+          <t>10917653.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>11596388.6</v>
+        <v>12566466.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>13292107.0</t>
+          <t>12794356.8</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>11264689.06</v>
+        <v>11192472.92</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-1695718</t>
+          <t>-227890</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>328936.5325934861</t>
+          <t>251747.3389076761</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>13133.16794023849</t>
+          <t>-172793.2263642792</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>8085769.0</t>
+          <t>10917653.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>10.42</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>16.84</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>12484</t>
+          <t>12472</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>437.14</t>
+          <t>164.837</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>-12.76</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.52</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,37 +2304,37 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>188</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -2344,23 +2344,23 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>49.6</v>
+        <v>49.58</v>
       </c>
       <c r="AN5" t="n">
         <v>49.14</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>49.16</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-178.57</t>
+          <t>-222.32</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,53 +2380,53 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-94.56</t>
+          <t>-96.50</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2025/10/09</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>26596260.96428571</t>
+          <t>26578338.83238231</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>21344598.0</t>
+          <t>8085769.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>14923710.6</v>
+        <v>11596388.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>13956611.9</t>
+          <t>13292107.0</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>11357891.38</v>
+        <v>11264689.06</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>967098</t>
+          <t>-1695718</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>386355.3261668038</t>
+          <t>328936.5325934861</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>581689.4038059711</t>
+          <t>13133.16794023849</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>21344598.0</t>
+          <t>8085769.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>10.42</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>16.84</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>12484</t>
+          <t>12472</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2561,17 +2561,17 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>346.337</t>
+          <t>437.14</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11.50</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,54 +2734,54 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>188</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>11.49</t>
+          <t>16.09</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>49.01000000000001</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>49.63</v>
+        <v>49.6</v>
       </c>
       <c r="AN6" t="n">
-        <v>49.15</v>
+        <v>49.14</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2790,17 +2790,17 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-132.60</t>
+          <t>-178.57</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,53 +2810,53 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-92.13</t>
+          <t>-94.56</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2025/10/09</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>26596260.96428571</t>
+          <t>26578338.83238231</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>16889257.0</t>
+          <t>21344598.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>13438369.4</v>
+        <v>14923710.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>13466583.0</t>
+          <t>13956611.9</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>11395162.18</v>
+        <v>11357891.38</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-28213</t>
+          <t>967098</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>350840.0393233188</t>
+          <t>386355.3261668038</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-47450.8450931944</t>
+          <t>581689.4038059711</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>16889257.0</t>
+          <t>21344598.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>10.42</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>16.84</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>12484</t>
+          <t>12472</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>113.787</t>
+          <t>346.337</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-8.11</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>11.50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,17 +3164,17 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>188</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -3184,17 +3184,17 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -3204,11 +3204,11 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>49.26000000000001</t>
+          <t>49.01000000000001</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>49.68</v>
+        <v>49.63</v>
       </c>
       <c r="AN7" t="n">
         <v>49.15</v>
@@ -3220,17 +3220,17 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-87.62</t>
+          <t>-132.60</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,53 +3240,53 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-89.52</t>
+          <t>-92.13</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2025/10/09</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>26596260.96428571</t>
+          <t>26578338.83238231</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>5595056.0</t>
+          <t>16889257.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>11967912.6</v>
+        <v>13438369.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>13023841.6</t>
+          <t>13466583.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>11508277.46</v>
+        <v>11395162.18</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-1055929</t>
+          <t>-28213</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>423256.5637626849</t>
+          <t>350840.0393233188</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-467169.9919101018</t>
+          <t>-47450.8450931944</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>5595056.0</t>
+          <t>16889257.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>10.42</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>16.84</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>12484</t>
+          <t>12472</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>124.255</t>
+          <t>113.787</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-8.11</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,37 +3594,37 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>188</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>31.03</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>11.49</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -3634,11 +3634,11 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>49.26000000000001</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>49.69</v>
+        <v>49.68</v>
       </c>
       <c r="AN8" t="n">
         <v>49.15</v>
@@ -3650,17 +3650,17 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-74.56</t>
+          <t>-87.62</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,53 +3670,53 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-87.23</t>
+          <t>-89.52</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2025/10/09</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>26596260.96428571</t>
+          <t>26578338.83238231</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>6067263.0</t>
+          <t>5595056.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>13022247</v>
+        <v>11967912.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>13893145.0</t>
+          <t>13023841.6</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>11517867.76</v>
+        <v>11508277.46</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-870898</t>
+          <t>-1055929</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>585152.301157737</t>
+          <t>423256.5637626849</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>160008.8337768205</t>
+          <t>-467169.9919101018</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>6067263.0</t>
+          <t>5595056.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>10.42</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>16.84</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>12484</t>
+          <t>12472</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>48.95</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>505.389</t>
+          <t>124.255</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,37 +4024,37 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>188</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -4064,33 +4064,33 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>49.71</v>
+        <v>49.69</v>
       </c>
       <c r="AN9" t="n">
-        <v>49.16</v>
+        <v>49.15</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>49.16</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-45.07</t>
+          <t>-74.56</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,53 +4100,53 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-84.85</t>
+          <t>-87.23</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2025/10/09</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>26596260.96428571</t>
+          <t>26578338.83238231</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>24722379.0</t>
+          <t>6067263.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>14987825.4</v>
+        <v>13022247</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>14283209.4</t>
+          <t>13893145.0</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>11515168.36</v>
+        <v>11517867.76</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>704616</t>
+          <t>-870898</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>662451.1134088128</t>
+          <t>585152.301157737</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>999670.3764089644</t>
+          <t>160008.8337768205</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>24722379.0</t>
+          <t>6067263.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>10.42</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>16.84</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>12484</t>
+          <t>12472</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,12 +4276,12 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>48.95</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>280.155</t>
+          <t>505.389</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,74 +4338,74 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>48.75</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>4.93</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-02-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-02-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
           <t>49.55</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>-19.61</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-02-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-02-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>49.55</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
       <c r="T10" t="inlineStr">
         <is>
           <t>58.3</t>
@@ -4418,12 +4418,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>9.30</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>188</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4469,60 +4469,60 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>49.97000000000001</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>49.73</v>
+        <v>49.71</v>
       </c>
       <c r="AN10" t="n">
         <v>49.16</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>49.17</t>
+          <t>49.16</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-10.99</t>
+          <t>-45.07</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
           <t>0.23</t>
         </is>
       </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>0.26</t>
-        </is>
-      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>1.55</t>
@@ -4530,58 +4530,58 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-83.14</t>
+          <t>-84.85</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2025/10/09</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>26596260.96428571</t>
+          <t>26578338.83238231</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>13917892.0</t>
+          <t>24722379.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>12989513.2</v>
+        <v>14987825.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>16157581.3</t>
+          <t>14283209.4</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>11144720.98</v>
+        <v>11515168.36</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-3168068</t>
+          <t>704616</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>601138.5201360579</t>
+          <t>662451.1134088128</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>164721.9238688461</t>
+          <t>999670.3764089644</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>13917892.0</t>
+          <t>24722379.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>10.42</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>16.84</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>12484</t>
+          <t>12472</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4743,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4753,42 +4753,42 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>-0.9</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>280.155</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>49.55</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>190.635</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-13.79</t>
+          <t>-19.61</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4848,12 +4848,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>9.30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,37 +4884,37 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>188</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -4924,33 +4924,33 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>50.06</t>
+          <t>49.97000000000001</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>49.71</v>
+        <v>49.73</v>
       </c>
       <c r="AN11" t="n">
         <v>49.16</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>49.16</t>
+          <t>49.17</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>-10.99</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,53 +4960,53 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-82.68</t>
+          <t>-83.14</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2025/10/09</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>26596260.96428571</t>
+          <t>26578338.83238231</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>9536973.0</t>
+          <t>13917892.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>13494796.6</v>
+        <v>12989513.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>15653412.6</t>
+          <t>16157581.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>11004239.68</v>
+        <v>11144720.98</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-2158616</t>
+          <t>-3168068</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>680486.9921846419</t>
+          <t>601138.5201360579</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>123679.1015305072</t>
+          <t>164721.9238688461</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>9536973.0</t>
+          <t>13917892.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>10.42</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>16.84</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>12484</t>
+          <t>12472</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>216.851</t>
+          <t>190.635</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-9.51</t>
+          <t>-13.79</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>7.20</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>188</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,39 +5329,39 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>71.76</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>50.06</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>49.67</v>
+        <v>49.71</v>
       </c>
       <c r="AN12" t="n">
-        <v>49.13</v>
+        <v>49.16</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5370,12 +5370,12 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5390,53 +5390,53 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-82.86</t>
+          <t>-82.68</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2025/10/09</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>26596260.96428571</t>
+          <t>26578338.83238231</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>10866728.0</t>
+          <t>9536973.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>14079770.6</v>
+        <v>13494796.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>15558958.7</t>
+          <t>15653412.6</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>11059068.34</v>
+        <v>11004239.68</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-1479188</t>
+          <t>-2158616</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>781724.7904853937</t>
+          <t>680486.9921846419</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>530013.5659925062</t>
+          <t>123679.1015305072</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>10866728.0</t>
+          <t>9536973.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>10.42</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>16.84</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>12484</t>
+          <t>12472</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,17 +5566,17 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-31.56</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>9.27</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5749,32 +5749,32 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>98.15</t>
+          <t>92.59</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -5784,33 +5784,33 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>94.86</t>
+          <t>95.14000000000001</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>92.88</v>
+        <v>93.15000000000001</v>
       </c>
       <c r="AN13" t="n">
-        <v>89.27</v>
+        <v>89.43000000000001</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>87.97</t>
+          <t>88.12</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-54.52</t>
+          <t>-54.27</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,48 +5830,48 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>19319.76214285714</t>
+          <t>19308.55848787447</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>9934.0</t>
+          <t>7644.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>15844.6</v>
+        <v>11119.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>16917.4</t>
+          <t>16246.3</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>12366.42</v>
+        <v>12428.1</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-1072</t>
+          <t>-5126</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>457.2806365016687</t>
+          <t>218.2253813802438</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-571.9930187052742</t>
+          <t>-1096.578521787593</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>9934.0</t>
+          <t>7644.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>11.85</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>25.92</t>
+          <t>25.97</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>30558</t>
+          <t>30494</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.27</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11.05</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6179,32 +6179,32 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>97.22</t>
+          <t>98.15</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -6214,23 +6214,23 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>94.64000000000001</t>
+          <t>94.86</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>92.58</v>
+        <v>92.88</v>
       </c>
       <c r="AN14" t="n">
-        <v>89.11</v>
+        <v>89.27</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>87.81</t>
+          <t>87.97</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-55.07</t>
+          <t>-54.52</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,48 +6260,48 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>19319.76214285714</t>
+          <t>19308.55848787447</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>18772.0</t>
+          <t>9934.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>17429.6</v>
+        <v>15844.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>17380.2</t>
+          <t>16917.4</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>12316.72</v>
+        <v>12366.42</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>-1072</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>644.4213010847493</t>
+          <t>457.2806365016687</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-47.51397791963245</t>
+          <t>-571.9930187052742</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>18772.0</t>
+          <t>9934.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>11.85</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>25.92</t>
+          <t>25.97</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>30558</t>
+          <t>30494</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>95.1</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>8.58</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6609,7 +6609,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6619,58 +6619,58 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>88.89</t>
+          <t>97.22</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>94.36</t>
+          <t>94.64000000000001</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>92.23999999999999</v>
+        <v>92.58</v>
       </c>
       <c r="AN15" t="n">
-        <v>88.95</v>
+        <v>89.11</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>87.64</t>
+          <t>87.81</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-55.73</t>
+          <t>-55.07</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,48 +6690,48 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>19319.76214285714</t>
+          <t>19308.55848787447</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>7444.0</t>
+          <t>18772.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>17049.8</v>
+        <v>17429.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>17620.3</t>
+          <t>17380.2</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>12079.36</v>
+        <v>12316.72</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-570</t>
+          <t>49</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>770.2277154491823</t>
+          <t>644.4213010847493</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-243.4898490144406</t>
+          <t>-47.51397791963245</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>7444.0</t>
+          <t>18772.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>11.85</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>25.92</t>
+          <t>25.97</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>30558</t>
+          <t>30494</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>95.1</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6908,7 +6908,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>8.58</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>6.99</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7039,68 +7039,68 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>88.89</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>94.14000000000001</t>
+          <t>94.36</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>91.92</v>
+        <v>92.23999999999999</v>
       </c>
       <c r="AN16" t="n">
-        <v>88.81999999999999</v>
+        <v>88.95</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>87.49</t>
+          <t>87.64</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-56.30</t>
+          <t>-55.73</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,48 +7120,48 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>19319.76214285714</t>
+          <t>19308.55848787447</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>11803.0</t>
+          <t>7444.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>20205.2</v>
+        <v>17049.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>19845.5</t>
+          <t>17620.3</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>12067.32</v>
+        <v>12079.36</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>-570</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>954.5399998971137</t>
+          <t>770.2277154491823</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>698.9549726006335</t>
+          <t>-243.4898490144406</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>11803.0</t>
+          <t>7444.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>11.85</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>25.92</t>
+          <t>25.97</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>30558</t>
+          <t>30494</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>334.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18.84</t>
+          <t>6.99</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7469,204 +7469,204 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>88.02</t>
+          <t>87.88</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>94.16</t>
+          <t>94.14000000000001</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>91.66</v>
+        <v>91.92</v>
       </c>
       <c r="AN17" t="n">
-        <v>88.69</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>87.34</t>
+          <t>87.49</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>-56.30</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>2025/10/15</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>19308.55848787447</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>11803.0</t>
+        </is>
+      </c>
+      <c r="AX17" t="n">
+        <v>20205.2</v>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>19845.5</t>
+        </is>
+      </c>
+      <c r="AZ17" t="n">
+        <v>12067.32</v>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>954.5399998971137</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>698.9549726006335</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>11803.0</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>2025/10/23</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>5.83</t>
+        </is>
+      </c>
+      <c r="BI17" t="inlineStr">
+        <is>
+          <t>元大期貨</t>
+        </is>
+      </c>
+      <c r="BJ17" t="inlineStr">
+        <is>
+          <t>元大期貨</t>
+        </is>
+      </c>
+      <c r="BK17" t="inlineStr">
+        <is>
+          <t>金融業</t>
+        </is>
+      </c>
+      <c r="BL17" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM17" t="inlineStr">
+        <is>
+          <t>0.27</t>
+        </is>
+      </c>
+      <c r="BN17" t="inlineStr">
+        <is>
+          <t>0.586310700095985</t>
+        </is>
+      </c>
+      <c r="BO17" t="inlineStr">
+        <is>
+          <t>8.007619922843494</t>
+        </is>
+      </c>
+      <c r="BP17" t="inlineStr">
+        <is>
+          <t>-12.34648294771329</t>
+        </is>
+      </c>
+      <c r="BQ17" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR17" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS17" t="inlineStr">
+        <is>
           <t>1.61</t>
         </is>
       </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="AT17" t="inlineStr">
-        <is>
-          <t>-56.98</t>
-        </is>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>2025/10/15</t>
-        </is>
-      </c>
-      <c r="AV17" t="inlineStr">
-        <is>
-          <t>19319.76214285714</t>
-        </is>
-      </c>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>31270.0</t>
-        </is>
-      </c>
-      <c r="AX17" t="n">
-        <v>21373.2</v>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>19590.6</t>
-        </is>
-      </c>
-      <c r="AZ17" t="n">
-        <v>11958.24</v>
-      </c>
-      <c r="BA17" t="inlineStr">
-        <is>
-          <t>1782</t>
-        </is>
-      </c>
-      <c r="BB17" t="inlineStr">
-        <is>
-          <t>1001.01000486011</t>
-        </is>
-      </c>
-      <c r="BC17" t="inlineStr">
-        <is>
-          <t>1553.306325886435</t>
-        </is>
-      </c>
-      <c r="BD17" t="inlineStr">
-        <is>
-          <t>31270.0</t>
-        </is>
-      </c>
-      <c r="BE17" t="inlineStr">
-        <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="BF17" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr">
-        <is>
-          <t>2025/10/23</t>
-        </is>
-      </c>
-      <c r="BH17" t="inlineStr">
-        <is>
-          <t>5.27</t>
-        </is>
-      </c>
-      <c r="BI17" t="inlineStr">
-        <is>
-          <t>元大期貨</t>
-        </is>
-      </c>
-      <c r="BJ17" t="inlineStr">
-        <is>
-          <t>元大期貨</t>
-        </is>
-      </c>
-      <c r="BK17" t="inlineStr">
-        <is>
-          <t>金融業</t>
-        </is>
-      </c>
-      <c r="BL17" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM17" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="BN17" t="inlineStr">
-        <is>
-          <t>0.586310700095985</t>
-        </is>
-      </c>
-      <c r="BO17" t="inlineStr">
-        <is>
-          <t>8.007619922843494</t>
-        </is>
-      </c>
-      <c r="BP17" t="inlineStr">
-        <is>
-          <t>-12.34648294771329</t>
-        </is>
-      </c>
-      <c r="BQ17" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
-        </is>
-      </c>
-      <c r="BR17" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS17" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>11.85</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>25.92</t>
+          <t>25.97</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>30558</t>
+          <t>30494</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>188.0</t>
+          <t>334.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>93.9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10.60</t>
+          <t>18.84</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7899,68 +7899,68 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>96.97</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>90.22</t>
+          <t>88.02</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>94.18</t>
+          <t>94.16</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>91.42</v>
+        <v>91.66</v>
       </c>
       <c r="AN18" t="n">
-        <v>88.56999999999999</v>
+        <v>88.69</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.34</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>14.91</t>
+          <t>9.14</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-57.96</t>
+          <t>-56.98</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,48 +7980,48 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>19319.76214285714</t>
+          <t>19308.55848787447</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>17859.0</t>
+          <t>31270.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>17990.2</v>
+        <v>21373.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>17411.4</t>
+          <t>19590.6</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>11472.62</v>
+        <v>11958.24</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>900.5924919462329</t>
+          <t>1001.01000486011</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>632.5830332273472</t>
+          <t>1553.306325886435</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>17859.0</t>
+          <t>31270.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>11.85</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>25.92</t>
+          <t>25.97</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>30558</t>
+          <t>30494</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>93.9</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>188.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.60</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8329,68 +8329,68 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>92.11</t>
+          <t>96.97</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>91.23</t>
+          <t>90.22</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>94.18</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>91.08</v>
+        <v>91.42</v>
       </c>
       <c r="AN19" t="n">
-        <v>88.45</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>87.06</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>18.54</t>
+          <t>14.91</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-59.53</t>
+          <t>-57.96</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,48 +8410,48 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>19319.76214285714</t>
+          <t>19308.55848787447</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>16873.0</t>
+          <t>17859.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>17330.8</v>
+        <v>17990.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>17510.1</t>
+          <t>17411.4</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>11244.72</v>
+        <v>11472.62</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-179</t>
+          <t>578</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>949.3214844405758</t>
+          <t>900.5924919462329</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>731.5646496705303</t>
+          <t>632.5830332273472</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>16873.0</t>
+          <t>17859.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8521,12 +8521,12 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>11.85</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>25.92</t>
+          <t>25.97</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>30558</t>
+          <t>30494</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>8.04</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8759,68 +8759,68 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>81.58</t>
+          <t>92.11</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>93.86</t>
+          <t>91.23</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>93.82</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>90.70999999999999</v>
+        <v>91.08</v>
       </c>
       <c r="AN20" t="n">
-        <v>88.33</v>
+        <v>88.45</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>86.93</t>
+          <t>87.06</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>22.80</t>
+          <t>18.54</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-61.41</t>
+          <t>-59.53</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,48 +8840,48 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>19319.76214285714</t>
+          <t>19308.55848787447</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>23221.0</t>
+          <t>16873.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>18190.8</v>
+        <v>17330.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>16836.8</t>
+          <t>17510.1</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>11205.54</v>
+        <v>11244.72</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>-179</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>988.9136362169477</t>
+          <t>949.3214844405758</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>952.4825071011255</t>
+          <t>731.5646496705303</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>23221.0</t>
+          <t>16873.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,12 +8941,12 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>11.85</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>25.92</t>
+          <t>25.97</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>30558</t>
+          <t>30494</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
+          <t>93.9</t>
+        </is>
+      </c>
+      <c r="CE20" t="inlineStr">
+        <is>
           <t>94.7</t>
         </is>
       </c>
-      <c r="CE20" t="inlineStr">
-        <is>
-          <t>94.7</t>
-        </is>
-      </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>187.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>21.90</t>
+          <t>8.04</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9108,7 +9108,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10.55</t>
+          <t>13.99</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9189,68 +9189,68 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>81.58</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.86</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>93.47999999999999</t>
+          <t>93.82</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>90.34999999999999</v>
+        <v>90.70999999999999</v>
       </c>
       <c r="AN21" t="n">
-        <v>88.23</v>
+        <v>88.33</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.93</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>22.80</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-63.61</t>
+          <t>-61.41</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,48 +9270,48 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>19319.76214285714</t>
+          <t>19308.55848787447</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>17643.0</t>
+          <t>23221.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>19485.8</v>
+        <v>18190.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>15984.8</t>
+          <t>16836.8</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>11103.86</v>
+        <v>11205.54</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>3501</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>995.53747787437</t>
+          <t>988.9136362169477</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>553.9193567483671</t>
+          <t>952.4825071011255</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>17643.0</t>
+          <t>23221.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>5.16</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>11.85</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>25.92</t>
+          <t>25.97</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>30558</t>
+          <t>30494</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>187.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9518,7 +9518,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>11.03</t>
+          <t>21.90</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9538,7 +9538,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -9578,7 +9578,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>7.55</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>8.63</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9634,53 +9634,53 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>92.82</t>
+          <t>93.47999999999999</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>89.98</v>
+        <v>90.34999999999999</v>
       </c>
       <c r="AN22" t="n">
-        <v>88.09</v>
+        <v>88.23</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>86.66</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>30.52</t>
+          <t>29.27</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-66.27</t>
+          <t>-63.61</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,48 +9700,48 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>19319.76214285714</t>
+          <t>19308.55848787447</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>14355.0</t>
+          <t>17643.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>17808</v>
+        <v>19485.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>16039.2</t>
+          <t>15984.8</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>10954</v>
+        <v>11103.86</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>1768</t>
+          <t>3501</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>1075.831681715461</t>
+          <t>995.53747787437</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>562.4034506462722</t>
+          <t>553.9193567483671</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>14355.0</t>
+          <t>17643.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>11.85</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>25.92</t>
+          <t>25.97</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>30558</t>
+          <t>30494</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-13.59</t>
+          <t>11.03</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9968,7 +9968,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>7.55</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>8.80</t>
+          <t>8.63</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10064,53 +10064,53 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>92.82</t>
+        </is>
+      </c>
+      <c r="AM23" t="n">
+        <v>89.98</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>88.09</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>86.66</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>30.52</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
           <t>1.65</t>
         </is>
       </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>92.16</t>
-        </is>
-      </c>
-      <c r="AM23" t="n">
-        <v>89.63</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>87.95</v>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>86.52</t>
-        </is>
-      </c>
-      <c r="AP23" t="inlineStr">
-        <is>
-          <t>31.22</t>
-        </is>
-      </c>
-      <c r="AQ23" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-68.84</t>
+          <t>-66.27</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,48 +10130,48 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>19319.76214285714</t>
+          <t>19308.55848787447</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>14562.0</t>
+          <t>14355.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>16832.6</v>
+        <v>17808</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>19479.0</t>
+          <t>16039.2</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>10822.66</v>
+        <v>10954</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-2646</t>
+          <t>1768</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>1169.182269182587</t>
+          <t>1075.831681715461</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>906.7234615487687</t>
+          <t>562.4034506462722</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>14562.0</t>
+          <t>14355.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="BF23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>11.85</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>25.92</t>
+          <t>25.97</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>30558</t>
+          <t>30494</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/期貨業.xlsx
+++ b/Result/checksun_type/期貨業.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>187.779</t>
+          <t>380.391</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,97 +918,97 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-12.82</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>49.95</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-02-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-02-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>49.95</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
         <is>
           <t>49.7</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>49.55</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>58.3</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>57.5</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0.71</t>
-        </is>
-      </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>-13.57</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>12.63</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -1019,70 +1019,70 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>380</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>95.83</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>90.61</t>
+          <t>98.61</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>49.56</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>49.63</v>
+        <v>49.64</v>
       </c>
       <c r="AN2" t="n">
-        <v>49.2</v>
+        <v>49.21</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>49.19</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>41.80</t>
+          <t>78.29</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
       <c r="AS2" t="inlineStr">
         <is>
           <t>1.55</t>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-97.56</t>
+          <t>-96.97</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,48 +1100,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>26578338.83238231</t>
+          <t>26581056.82692308</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>9355231.0</t>
+          <t>18990914.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>12002864.4</v>
+        <v>11532127.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>12720616.9</t>
+          <t>13227919.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>11280841.36</v>
+        <v>11457402.2</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-717752</t>
+          <t>-1695791</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>54352.68804154852</t>
+          <t>58393.91103422501</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-527126.2404232193</t>
+          <t>80620.63749394566</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>9355231.0</t>
+          <t>18990914.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>10.42</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>12472</t>
+          <t>12484</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>49.85</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>50.2</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
           <t>49.95</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>49.9</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1303,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>207.186</t>
+          <t>187.779</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,112 +1328,112 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-5.64</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>49.95</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>6.05</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-02-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-02-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>49.7</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>49.55</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>58.3</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>57.5</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>0.81</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>-13.57</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1449,68 +1449,68 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>380</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.83</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>90.61</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.56</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>49.61</v>
+        <v>49.63</v>
       </c>
       <c r="AN3" t="n">
-        <v>49.18</v>
+        <v>49.2</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>49.18</t>
+          <t>49.19</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-42.74</t>
+          <t>41.80</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-97.82</t>
+          <t>-97.56</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>26578338.83238231</t>
+          <t>26581056.82692308</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>10311071.0</t>
+          <t>9355231.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>13509669.6</v>
+        <v>12002864.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>12738791.1</t>
+          <t>12720616.9</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>11218520</v>
+        <v>11280841.36</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>770878</t>
+          <t>-717752</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>160076.1295805972</t>
+          <t>54352.68804154852</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-344115.5217183363</t>
+          <t>-527126.2404232193</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>10311071.0</t>
+          <t>9355231.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>10.42</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>12472</t>
+          <t>12484</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>220.404</t>
+          <t>207.186</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,112 +1758,112 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>49.95</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>6.05</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>49.95</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
           <t>49.7</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>49.55</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.4</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-1.78</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-02-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-02-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>49.55</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>58.3</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>57.5</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0.30</t>
-        </is>
-      </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-13.57</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1879,68 +1879,68 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>380</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>44.41</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
+          <t>49.33</t>
+        </is>
+      </c>
+      <c r="AM4" t="n">
+        <v>49.61</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>49.18</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
           <t>49.18</t>
         </is>
       </c>
-      <c r="AM4" t="n">
-        <v>49.58</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>49.16</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>49.17</t>
-        </is>
-      </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-179.21</t>
+          <t>-42.74</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-97.59</t>
+          <t>-97.82</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>26578338.83238231</t>
+          <t>26581056.82692308</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>10917653.0</t>
+          <t>10311071.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>12566466.6</v>
+        <v>13509669.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>12794356.8</t>
+          <t>12738791.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>11192472.92</v>
+        <v>11218520</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-227890</t>
+          <t>770878</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>251747.3389076761</t>
+          <t>160076.1295805972</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-172793.2263642792</t>
+          <t>-344115.5217183363</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>10917653.0</t>
+          <t>10311071.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>10.42</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>12472</t>
+          <t>12484</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>164.837</t>
+          <t>220.404</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-12.76</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2223,77 +2223,77 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>2025-11-03 00:00:00</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>2025-11-17 00:00:00</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-02-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-02-12 00:00:00</t>
-        </is>
-      </c>
       <c r="Q5" t="inlineStr">
         <is>
+          <t>49.95</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
           <t>49.7</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>49.55</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>58.3</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>57.5</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>-0.61</t>
-        </is>
-      </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>-13.57</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2309,32 +2309,32 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>380</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>44.41</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -2344,33 +2344,33 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.18</t>
         </is>
       </c>
       <c r="AM5" t="n">
         <v>49.58</v>
       </c>
       <c r="AN5" t="n">
-        <v>49.14</v>
+        <v>49.16</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>49.16</t>
+          <t>49.17</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-222.32</t>
+          <t>-179.21</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-96.50</t>
+          <t>-97.59</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>26578338.83238231</t>
+          <t>26581056.82692308</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>8085769.0</t>
+          <t>10917653.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>11596388.6</v>
+        <v>12566466.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>13292107.0</t>
+          <t>12794356.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>11264689.06</v>
+        <v>11192472.92</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-1695718</t>
+          <t>-227890</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>328936.5325934861</t>
+          <t>251747.3389076761</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>13133.16794023849</t>
+          <t>-172793.2263642792</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>8085769.0</t>
+          <t>10917653.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>10.42</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>12472</t>
+          <t>12484</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>437.14</t>
+          <t>164.837</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>-12.76</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2653,77 +2653,77 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>2025-11-03 00:00:00</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>2025-11-17 00:00:00</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-02-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-02-12 00:00:00</t>
-        </is>
-      </c>
       <c r="Q6" t="inlineStr">
         <is>
+          <t>49.95</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
           <t>49.7</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>49.55</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>58.3</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>57.5</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>-1.11</t>
-        </is>
-      </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-13.57</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14.52</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2739,32 +2739,32 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>380</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2774,23 +2774,23 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>49.6</v>
+        <v>49.58</v>
       </c>
       <c r="AN6" t="n">
         <v>49.14</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>49.16</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-178.57</t>
+          <t>-222.32</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-94.56</t>
+          <t>-96.50</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>26578338.83238231</t>
+          <t>26581056.82692308</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>21344598.0</t>
+          <t>8085769.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>14923710.6</v>
+        <v>11596388.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>13956611.9</t>
+          <t>13292107.0</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>11357891.38</v>
+        <v>11264689.06</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>967098</t>
+          <t>-1695718</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>386355.3261668038</t>
+          <t>328936.5325934861</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>581689.4038059711</t>
+          <t>13133.16794023849</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>21344598.0</t>
+          <t>8085769.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>10.42</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>12472</t>
+          <t>12484</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2991,17 +2991,17 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>346.337</t>
+          <t>437.14</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3083,77 +3083,77 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>2025-11-03 00:00:00</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2025-11-17 00:00:00</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-02-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-02-12 00:00:00</t>
-        </is>
-      </c>
       <c r="Q7" t="inlineStr">
         <is>
+          <t>49.95</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
           <t>49.7</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>49.55</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>58.3</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>57.5</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>-1.61</t>
-        </is>
-      </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>-13.57</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11.50</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,49 +3169,49 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>380</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>11.49</t>
+          <t>16.09</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>49.01000000000001</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>49.63</v>
+        <v>49.6</v>
       </c>
       <c r="AN7" t="n">
-        <v>49.15</v>
+        <v>49.14</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3220,17 +3220,17 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-132.60</t>
+          <t>-178.57</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-92.13</t>
+          <t>-94.56</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>26578338.83238231</t>
+          <t>26581056.82692308</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>16889257.0</t>
+          <t>21344598.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>13438369.4</v>
+        <v>14923710.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>13466583.0</t>
+          <t>13956611.9</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>11395162.18</v>
+        <v>11357891.38</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-28213</t>
+          <t>967098</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>350840.0393233188</t>
+          <t>386355.3261668038</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-47450.8450931944</t>
+          <t>581689.4038059711</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>16889257.0</t>
+          <t>21344598.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,12 +3351,12 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>10.42</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>12472</t>
+          <t>12484</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>113.787</t>
+          <t>346.337</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-8.11</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3513,77 +3513,77 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
           <t>2025-11-03 00:00:00</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>2025-11-17 00:00:00</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-02-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-02-12 00:00:00</t>
-        </is>
-      </c>
       <c r="Q8" t="inlineStr">
         <is>
+          <t>49.95</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
           <t>49.7</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>49.55</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>58.3</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>57.5</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>-0.71</t>
-        </is>
-      </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>-13.57</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>11.50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3599,12 +3599,12 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>380</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -3614,17 +3614,17 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -3634,11 +3634,11 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>49.26000000000001</t>
+          <t>49.01000000000001</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>49.68</v>
+        <v>49.63</v>
       </c>
       <c r="AN8" t="n">
         <v>49.15</v>
@@ -3650,17 +3650,17 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-87.62</t>
+          <t>-132.60</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-89.52</t>
+          <t>-92.13</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>26578338.83238231</t>
+          <t>26581056.82692308</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>5595056.0</t>
+          <t>16889257.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>11967912.6</v>
+        <v>13438369.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>13023841.6</t>
+          <t>13466583.0</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>11508277.46</v>
+        <v>11395162.18</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-1055929</t>
+          <t>-28213</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>423256.5637626849</t>
+          <t>350840.0393233188</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-467169.9919101018</t>
+          <t>-47450.8450931944</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>5595056.0</t>
+          <t>16889257.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>10.42</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>12472</t>
+          <t>12484</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>124.255</t>
+          <t>113.787</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-8.11</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3943,77 +3943,77 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>2025-11-03 00:00:00</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>2025-11-17 00:00:00</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-02-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-02-12 00:00:00</t>
-        </is>
-      </c>
       <c r="Q9" t="inlineStr">
         <is>
+          <t>49.95</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
           <t>49.7</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>49.55</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>58.3</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>57.5</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>-1.51</t>
-        </is>
-      </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>-13.57</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4029,32 +4029,32 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>380</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>31.03</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>11.49</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -4064,11 +4064,11 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>49.26000000000001</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>49.69</v>
+        <v>49.68</v>
       </c>
       <c r="AN9" t="n">
         <v>49.15</v>
@@ -4080,17 +4080,17 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-74.56</t>
+          <t>-87.62</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-87.23</t>
+          <t>-89.52</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>26578338.83238231</t>
+          <t>26581056.82692308</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>6067263.0</t>
+          <t>5595056.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>13022247</v>
+        <v>11967912.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>13893145.0</t>
+          <t>13023841.6</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>11517867.76</v>
+        <v>11508277.46</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-870898</t>
+          <t>-1055929</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>585152.301157737</t>
+          <t>423256.5637626849</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>160008.8337768205</t>
+          <t>-467169.9919101018</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>6067263.0</t>
+          <t>5595056.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>10.42</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>12472</t>
+          <t>12484</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>48.95</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>505.389</t>
+          <t>124.255</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4373,77 +4373,77 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>2025-11-03 00:00:00</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>2025-11-17 00:00:00</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-02-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-02-12 00:00:00</t>
-        </is>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
+          <t>49.95</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
           <t>49.7</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>49.55</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>58.3</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>57.5</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>-1.61</t>
-        </is>
-      </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>-13.57</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4459,32 +4459,32 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>380</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -4494,33 +4494,33 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>49.71</v>
+        <v>49.69</v>
       </c>
       <c r="AN10" t="n">
-        <v>49.16</v>
+        <v>49.15</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>49.16</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-45.07</t>
+          <t>-74.56</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-84.85</t>
+          <t>-87.23</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>26578338.83238231</t>
+          <t>26581056.82692308</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>24722379.0</t>
+          <t>6067263.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>14987825.4</v>
+        <v>13022247</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>14283209.4</t>
+          <t>13893145.0</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>11515168.36</v>
+        <v>11517867.76</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>704616</t>
+          <t>-870898</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>662451.1134088128</t>
+          <t>585152.301157737</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>999670.3764089644</t>
+          <t>160008.8337768205</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>24722379.0</t>
+          <t>6067263.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>10.42</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>12472</t>
+          <t>12484</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,12 +4706,12 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>48.95</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>280.155</t>
+          <t>505.389</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,112 +4768,112 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>48.75</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>4.93</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>49.95</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
           <t>49.55</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>-19.61</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-02-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-02-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>49.55</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>58.3</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>57.5</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>-0.30</t>
-        </is>
-      </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>-13.57</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>9.30</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>380</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,60 +4899,60 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>49.97000000000001</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>49.73</v>
+        <v>49.71</v>
       </c>
       <c r="AN11" t="n">
         <v>49.16</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>49.17</t>
+          <t>49.16</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-10.99</t>
+          <t>-45.07</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
           <t>0.23</t>
         </is>
       </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>0.26</t>
-        </is>
-      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>1.55</t>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-83.14</t>
+          <t>-84.85</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,48 +4970,48 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>26578338.83238231</t>
+          <t>26581056.82692308</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>13917892.0</t>
+          <t>24722379.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>12989513.2</v>
+        <v>14987825.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>16157581.3</t>
+          <t>14283209.4</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>11144720.98</v>
+        <v>11515168.36</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-3168068</t>
+          <t>704616</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>601138.5201360579</t>
+          <t>662451.1134088128</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>164721.9238688461</t>
+          <t>999670.3764089644</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>13917892.0</t>
+          <t>24722379.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>10.42</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>12472</t>
+          <t>12484</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5173,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5183,127 +5183,127 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>-0.9</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>280.155</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>49.55</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>190.635</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-19.61</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>49.95</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>49.55</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>-0.30</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>-13.79</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-02-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-02-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>49.55</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>58.3</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>57.5</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>0.60</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>0.91</t>
-        </is>
-      </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>-13.57</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>9.30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,32 +5319,32 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>380</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -5354,33 +5354,33 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>50.06</t>
+          <t>49.97000000000001</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>49.71</v>
+        <v>49.73</v>
       </c>
       <c r="AN12" t="n">
         <v>49.16</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>49.16</t>
+          <t>49.17</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>-10.99</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-82.68</t>
+          <t>-83.14</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>26578338.83238231</t>
+          <t>26581056.82692308</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>9536973.0</t>
+          <t>13917892.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>13494796.6</v>
+        <v>12989513.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>15653412.6</t>
+          <t>16157581.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>11004239.68</v>
+        <v>11144720.98</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-2158616</t>
+          <t>-3168068</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>680486.9921846419</t>
+          <t>601138.5201360579</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>123679.1015305072</t>
+          <t>164721.9238688461</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>9536973.0</t>
+          <t>13917892.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>10.42</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>12472</t>
+          <t>12484</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5603,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-31.56</t>
+          <t>-29.56</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-01 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,37 +5744,37 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>92.59</t>
+          <t>74.95</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -5784,33 +5784,33 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>95.14000000000001</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>93.15000000000001</v>
+        <v>93.38</v>
       </c>
       <c r="AN13" t="n">
-        <v>89.43000000000001</v>
+        <v>89.58</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>88.12</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-54.27</t>
+          <t>-54.57</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,48 +5830,48 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>19308.55848787447</t>
+          <t>19304.84615384615</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>7644.0</t>
+          <t>11135.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>11119.4</v>
+        <v>10985.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>16246.3</t>
+          <t>15595.5</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>12428.1</v>
+        <v>12513.22</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-5126</t>
+          <t>-4609</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>218.2253813802438</t>
+          <t>3.952413337048682</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-1096.578521787593</t>
+          <t>-1174.548910900525</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>7644.0</t>
+          <t>11135.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>11.85</t>
+          <t>11.78</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>25.97</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>30494</t>
+          <t>30302</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>95.4</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,102 +6068,102 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
+          <t>-0.63</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>-31.56</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2025-10-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>87.4</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>94.7</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>87.4</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>87.3</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>87.6</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>9.04</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>4.51</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
           <t>-0.21</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>-6.34</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2025-10-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2025-11-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2025-08-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>87.4</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>87.4</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>87.3</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>87.6</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>9.27</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>-0.23</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>5.87</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>0.21</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,37 +6174,37 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>98.15</t>
+          <t>92.59</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -6214,33 +6214,33 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>94.86</t>
+          <t>95.14000000000001</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>92.88</v>
+        <v>93.15000000000001</v>
       </c>
       <c r="AN14" t="n">
-        <v>89.27</v>
+        <v>89.43000000000001</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>87.97</t>
+          <t>88.12</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-54.52</t>
+          <t>-54.27</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,48 +6260,48 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>19308.55848787447</t>
+          <t>19304.84615384615</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>9934.0</t>
+          <t>7644.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>15844.6</v>
+        <v>11119.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>16917.4</t>
+          <t>16246.3</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>12366.42</v>
+        <v>12428.1</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-1072</t>
+          <t>-5126</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>457.2806365016687</t>
+          <t>218.2253813802438</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-571.9930187052742</t>
+          <t>-1096.578521787593</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>9934.0</t>
+          <t>7644.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>11.85</t>
+          <t>11.78</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>25.97</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>30494</t>
+          <t>30302</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-01 00:00:00</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.27</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11.05</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,37 +6604,37 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>97.22</t>
+          <t>98.15</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -6644,23 +6644,23 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>94.64000000000001</t>
+          <t>94.86</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>92.58</v>
+        <v>92.88</v>
       </c>
       <c r="AN15" t="n">
-        <v>89.11</v>
+        <v>89.27</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>87.81</t>
+          <t>87.97</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-55.07</t>
+          <t>-54.52</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,48 +6690,48 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>19308.55848787447</t>
+          <t>19304.84615384615</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>18772.0</t>
+          <t>9934.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>17429.6</v>
+        <v>15844.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>17380.2</t>
+          <t>16917.4</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>12316.72</v>
+        <v>12366.42</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>-1072</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>644.4213010847493</t>
+          <t>457.2806365016687</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-47.51397791963245</t>
+          <t>-571.9930187052742</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>18772.0</t>
+          <t>9934.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>11.85</t>
+          <t>11.78</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>25.97</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>30494</t>
+          <t>30302</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>95.1</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-01 00:00:00</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -6978,7 +6978,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>8.58</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,12 +7034,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7049,58 +7049,58 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>88.89</t>
+          <t>97.22</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>94.36</t>
+          <t>94.64000000000001</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>92.23999999999999</v>
+        <v>92.58</v>
       </c>
       <c r="AN16" t="n">
-        <v>88.95</v>
+        <v>89.11</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>87.64</t>
+          <t>87.81</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-55.73</t>
+          <t>-55.07</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,48 +7120,48 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>19308.55848787447</t>
+          <t>19304.84615384615</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>7444.0</t>
+          <t>18772.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>17049.8</v>
+        <v>17429.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>17620.3</t>
+          <t>17380.2</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>12079.36</v>
+        <v>12316.72</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-570</t>
+          <t>49</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>770.2277154491823</t>
+          <t>644.4213010847493</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-243.4898490144406</t>
+          <t>-47.51397791963245</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>7444.0</t>
+          <t>18772.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>11.85</t>
+          <t>11.78</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>25.97</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>30494</t>
+          <t>30302</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>95.1</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7338,7 +7338,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-01 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>8.58</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>6.99</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>88.89</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>94.14000000000001</t>
+          <t>94.36</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>91.92</v>
+        <v>92.23999999999999</v>
       </c>
       <c r="AN17" t="n">
-        <v>88.81999999999999</v>
+        <v>88.95</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>87.49</t>
+          <t>87.64</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-56.30</t>
+          <t>-55.73</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,48 +7550,48 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>19308.55848787447</t>
+          <t>19304.84615384615</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>11803.0</t>
+          <t>7444.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>20205.2</v>
+        <v>17049.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>19845.5</t>
+          <t>17620.3</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>12067.32</v>
+        <v>12079.36</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>-570</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>954.5399998971137</t>
+          <t>770.2277154491823</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>698.9549726006335</t>
+          <t>-243.4898490144406</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>11803.0</t>
+          <t>7444.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>11.85</t>
+          <t>11.78</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>25.97</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>30494</t>
+          <t>30302</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>334.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-01 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18.84</t>
+          <t>6.99</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,209 +7894,209 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>88.02</t>
+          <t>87.88</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>94.16</t>
+          <t>94.14000000000001</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>91.66</v>
+        <v>91.92</v>
       </c>
       <c r="AN18" t="n">
-        <v>88.69</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>87.34</t>
+          <t>87.49</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>-56.30</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>2025/10/15</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>19304.84615384615</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>11803.0</t>
+        </is>
+      </c>
+      <c r="AX18" t="n">
+        <v>20205.2</v>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>19845.5</t>
+        </is>
+      </c>
+      <c r="AZ18" t="n">
+        <v>12067.32</v>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>954.5399998971137</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>698.9549726006335</t>
+        </is>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>11803.0</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>2025/10/23</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>5.83</t>
+        </is>
+      </c>
+      <c r="BI18" t="inlineStr">
+        <is>
+          <t>元大期貨</t>
+        </is>
+      </c>
+      <c r="BJ18" t="inlineStr">
+        <is>
+          <t>元大期貨</t>
+        </is>
+      </c>
+      <c r="BK18" t="inlineStr">
+        <is>
+          <t>金融業</t>
+        </is>
+      </c>
+      <c r="BL18" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM18" t="inlineStr">
+        <is>
+          <t>0.27</t>
+        </is>
+      </c>
+      <c r="BN18" t="inlineStr">
+        <is>
+          <t>0.586310700095985</t>
+        </is>
+      </c>
+      <c r="BO18" t="inlineStr">
+        <is>
+          <t>8.007619922843494</t>
+        </is>
+      </c>
+      <c r="BP18" t="inlineStr">
+        <is>
+          <t>-12.34648294771329</t>
+        </is>
+      </c>
+      <c r="BQ18" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR18" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS18" t="inlineStr">
+        <is>
           <t>1.61</t>
         </is>
       </c>
-      <c r="AS18" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="AT18" t="inlineStr">
-        <is>
-          <t>-56.98</t>
-        </is>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>2025/10/15</t>
-        </is>
-      </c>
-      <c r="AV18" t="inlineStr">
-        <is>
-          <t>19308.55848787447</t>
-        </is>
-      </c>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>31270.0</t>
-        </is>
-      </c>
-      <c r="AX18" t="n">
-        <v>21373.2</v>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>19590.6</t>
-        </is>
-      </c>
-      <c r="AZ18" t="n">
-        <v>11958.24</v>
-      </c>
-      <c r="BA18" t="inlineStr">
-        <is>
-          <t>1782</t>
-        </is>
-      </c>
-      <c r="BB18" t="inlineStr">
-        <is>
-          <t>1001.01000486011</t>
-        </is>
-      </c>
-      <c r="BC18" t="inlineStr">
-        <is>
-          <t>1553.306325886435</t>
-        </is>
-      </c>
-      <c r="BD18" t="inlineStr">
-        <is>
-          <t>31270.0</t>
-        </is>
-      </c>
-      <c r="BE18" t="inlineStr">
-        <is>
-          <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="BF18" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr">
-        <is>
-          <t>2025/10/23</t>
-        </is>
-      </c>
-      <c r="BH18" t="inlineStr">
-        <is>
-          <t>5.27</t>
-        </is>
-      </c>
-      <c r="BI18" t="inlineStr">
-        <is>
-          <t>元大期貨</t>
-        </is>
-      </c>
-      <c r="BJ18" t="inlineStr">
-        <is>
-          <t>元大期貨</t>
-        </is>
-      </c>
-      <c r="BK18" t="inlineStr">
-        <is>
-          <t>金融業</t>
-        </is>
-      </c>
-      <c r="BL18" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM18" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="BN18" t="inlineStr">
-        <is>
-          <t>0.586310700095985</t>
-        </is>
-      </c>
-      <c r="BO18" t="inlineStr">
-        <is>
-          <t>8.007619922843494</t>
-        </is>
-      </c>
-      <c r="BP18" t="inlineStr">
-        <is>
-          <t>-12.34648294771329</t>
-        </is>
-      </c>
-      <c r="BQ18" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
-        </is>
-      </c>
-      <c r="BR18" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS18" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>11.85</t>
+          <t>11.78</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>25.97</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>30494</t>
+          <t>30302</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>188.0</t>
+          <t>334.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>93.9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-01 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10.60</t>
+          <t>18.84</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>96.97</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>90.22</t>
+          <t>88.02</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>94.18</t>
+          <t>94.16</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>91.42</v>
+        <v>91.66</v>
       </c>
       <c r="AN19" t="n">
-        <v>88.56999999999999</v>
+        <v>88.69</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.34</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>14.91</t>
+          <t>9.14</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-57.96</t>
+          <t>-56.98</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,48 +8410,48 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>19308.55848787447</t>
+          <t>19304.84615384615</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>17859.0</t>
+          <t>31270.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>17990.2</v>
+        <v>21373.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>17411.4</t>
+          <t>19590.6</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>11472.62</v>
+        <v>11958.24</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>900.5924919462329</t>
+          <t>1001.01000486011</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>632.5830332273472</t>
+          <t>1553.306325886435</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>17859.0</t>
+          <t>31270.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>11.85</t>
+          <t>11.78</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>25.97</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>30494</t>
+          <t>30302</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>93.9</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>188.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-01 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -8698,7 +8698,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -8718,12 +8718,12 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.60</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>92.11</t>
+          <t>96.97</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>91.23</t>
+          <t>90.22</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>94.18</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>91.08</v>
+        <v>91.42</v>
       </c>
       <c r="AN20" t="n">
-        <v>88.45</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>87.06</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>18.54</t>
+          <t>14.91</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-59.53</t>
+          <t>-57.96</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,48 +8840,48 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>19308.55848787447</t>
+          <t>19304.84615384615</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>16873.0</t>
+          <t>17859.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>17330.8</v>
+        <v>17990.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>17510.1</t>
+          <t>17411.4</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>11244.72</v>
+        <v>11472.62</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-179</t>
+          <t>578</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>949.3214844405758</t>
+          <t>900.5924919462329</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>731.5646496705303</t>
+          <t>632.5830332273472</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>16873.0</t>
+          <t>17859.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>11.85</t>
+          <t>11.78</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>25.97</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>30494</t>
+          <t>30302</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>8.04</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9108,7 +9108,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-01 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -9128,7 +9128,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -9148,12 +9148,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>81.58</t>
+          <t>92.11</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>93.86</t>
+          <t>91.23</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>93.82</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>90.70999999999999</v>
+        <v>91.08</v>
       </c>
       <c r="AN21" t="n">
-        <v>88.33</v>
+        <v>88.45</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>86.93</t>
+          <t>87.06</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>22.80</t>
+          <t>18.54</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-61.41</t>
+          <t>-59.53</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,48 +9270,48 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>19308.55848787447</t>
+          <t>19304.84615384615</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>23221.0</t>
+          <t>16873.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>18190.8</v>
+        <v>17330.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>16836.8</t>
+          <t>17510.1</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>11205.54</v>
+        <v>11244.72</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>-179</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>988.9136362169477</t>
+          <t>949.3214844405758</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>952.4825071011255</t>
+          <t>731.5646496705303</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>23221.0</t>
+          <t>16873.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>11.85</t>
+          <t>11.78</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>25.97</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>30494</t>
+          <t>30302</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
+          <t>93.9</t>
+        </is>
+      </c>
+      <c r="CE21" t="inlineStr">
+        <is>
           <t>94.7</t>
         </is>
       </c>
-      <c r="CE21" t="inlineStr">
-        <is>
-          <t>94.7</t>
-        </is>
-      </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>187.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9518,7 +9518,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>21.90</t>
+          <t>8.04</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9538,7 +9538,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-01 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -9558,7 +9558,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10.55</t>
+          <t>13.99</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,73 +9614,73 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>81.58</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.86</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>93.47999999999999</t>
+          <t>93.82</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>90.34999999999999</v>
+        <v>90.70999999999999</v>
       </c>
       <c r="AN22" t="n">
-        <v>88.23</v>
+        <v>88.33</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.93</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>22.80</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-63.61</t>
+          <t>-61.41</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,48 +9700,48 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>19308.55848787447</t>
+          <t>19304.84615384615</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>17643.0</t>
+          <t>23221.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>19485.8</v>
+        <v>18190.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>15984.8</t>
+          <t>16836.8</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>11103.86</v>
+        <v>11205.54</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>3501</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>995.53747787437</t>
+          <t>988.9136362169477</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>553.9193567483671</t>
+          <t>952.4825071011255</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>17643.0</t>
+          <t>23221.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>5.16</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>11.85</t>
+          <t>11.78</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>25.97</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>30494</t>
+          <t>30302</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>187.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>11.03</t>
+          <t>21.90</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9968,7 +9968,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-01 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -9988,7 +9988,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -10008,12 +10008,12 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>7.55</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>8.63</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10064,53 +10064,53 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>92.82</t>
+          <t>93.47999999999999</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>89.98</v>
+        <v>90.34999999999999</v>
       </c>
       <c r="AN23" t="n">
-        <v>88.09</v>
+        <v>88.23</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>86.66</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>30.52</t>
+          <t>29.27</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-66.27</t>
+          <t>-63.61</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,48 +10130,48 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>19308.55848787447</t>
+          <t>19304.84615384615</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>14355.0</t>
+          <t>17643.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>17808</v>
+        <v>19485.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>16039.2</t>
+          <t>15984.8</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>10954</v>
+        <v>11103.86</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>1768</t>
+          <t>3501</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>1075.831681715461</t>
+          <t>995.53747787437</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>562.4034506462722</t>
+          <t>553.9193567483671</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>14355.0</t>
+          <t>17643.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="BF23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>11.85</t>
+          <t>11.78</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>25.97</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>30494</t>
+          <t>30302</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>94.8</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/期貨業.xlsx
+++ b/Result/checksun_type/期貨業.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>380.391</t>
+          <t>79.08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,74 +898,74 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>49.85</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-4.00</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-12-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>49.95</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-12.82</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-12-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>49.95</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>49.95</t>
-        </is>
-      </c>
       <c r="T2" t="inlineStr">
         <is>
           <t>49.7</t>
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12.63</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>98.61</t>
+          <t>95.83</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>49.87</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>49.64</v>
+        <v>49.62</v>
       </c>
       <c r="AN2" t="n">
-        <v>49.21</v>
+        <v>49.24</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.21</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>78.29</t>
+          <t>71.91</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-96.97</t>
+          <t>-96.31</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,48 +1100,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>26581056.82692308</t>
+          <t>26551660.67069701</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>18990914.0</t>
+          <t>3943706.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>11532127.6</v>
+        <v>10703715</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>13227919.1</t>
+          <t>11150051.8</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>11457402.2</v>
+        <v>11217869</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-1695791</t>
+          <t>-446336</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>58393.91103422501</t>
+          <t>-46668.63895586941</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>80620.63749394566</t>
+          <t>-624512.6639013886</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>18990914.0</t>
+          <t>3943706.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>10.41</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>17.08</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>12484</t>
+          <t>12459</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>187.779</t>
+          <t>380.391</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-12.82</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1423,96 +1423,96 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>12.63</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>95.83</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>90.61</t>
+          <t>98.61</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>49.56</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>49.63</v>
+        <v>49.64</v>
       </c>
       <c r="AN3" t="n">
-        <v>49.2</v>
+        <v>49.21</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>49.19</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>41.80</t>
+          <t>78.29</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
       <c r="AS3" t="inlineStr">
         <is>
           <t>1.55</t>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-97.56</t>
+          <t>-96.97</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,48 +1530,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>26581056.82692308</t>
+          <t>26551660.67069701</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>9355231.0</t>
+          <t>18990914.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>12002864.4</v>
+        <v>11532127.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>12720616.9</t>
+          <t>13227919.1</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>11280841.36</v>
+        <v>11457402.2</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-717752</t>
+          <t>-1695791</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>54352.68804154852</t>
+          <t>58393.91103422501</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-527126.2404232193</t>
+          <t>80620.63749394566</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>9355231.0</t>
+          <t>18990914.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,12 +1631,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>10.41</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>17.08</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>12484</t>
+          <t>12459</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>49.85</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>50.2</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
           <t>49.95</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>49.9</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>207.186</t>
+          <t>187.779</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,64 +1758,64 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-0.1</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-5.64</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-12-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>49.95</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>6.05</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-12-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>49.95</t>
-        </is>
-      </c>
       <c r="R4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.83</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>90.61</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.56</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>49.61</v>
+        <v>49.63</v>
       </c>
       <c r="AN4" t="n">
-        <v>49.18</v>
+        <v>49.2</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>49.18</t>
+          <t>49.19</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-42.74</t>
+          <t>41.80</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-97.82</t>
+          <t>-97.56</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>26581056.82692308</t>
+          <t>26551660.67069701</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>10311071.0</t>
+          <t>9355231.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>13509669.6</v>
+        <v>12002864.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>12738791.1</t>
+          <t>12720616.9</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>11218520</v>
+        <v>11280841.36</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>770878</t>
+          <t>-717752</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>160076.1295805972</t>
+          <t>54352.68804154852</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-344115.5217183363</t>
+          <t>-527126.2404232193</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>10311071.0</t>
+          <t>9355231.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>10.41</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>17.08</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>12484</t>
+          <t>12459</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>220.404</t>
+          <t>207.186</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,79 +2188,79 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>49.95</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-0.2</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>6.05</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-12-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>49.95</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
           <t>49.7</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-1.78</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-12-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>49.95</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
       <c r="U5" t="inlineStr">
         <is>
           <t>49.55</t>
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>44.41</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
+          <t>49.33</t>
+        </is>
+      </c>
+      <c r="AM5" t="n">
+        <v>49.61</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>49.18</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
           <t>49.18</t>
         </is>
       </c>
-      <c r="AM5" t="n">
-        <v>49.58</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>49.16</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>49.17</t>
-        </is>
-      </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-179.21</t>
+          <t>-42.74</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-97.59</t>
+          <t>-97.82</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>26581056.82692308</t>
+          <t>26551660.67069701</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>10917653.0</t>
+          <t>10311071.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>12566466.6</v>
+        <v>13509669.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>12794356.8</t>
+          <t>12738791.1</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>11192472.92</v>
+        <v>11218520</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-227890</t>
+          <t>770878</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>251747.3389076761</t>
+          <t>160076.1295805972</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-172793.2263642792</t>
+          <t>-344115.5217183363</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>10917653.0</t>
+          <t>10311071.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>10.41</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>17.08</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>12484</t>
+          <t>12459</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>164.837</t>
+          <t>220.404</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-12.76</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,37 +2734,37 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>44.41</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2774,33 +2774,33 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.18</t>
         </is>
       </c>
       <c r="AM6" t="n">
         <v>49.58</v>
       </c>
       <c r="AN6" t="n">
-        <v>49.14</v>
+        <v>49.16</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>49.16</t>
+          <t>49.17</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-222.32</t>
+          <t>-179.21</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-96.50</t>
+          <t>-97.59</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>26581056.82692308</t>
+          <t>26551660.67069701</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>8085769.0</t>
+          <t>10917653.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>11596388.6</v>
+        <v>12566466.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>13292107.0</t>
+          <t>12794356.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>11264689.06</v>
+        <v>11192472.92</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-1695718</t>
+          <t>-227890</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>328936.5325934861</t>
+          <t>251747.3389076761</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>13133.16794023849</t>
+          <t>-172793.2263642792</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>8085769.0</t>
+          <t>10917653.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>10.41</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>17.08</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>12484</t>
+          <t>12459</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>437.14</t>
+          <t>164.837</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>-12.76</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14.52</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,37 +3164,37 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -3204,23 +3204,23 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>49.6</v>
+        <v>49.58</v>
       </c>
       <c r="AN7" t="n">
         <v>49.14</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>49.16</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-178.57</t>
+          <t>-222.32</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-94.56</t>
+          <t>-96.50</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>26581056.82692308</t>
+          <t>26551660.67069701</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>21344598.0</t>
+          <t>8085769.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>14923710.6</v>
+        <v>11596388.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>13956611.9</t>
+          <t>13292107.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>11357891.38</v>
+        <v>11264689.06</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>967098</t>
+          <t>-1695718</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>386355.3261668038</t>
+          <t>328936.5325934861</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>581689.4038059711</t>
+          <t>13133.16794023849</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>21344598.0</t>
+          <t>8085769.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>10.41</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>17.08</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>12484</t>
+          <t>12459</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3421,17 +3421,17 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>346.337</t>
+          <t>437.14</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11.50</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,54 +3594,54 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>11.49</t>
+          <t>16.09</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>49.01000000000001</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>49.63</v>
+        <v>49.6</v>
       </c>
       <c r="AN8" t="n">
-        <v>49.15</v>
+        <v>49.14</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3650,17 +3650,17 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-132.60</t>
+          <t>-178.57</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-92.13</t>
+          <t>-94.56</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>26581056.82692308</t>
+          <t>26551660.67069701</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>16889257.0</t>
+          <t>21344598.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>13438369.4</v>
+        <v>14923710.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>13466583.0</t>
+          <t>13956611.9</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>11395162.18</v>
+        <v>11357891.38</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-28213</t>
+          <t>967098</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>350840.0393233188</t>
+          <t>386355.3261668038</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-47450.8450931944</t>
+          <t>581689.4038059711</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>16889257.0</t>
+          <t>21344598.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>10.41</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>17.08</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>12484</t>
+          <t>12459</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>113.787</t>
+          <t>346.337</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-8.11</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>11.50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,17 +4024,17 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4044,17 +4044,17 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -4064,11 +4064,11 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>49.26000000000001</t>
+          <t>49.01000000000001</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>49.68</v>
+        <v>49.63</v>
       </c>
       <c r="AN9" t="n">
         <v>49.15</v>
@@ -4080,17 +4080,17 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-87.62</t>
+          <t>-132.60</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-89.52</t>
+          <t>-92.13</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>26581056.82692308</t>
+          <t>26551660.67069701</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>5595056.0</t>
+          <t>16889257.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>11967912.6</v>
+        <v>13438369.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>13023841.6</t>
+          <t>13466583.0</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>11508277.46</v>
+        <v>11395162.18</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-1055929</t>
+          <t>-28213</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>423256.5637626849</t>
+          <t>350840.0393233188</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-467169.9919101018</t>
+          <t>-47450.8450931944</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>5595056.0</t>
+          <t>16889257.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>10.41</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>17.08</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>12484</t>
+          <t>12459</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>124.255</t>
+          <t>113.787</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-8.11</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,37 +4454,37 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>31.03</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>11.49</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -4494,11 +4494,11 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>49.26000000000001</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>49.69</v>
+        <v>49.68</v>
       </c>
       <c r="AN10" t="n">
         <v>49.15</v>
@@ -4510,17 +4510,17 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-74.56</t>
+          <t>-87.62</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-87.23</t>
+          <t>-89.52</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>26581056.82692308</t>
+          <t>26551660.67069701</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>6067263.0</t>
+          <t>5595056.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>13022247</v>
+        <v>11967912.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>13893145.0</t>
+          <t>13023841.6</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>11517867.76</v>
+        <v>11508277.46</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-870898</t>
+          <t>-1055929</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>585152.301157737</t>
+          <t>423256.5637626849</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>160008.8337768205</t>
+          <t>-467169.9919101018</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>6067263.0</t>
+          <t>5595056.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>10.41</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>17.08</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>12484</t>
+          <t>12459</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>48.95</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>505.389</t>
+          <t>124.255</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,37 +4884,37 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -4924,33 +4924,33 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>49.71</v>
+        <v>49.69</v>
       </c>
       <c r="AN11" t="n">
-        <v>49.16</v>
+        <v>49.15</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>49.16</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-45.07</t>
+          <t>-74.56</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-84.85</t>
+          <t>-87.23</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>26581056.82692308</t>
+          <t>26551660.67069701</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>24722379.0</t>
+          <t>6067263.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>14987825.4</v>
+        <v>13022247</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>14283209.4</t>
+          <t>13893145.0</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>11515168.36</v>
+        <v>11517867.76</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>704616</t>
+          <t>-870898</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>662451.1134088128</t>
+          <t>585152.301157737</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>999670.3764089644</t>
+          <t>160008.8337768205</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>24722379.0</t>
+          <t>6067263.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>10.41</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>17.08</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>12484</t>
+          <t>12459</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>48.95</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>280.155</t>
+          <t>505.389</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,87 +5198,87 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>48.75</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>4.93</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-12-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>49.95</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
           <t>49.55</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>-19.61</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-12-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>49.95</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>49.55</t>
-        </is>
-      </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>9.30</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,60 +5329,60 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>49.97000000000001</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>49.73</v>
+        <v>49.71</v>
       </c>
       <c r="AN12" t="n">
         <v>49.16</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>49.17</t>
+          <t>49.16</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-10.99</t>
+          <t>-45.07</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
           <t>0.23</t>
         </is>
       </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>0.26</t>
-        </is>
-      </c>
       <c r="AS12" t="inlineStr">
         <is>
           <t>1.55</t>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-83.14</t>
+          <t>-84.85</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,48 +5400,48 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>26581056.82692308</t>
+          <t>26551660.67069701</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>13917892.0</t>
+          <t>24722379.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>12989513.2</v>
+        <v>14987825.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>16157581.3</t>
+          <t>14283209.4</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>11144720.98</v>
+        <v>11515168.36</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-3168068</t>
+          <t>704616</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>601138.5201360579</t>
+          <t>662451.1134088128</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>164721.9238688461</t>
+          <t>999670.3764089644</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>13917892.0</t>
+          <t>24722379.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>10.41</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>17.08</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>12484</t>
+          <t>12459</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>118.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,72 +5628,72 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>-20.46</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2025-10-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>87.4</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
           <t>94.7</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>-29.56</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2025-10-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2025-08-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>87.4</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>94.7</t>
-        </is>
-      </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5749,68 +5749,68 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>94</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>74.95</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>95.02000000000001</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>93.38</v>
+        <v>93.56</v>
       </c>
       <c r="AN13" t="n">
-        <v>89.58</v>
+        <v>89.73</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-9.34</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-54.57</t>
+          <t>-55.61</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,48 +5830,48 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>19304.84615384615</t>
+          <t>19296.16856330014</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>11135.0</t>
+          <t>8803.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>10985.8</v>
+        <v>11257.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>15595.5</t>
+          <t>14153.7</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>12513.22</v>
+        <v>12542.78</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-4609</t>
+          <t>-2896</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>3.952413337048682</t>
+          <t>-208.1424903312762</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-1174.548910900525</t>
+          <t>-1374.664460507063</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>11135.0</t>
+          <t>8803.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>11.78</t>
+          <t>11.69</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>25.98</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>30302</t>
+          <t>30078</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>93.9</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>95.4</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6033,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-31.56</t>
+          <t>-29.56</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6138,12 +6138,12 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6179,32 +6179,32 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>94</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>92.59</t>
+          <t>74.95</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -6214,33 +6214,33 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>95.14000000000001</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>93.15000000000001</v>
+        <v>93.38</v>
       </c>
       <c r="AN14" t="n">
-        <v>89.43000000000001</v>
+        <v>89.58</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>88.12</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-54.27</t>
+          <t>-54.57</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>19304.84615384615</t>
+          <t>19296.16856330014</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>7644.0</t>
+          <t>11135.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>11119.4</v>
+        <v>10985.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>16246.3</t>
+          <t>15595.5</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>12428.1</v>
+        <v>12513.22</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-5126</t>
+          <t>-4609</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>218.2253813802438</t>
+          <t>3.952413337048682</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-1096.578521787593</t>
+          <t>-1174.548910900525</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>7644.0</t>
+          <t>11135.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>11.78</t>
+          <t>11.69</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>25.98</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>30302</t>
+          <t>30078</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>95.4</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-31.56</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>9.27</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6609,32 +6609,32 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>94</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>98.15</t>
+          <t>92.59</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -6644,33 +6644,33 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>94.86</t>
+          <t>95.14000000000001</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>92.88</v>
+        <v>93.15000000000001</v>
       </c>
       <c r="AN15" t="n">
-        <v>89.27</v>
+        <v>89.43000000000001</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>87.97</t>
+          <t>88.12</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-54.52</t>
+          <t>-54.27</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>19304.84615384615</t>
+          <t>19296.16856330014</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>9934.0</t>
+          <t>7644.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>15844.6</v>
+        <v>11119.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>16917.4</t>
+          <t>16246.3</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>12366.42</v>
+        <v>12428.1</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-1072</t>
+          <t>-5126</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>457.2806365016687</t>
+          <t>218.2253813802438</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-571.9930187052742</t>
+          <t>-1096.578521787593</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>9934.0</t>
+          <t>7644.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>11.78</t>
+          <t>11.69</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>25.98</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>30302</t>
+          <t>30078</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.27</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11.05</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7039,32 +7039,32 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>94</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>97.22</t>
+          <t>98.15</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -7074,23 +7074,23 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>94.64000000000001</t>
+          <t>94.86</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>92.58</v>
+        <v>92.88</v>
       </c>
       <c r="AN16" t="n">
-        <v>89.11</v>
+        <v>89.27</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>87.81</t>
+          <t>87.97</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-55.07</t>
+          <t>-54.52</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>19304.84615384615</t>
+          <t>19296.16856330014</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>18772.0</t>
+          <t>9934.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>17429.6</v>
+        <v>15844.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>17380.2</t>
+          <t>16917.4</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>12316.72</v>
+        <v>12366.42</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>-1072</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>644.4213010847493</t>
+          <t>457.2806365016687</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-47.51397791963245</t>
+          <t>-571.9930187052742</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>18772.0</t>
+          <t>9934.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>11.78</t>
+          <t>11.69</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>25.98</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>30302</t>
+          <t>30078</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>95.1</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,102 +7358,102 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
+          <t>-1.7</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2025-10-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>87.4</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>94.7</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>87.4</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>87.3</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>87.6</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>9.38</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11.05</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
           <t>-0.21</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>-3.24</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2025-10-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>2025-08-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>87.4</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>94.7</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>87.4</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>87.3</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>87.6</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>8.58</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>0.21</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>-0.23</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>4.46</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>1.39</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>94</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7479,58 +7479,58 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>88.89</t>
+          <t>97.22</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>94.36</t>
+          <t>94.64000000000001</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>92.23999999999999</v>
+        <v>92.58</v>
       </c>
       <c r="AN17" t="n">
-        <v>88.95</v>
+        <v>89.11</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>87.64</t>
+          <t>87.81</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-55.73</t>
+          <t>-55.07</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>19304.84615384615</t>
+          <t>19296.16856330014</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>7444.0</t>
+          <t>18772.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>17049.8</v>
+        <v>17429.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>17620.3</t>
+          <t>17380.2</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>12079.36</v>
+        <v>12316.72</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-570</t>
+          <t>49</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>770.2277154491823</t>
+          <t>644.4213010847493</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-243.4898490144406</t>
+          <t>-47.51397791963245</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>7444.0</t>
+          <t>18772.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7661,12 +7661,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>11.78</t>
+          <t>11.69</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>25.98</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>30302</t>
+          <t>30078</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>95.1</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7768,7 +7768,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>8.58</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>6.99</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7899,68 +7899,68 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>94</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>88.89</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>94.14000000000001</t>
+          <t>94.36</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>91.92</v>
+        <v>92.23999999999999</v>
       </c>
       <c r="AN18" t="n">
-        <v>88.81999999999999</v>
+        <v>88.95</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>87.49</t>
+          <t>87.64</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-56.30</t>
+          <t>-55.73</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>19304.84615384615</t>
+          <t>19296.16856330014</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>11803.0</t>
+          <t>7444.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>20205.2</v>
+        <v>17049.8</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>19845.5</t>
+          <t>17620.3</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>12067.32</v>
+        <v>12079.36</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>-570</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>954.5399998971137</t>
+          <t>770.2277154491823</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>698.9549726006335</t>
+          <t>-243.4898490144406</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>11803.0</t>
+          <t>7444.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>11.78</t>
+          <t>11.69</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>25.98</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>30302</t>
+          <t>30078</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>334.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18.84</t>
+          <t>6.99</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8329,204 +8329,204 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>94</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>88.02</t>
+          <t>87.88</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>94.16</t>
+          <t>94.14000000000001</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>91.66</v>
+        <v>91.92</v>
       </c>
       <c r="AN19" t="n">
-        <v>88.69</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>87.34</t>
+          <t>87.49</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>-56.30</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>2025/10/15</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>19296.16856330014</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>11803.0</t>
+        </is>
+      </c>
+      <c r="AX19" t="n">
+        <v>20205.2</v>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>19845.5</t>
+        </is>
+      </c>
+      <c r="AZ19" t="n">
+        <v>12067.32</v>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>954.5399998971137</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>698.9549726006335</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>11803.0</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>2025/10/23</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>5.83</t>
+        </is>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>元大期貨</t>
+        </is>
+      </c>
+      <c r="BJ19" t="inlineStr">
+        <is>
+          <t>元大期貨</t>
+        </is>
+      </c>
+      <c r="BK19" t="inlineStr">
+        <is>
+          <t>金融業</t>
+        </is>
+      </c>
+      <c r="BL19" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM19" t="inlineStr">
+        <is>
+          <t>0.27</t>
+        </is>
+      </c>
+      <c r="BN19" t="inlineStr">
+        <is>
+          <t>0.586310700095985</t>
+        </is>
+      </c>
+      <c r="BO19" t="inlineStr">
+        <is>
+          <t>8.007619922843494</t>
+        </is>
+      </c>
+      <c r="BP19" t="inlineStr">
+        <is>
+          <t>-12.34648294771329</t>
+        </is>
+      </c>
+      <c r="BQ19" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR19" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS19" t="inlineStr">
+        <is>
           <t>1.61</t>
         </is>
       </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="AT19" t="inlineStr">
-        <is>
-          <t>-56.98</t>
-        </is>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>2025/10/15</t>
-        </is>
-      </c>
-      <c r="AV19" t="inlineStr">
-        <is>
-          <t>19304.84615384615</t>
-        </is>
-      </c>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>31270.0</t>
-        </is>
-      </c>
-      <c r="AX19" t="n">
-        <v>21373.2</v>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>19590.6</t>
-        </is>
-      </c>
-      <c r="AZ19" t="n">
-        <v>11958.24</v>
-      </c>
-      <c r="BA19" t="inlineStr">
-        <is>
-          <t>1782</t>
-        </is>
-      </c>
-      <c r="BB19" t="inlineStr">
-        <is>
-          <t>1001.01000486011</t>
-        </is>
-      </c>
-      <c r="BC19" t="inlineStr">
-        <is>
-          <t>1553.306325886435</t>
-        </is>
-      </c>
-      <c r="BD19" t="inlineStr">
-        <is>
-          <t>31270.0</t>
-        </is>
-      </c>
-      <c r="BE19" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="BF19" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="BG19" t="inlineStr">
-        <is>
-          <t>2025/10/23</t>
-        </is>
-      </c>
-      <c r="BH19" t="inlineStr">
-        <is>
-          <t>5.27</t>
-        </is>
-      </c>
-      <c r="BI19" t="inlineStr">
-        <is>
-          <t>元大期貨</t>
-        </is>
-      </c>
-      <c r="BJ19" t="inlineStr">
-        <is>
-          <t>元大期貨</t>
-        </is>
-      </c>
-      <c r="BK19" t="inlineStr">
-        <is>
-          <t>金融業</t>
-        </is>
-      </c>
-      <c r="BL19" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM19" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="BN19" t="inlineStr">
-        <is>
-          <t>0.586310700095985</t>
-        </is>
-      </c>
-      <c r="BO19" t="inlineStr">
-        <is>
-          <t>8.007619922843494</t>
-        </is>
-      </c>
-      <c r="BP19" t="inlineStr">
-        <is>
-          <t>-12.34648294771329</t>
-        </is>
-      </c>
-      <c r="BQ19" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
-        </is>
-      </c>
-      <c r="BR19" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS19" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>11.78</t>
+          <t>11.69</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>25.98</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>30302</t>
+          <t>30078</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>188.0</t>
+          <t>334.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>93.9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8718,12 +8718,12 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10.60</t>
+          <t>18.84</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8759,68 +8759,68 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>94</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>96.97</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>90.22</t>
+          <t>88.02</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>94.18</t>
+          <t>94.16</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>91.42</v>
+        <v>91.66</v>
       </c>
       <c r="AN20" t="n">
-        <v>88.56999999999999</v>
+        <v>88.69</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.34</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>14.91</t>
+          <t>9.14</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-57.96</t>
+          <t>-56.98</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>19304.84615384615</t>
+          <t>19296.16856330014</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>17859.0</t>
+          <t>31270.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>17990.2</v>
+        <v>21373.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>17411.4</t>
+          <t>19590.6</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>11472.62</v>
+        <v>11958.24</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>900.5924919462329</t>
+          <t>1001.01000486011</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>632.5830332273472</t>
+          <t>1553.306325886435</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>17859.0</t>
+          <t>31270.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,22 +8941,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>11.78</t>
+          <t>11.69</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>25.98</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>30302</t>
+          <t>30078</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>93.9</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>188.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9148,12 +9148,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.60</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9189,68 +9189,68 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>94</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>92.11</t>
+          <t>96.97</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>91.23</t>
+          <t>90.22</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>94.18</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>91.08</v>
+        <v>91.42</v>
       </c>
       <c r="AN21" t="n">
-        <v>88.45</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>87.06</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>18.54</t>
+          <t>14.91</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-59.53</t>
+          <t>-57.96</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>19304.84615384615</t>
+          <t>19296.16856330014</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>16873.0</t>
+          <t>17859.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>17330.8</v>
+        <v>17990.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>17510.1</t>
+          <t>17411.4</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>11244.72</v>
+        <v>11472.62</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-179</t>
+          <t>578</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>949.3214844405758</t>
+          <t>900.5924919462329</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>731.5646496705303</t>
+          <t>632.5830332273472</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>16873.0</t>
+          <t>17859.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>11.78</t>
+          <t>11.69</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>25.98</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>30302</t>
+          <t>30078</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9518,7 +9518,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>8.04</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9619,68 +9619,68 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>94</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>81.58</t>
+          <t>92.11</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>93.86</t>
+          <t>91.23</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>93.82</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>90.70999999999999</v>
+        <v>91.08</v>
       </c>
       <c r="AN22" t="n">
-        <v>88.33</v>
+        <v>88.45</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>86.93</t>
+          <t>87.06</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>22.80</t>
+          <t>18.54</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-61.41</t>
+          <t>-59.53</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>19304.84615384615</t>
+          <t>19296.16856330014</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>23221.0</t>
+          <t>16873.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>18190.8</v>
+        <v>17330.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>16836.8</t>
+          <t>17510.1</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>11205.54</v>
+        <v>11244.72</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>-179</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>988.9136362169477</t>
+          <t>949.3214844405758</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>952.4825071011255</t>
+          <t>731.5646496705303</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>23221.0</t>
+          <t>16873.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>11.78</t>
+          <t>11.69</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>25.98</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>30302</t>
+          <t>30078</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
+          <t>93.9</t>
+        </is>
+      </c>
+      <c r="CE22" t="inlineStr">
+        <is>
           <t>94.7</t>
         </is>
       </c>
-      <c r="CE22" t="inlineStr">
-        <is>
-          <t>94.7</t>
-        </is>
-      </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>187.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>21.90</t>
+          <t>8.04</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10008,12 +10008,12 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10.55</t>
+          <t>13.99</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10049,68 +10049,68 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>94</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>81.58</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.86</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>93.47999999999999</t>
+          <t>93.82</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>90.34999999999999</v>
+        <v>90.70999999999999</v>
       </c>
       <c r="AN23" t="n">
-        <v>88.23</v>
+        <v>88.33</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.93</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>22.80</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-63.61</t>
+          <t>-61.41</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>19304.84615384615</t>
+          <t>19296.16856330014</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>17643.0</t>
+          <t>23221.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>19485.8</v>
+        <v>18190.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>15984.8</t>
+          <t>16836.8</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>11103.86</v>
+        <v>11205.54</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>3501</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>995.53747787437</t>
+          <t>988.9136362169477</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>553.9193567483671</t>
+          <t>952.4825071011255</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>17643.0</t>
+          <t>23221.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>5.16</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>11.78</t>
+          <t>11.69</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>25.98</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>30302</t>
+          <t>30078</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/期貨業.xlsx
+++ b/Result/checksun_type/期貨業.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>79.08</t>
+          <t>157.681</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-4.00</t>
+          <t>-10.92</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,17 +1014,17 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>158</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>95.83</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1034,53 +1034,53 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>49.87</t>
+          <t>49.91</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>49.62</v>
+        <v>49.63</v>
       </c>
       <c r="AN2" t="n">
-        <v>49.24</v>
+        <v>49.26</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>49.21</t>
+          <t>49.22</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>71.91</t>
+          <t>65.01</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-96.31</t>
+          <t>-95.59</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,48 +1100,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>26551660.67069701</t>
+          <t>26530695.73934659</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>3943706.0</t>
+          <t>7861566.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>10703715</v>
+        <v>10092497.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>11150051.8</t>
+          <t>11329482.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>11217869</v>
+        <v>11025025.48</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-446336</t>
+          <t>-1236984</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-46668.63895586941</t>
+          <t>-163897.1034673644</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-624512.6639013886</t>
+          <t>-808653.6582805868</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>3943706.0</t>
+          <t>7861566.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>10.41</t>
+          <t>10.42</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>17.08</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>12459</t>
+          <t>12472</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1276,12 +1276,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,89 +1313,89 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>-0.2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>79.08</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>49.85</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>380.391</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-4.00</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-12-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>49.95</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-12.82</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-12-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>49.95</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>49.95</t>
-        </is>
-      </c>
       <c r="T3" t="inlineStr">
         <is>
           <t>49.7</t>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12.63</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>158</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>98.61</t>
+          <t>95.83</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>49.87</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>49.64</v>
+        <v>49.62</v>
       </c>
       <c r="AN3" t="n">
-        <v>49.21</v>
+        <v>49.24</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.21</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>78.29</t>
+          <t>71.91</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-96.97</t>
+          <t>-96.31</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,48 +1530,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>26551660.67069701</t>
+          <t>26530695.73934659</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>18990914.0</t>
+          <t>3943706.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>11532127.6</v>
+        <v>10703715</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>13227919.1</t>
+          <t>11150051.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>11457402.2</v>
+        <v>11217869</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-1695791</t>
+          <t>-446336</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>58393.91103422501</t>
+          <t>-46668.63895586941</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>80620.63749394566</t>
+          <t>-624512.6639013886</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>18990914.0</t>
+          <t>3943706.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>10.41</t>
+          <t>10.42</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>17.08</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>12459</t>
+          <t>12472</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1701,17 +1701,17 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,34 +1743,34 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>380.391</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>49.95</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>-0.1</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>187.779</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>49.9</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -1778,12 +1778,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-12.82</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1853,96 +1853,96 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>12.63</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>158</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>95.83</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>90.61</t>
+          <t>98.61</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>49.56</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>49.63</v>
+        <v>49.64</v>
       </c>
       <c r="AN4" t="n">
-        <v>49.2</v>
+        <v>49.21</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>49.19</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>41.80</t>
+          <t>78.29</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
       <c r="AS4" t="inlineStr">
         <is>
           <t>1.55</t>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-97.56</t>
+          <t>-96.97</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,48 +1960,48 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>26551660.67069701</t>
+          <t>26530695.73934659</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>9355231.0</t>
+          <t>18990914.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>12002864.4</v>
+        <v>11532127.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>12720616.9</t>
+          <t>13227919.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>11280841.36</v>
+        <v>11457402.2</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-717752</t>
+          <t>-1695791</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>54352.68804154852</t>
+          <t>58393.91103422501</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-527126.2404232193</t>
+          <t>80620.63749394566</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>9355231.0</t>
+          <t>18990914.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>10.41</t>
+          <t>10.42</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>17.08</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>12459</t>
+          <t>12472</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
+          <t>49.85</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>50.2</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
           <t>49.95</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
-        <is>
-          <t>49.9</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2163,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>207.186</t>
+          <t>187.779</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,64 +2188,64 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-5.64</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-12-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>49.95</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>6.05</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-12-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>49.95</t>
-        </is>
-      </c>
       <c r="R5" t="inlineStr">
         <is>
           <t>0</t>
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>158</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.83</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>90.61</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.56</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>49.61</v>
+        <v>49.63</v>
       </c>
       <c r="AN5" t="n">
-        <v>49.18</v>
+        <v>49.2</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>49.18</t>
+          <t>49.19</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-42.74</t>
+          <t>41.80</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-97.82</t>
+          <t>-97.56</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>26551660.67069701</t>
+          <t>26530695.73934659</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>10311071.0</t>
+          <t>9355231.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>13509669.6</v>
+        <v>12002864.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>12738791.1</t>
+          <t>12720616.9</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>11218520</v>
+        <v>11280841.36</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>770878</t>
+          <t>-717752</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>160076.1295805972</t>
+          <t>54352.68804154852</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-344115.5217183363</t>
+          <t>-527126.2404232193</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>10311071.0</t>
+          <t>9355231.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>10.41</t>
+          <t>10.42</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>17.08</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>12459</t>
+          <t>12472</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>220.404</t>
+          <t>207.186</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,79 +2618,79 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>49.95</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-0.1</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>6.05</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-12-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>49.95</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
           <t>49.7</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-1.78</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-12-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>49.95</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
       <c r="U6" t="inlineStr">
         <is>
           <t>49.55</t>
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>158</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>44.41</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
+          <t>49.33</t>
+        </is>
+      </c>
+      <c r="AM6" t="n">
+        <v>49.61</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>49.18</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
           <t>49.18</t>
         </is>
       </c>
-      <c r="AM6" t="n">
-        <v>49.58</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>49.16</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>49.17</t>
-        </is>
-      </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-179.21</t>
+          <t>-42.74</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-97.59</t>
+          <t>-97.82</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>26551660.67069701</t>
+          <t>26530695.73934659</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>10917653.0</t>
+          <t>10311071.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>12566466.6</v>
+        <v>13509669.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>12794356.8</t>
+          <t>12738791.1</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>11192472.92</v>
+        <v>11218520</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-227890</t>
+          <t>770878</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>251747.3389076761</t>
+          <t>160076.1295805972</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-172793.2263642792</t>
+          <t>-344115.5217183363</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>10917653.0</t>
+          <t>10311071.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>10.41</t>
+          <t>10.42</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>17.08</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>12459</t>
+          <t>12472</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>164.837</t>
+          <t>220.404</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-12.76</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,37 +3164,37 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>158</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>44.41</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -3204,33 +3204,33 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.18</t>
         </is>
       </c>
       <c r="AM7" t="n">
         <v>49.58</v>
       </c>
       <c r="AN7" t="n">
-        <v>49.14</v>
+        <v>49.16</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>49.16</t>
+          <t>49.17</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-222.32</t>
+          <t>-179.21</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-96.50</t>
+          <t>-97.59</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>26551660.67069701</t>
+          <t>26530695.73934659</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>8085769.0</t>
+          <t>10917653.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>11596388.6</v>
+        <v>12566466.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>13292107.0</t>
+          <t>12794356.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>11264689.06</v>
+        <v>11192472.92</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-1695718</t>
+          <t>-227890</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>328936.5325934861</t>
+          <t>251747.3389076761</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>13133.16794023849</t>
+          <t>-172793.2263642792</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>8085769.0</t>
+          <t>10917653.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>10.41</t>
+          <t>10.42</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>17.08</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>12459</t>
+          <t>12472</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>437.14</t>
+          <t>164.837</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>-12.76</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14.52</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,37 +3594,37 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>158</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -3634,23 +3634,23 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>49.6</v>
+        <v>49.58</v>
       </c>
       <c r="AN8" t="n">
         <v>49.14</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>49.16</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-178.57</t>
+          <t>-222.32</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-94.56</t>
+          <t>-96.50</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>26551660.67069701</t>
+          <t>26530695.73934659</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>21344598.0</t>
+          <t>8085769.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>14923710.6</v>
+        <v>11596388.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>13956611.9</t>
+          <t>13292107.0</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>11357891.38</v>
+        <v>11264689.06</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>967098</t>
+          <t>-1695718</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>386355.3261668038</t>
+          <t>328936.5325934861</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>581689.4038059711</t>
+          <t>13133.16794023849</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>21344598.0</t>
+          <t>8085769.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>10.41</t>
+          <t>10.42</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>17.08</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>12459</t>
+          <t>12472</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3851,17 +3851,17 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>346.337</t>
+          <t>437.14</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11.50</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,54 +4024,54 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>158</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>11.49</t>
+          <t>16.09</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>49.01000000000001</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>49.63</v>
+        <v>49.6</v>
       </c>
       <c r="AN9" t="n">
-        <v>49.15</v>
+        <v>49.14</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4080,17 +4080,17 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-132.60</t>
+          <t>-178.57</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-92.13</t>
+          <t>-94.56</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>26551660.67069701</t>
+          <t>26530695.73934659</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>16889257.0</t>
+          <t>21344598.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>13438369.4</v>
+        <v>14923710.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>13466583.0</t>
+          <t>13956611.9</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>11395162.18</v>
+        <v>11357891.38</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-28213</t>
+          <t>967098</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>350840.0393233188</t>
+          <t>386355.3261668038</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-47450.8450931944</t>
+          <t>581689.4038059711</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>16889257.0</t>
+          <t>21344598.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>10.41</t>
+          <t>10.42</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>17.08</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>12459</t>
+          <t>12472</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,12 +4276,12 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>113.787</t>
+          <t>346.337</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-8.11</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>11.50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,17 +4454,17 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>158</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -4474,17 +4474,17 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -4494,11 +4494,11 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>49.26000000000001</t>
+          <t>49.01000000000001</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>49.68</v>
+        <v>49.63</v>
       </c>
       <c r="AN10" t="n">
         <v>49.15</v>
@@ -4510,17 +4510,17 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-87.62</t>
+          <t>-132.60</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-89.52</t>
+          <t>-92.13</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>26551660.67069701</t>
+          <t>26530695.73934659</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>5595056.0</t>
+          <t>16889257.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>11967912.6</v>
+        <v>13438369.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>13023841.6</t>
+          <t>13466583.0</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>11508277.46</v>
+        <v>11395162.18</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-1055929</t>
+          <t>-28213</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>423256.5637626849</t>
+          <t>350840.0393233188</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-467169.9919101018</t>
+          <t>-47450.8450931944</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>5595056.0</t>
+          <t>16889257.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>10.41</t>
+          <t>10.42</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>17.08</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>12459</t>
+          <t>12472</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>124.255</t>
+          <t>113.787</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-8.11</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,37 +4884,37 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>158</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>31.03</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>11.49</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -4924,11 +4924,11 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>49.26000000000001</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>49.69</v>
+        <v>49.68</v>
       </c>
       <c r="AN11" t="n">
         <v>49.15</v>
@@ -4940,17 +4940,17 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-74.56</t>
+          <t>-87.62</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-87.23</t>
+          <t>-89.52</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>26551660.67069701</t>
+          <t>26530695.73934659</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>6067263.0</t>
+          <t>5595056.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>13022247</v>
+        <v>11967912.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>13893145.0</t>
+          <t>13023841.6</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>11517867.76</v>
+        <v>11508277.46</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-870898</t>
+          <t>-1055929</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>585152.301157737</t>
+          <t>423256.5637626849</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>160008.8337768205</t>
+          <t>-467169.9919101018</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>6067263.0</t>
+          <t>5595056.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>10.41</t>
+          <t>10.42</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>17.08</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>12459</t>
+          <t>12472</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>48.95</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>505.389</t>
+          <t>124.255</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,37 +5314,37 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>158</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -5354,33 +5354,33 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>49.71</v>
+        <v>49.69</v>
       </c>
       <c r="AN12" t="n">
-        <v>49.16</v>
+        <v>49.15</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>49.16</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-45.07</t>
+          <t>-74.56</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-84.85</t>
+          <t>-87.23</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>26551660.67069701</t>
+          <t>26530695.73934659</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>24722379.0</t>
+          <t>6067263.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>14987825.4</v>
+        <v>13022247</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>14283209.4</t>
+          <t>13893145.0</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>11515168.36</v>
+        <v>11517867.76</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>704616</t>
+          <t>-870898</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>662451.1134088128</t>
+          <t>585152.301157737</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>999670.3764089644</t>
+          <t>160008.8337768205</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>24722379.0</t>
+          <t>6067263.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>10.41</t>
+          <t>10.42</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>17.08</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>12459</t>
+          <t>12472</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,12 +5566,12 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>48.95</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-20.46</t>
+          <t>-31.93</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,12 +5723,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>95.02000000000001</t>
+          <t>94.58</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>93.56</v>
+        <v>93.73</v>
       </c>
       <c r="AN13" t="n">
-        <v>89.73</v>
+        <v>89.86</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>88.52</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-9.34</t>
+          <t>-16.89</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-55.61</t>
+          <t>-57.41</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>19296.16856330014</t>
+          <t>19284.63707386364</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>8803.0</t>
+          <t>7452.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>11257.6</v>
+        <v>8993.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>14153.7</t>
+          <t>13211.6</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>12542.78</v>
+        <v>12445.02</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-2896</t>
+          <t>-4218</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-208.1424903312762</t>
+          <t>-419.459604698613</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-1374.664460507063</t>
+          <t>-1581.703733718965</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>8803.0</t>
+          <t>7452.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>11.69</t>
+          <t>11.62</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>25.98</t>
+          <t>26.23</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>30078</t>
+          <t>29886</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>118.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,94 +6058,94 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-0.64</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>-20.46</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2025-10-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>87.4</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
           <t>94.7</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>87.3</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>87.6</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>-0.74</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>-29.56</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2025-10-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2025-08-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>87.4</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>94.7</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>87.4</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>87.3</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>87.6</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>8.35</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
       <c r="X14" t="inlineStr">
         <is>
           <t>-0.23</t>
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>74.95</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>95.02000000000001</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>93.38</v>
+        <v>93.56</v>
       </c>
       <c r="AN14" t="n">
-        <v>89.58</v>
+        <v>89.73</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-9.34</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-54.57</t>
+          <t>-55.61</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,48 +6260,48 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>19296.16856330014</t>
+          <t>19284.63707386364</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>11135.0</t>
+          <t>8803.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>10985.8</v>
+        <v>11257.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>15595.5</t>
+          <t>14153.7</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>12513.22</v>
+        <v>12542.78</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-4609</t>
+          <t>-2896</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>3.952413337048682</t>
+          <t>-208.1424903312762</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-1174.548910900525</t>
+          <t>-1374.664460507063</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>11135.0</t>
+          <t>8803.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>11.69</t>
+          <t>11.62</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>25.98</t>
+          <t>26.23</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>30078</t>
+          <t>29886</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>93.9</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>95.4</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6463,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-31.56</t>
+          <t>-29.56</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,37 +6604,37 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>92.59</t>
+          <t>74.95</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -6644,33 +6644,33 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>95.14000000000001</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>93.15000000000001</v>
+        <v>93.38</v>
       </c>
       <c r="AN15" t="n">
-        <v>89.43000000000001</v>
+        <v>89.58</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>88.12</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-54.27</t>
+          <t>-54.57</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>19296.16856330014</t>
+          <t>19284.63707386364</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>7644.0</t>
+          <t>11135.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>11119.4</v>
+        <v>10985.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>16246.3</t>
+          <t>15595.5</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>12428.1</v>
+        <v>12513.22</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-5126</t>
+          <t>-4609</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>218.2253813802438</t>
+          <t>3.952413337048682</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-1096.578521787593</t>
+          <t>-1174.548910900525</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>7644.0</t>
+          <t>11135.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>11.69</t>
+          <t>11.62</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>25.98</t>
+          <t>26.23</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>30078</t>
+          <t>29886</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>95.4</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-31.56</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>9.27</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,37 +7034,37 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>98.15</t>
+          <t>92.59</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -7074,33 +7074,33 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>94.86</t>
+          <t>95.14000000000001</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>92.88</v>
+        <v>93.15000000000001</v>
       </c>
       <c r="AN16" t="n">
-        <v>89.27</v>
+        <v>89.43000000000001</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>87.97</t>
+          <t>88.12</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-54.52</t>
+          <t>-54.27</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>19296.16856330014</t>
+          <t>19284.63707386364</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>9934.0</t>
+          <t>7644.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>15844.6</v>
+        <v>11119.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>16917.4</t>
+          <t>16246.3</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>12366.42</v>
+        <v>12428.1</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-1072</t>
+          <t>-5126</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>457.2806365016687</t>
+          <t>218.2253813802438</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-571.9930187052742</t>
+          <t>-1096.578521787593</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>9934.0</t>
+          <t>7644.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>11.69</t>
+          <t>11.62</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>25.98</t>
+          <t>26.23</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>30078</t>
+          <t>29886</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.27</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11.05</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,37 +7464,37 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>97.22</t>
+          <t>98.15</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -7504,23 +7504,23 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>94.64000000000001</t>
+          <t>94.86</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>92.58</v>
+        <v>92.88</v>
       </c>
       <c r="AN17" t="n">
-        <v>89.11</v>
+        <v>89.27</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>87.81</t>
+          <t>87.97</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
@@ -7530,7 +7530,7 @@
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-55.07</t>
+          <t>-54.52</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>19296.16856330014</t>
+          <t>19284.63707386364</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>18772.0</t>
+          <t>9934.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>17429.6</v>
+        <v>15844.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>17380.2</t>
+          <t>16917.4</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>12316.72</v>
+        <v>12366.42</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>-1072</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>644.4213010847493</t>
+          <t>457.2806365016687</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-47.51397791963245</t>
+          <t>-571.9930187052742</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>18772.0</t>
+          <t>9934.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7661,12 +7661,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>11.69</t>
+          <t>11.62</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>25.98</t>
+          <t>26.23</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>30078</t>
+          <t>29886</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>95.1</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>8.58</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,12 +7894,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7909,58 +7909,58 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>88.89</t>
+          <t>97.22</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>94.36</t>
+          <t>94.64000000000001</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>92.23999999999999</v>
+        <v>92.58</v>
       </c>
       <c r="AN18" t="n">
-        <v>88.95</v>
+        <v>89.11</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>87.64</t>
+          <t>87.81</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-55.73</t>
+          <t>-55.07</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>19296.16856330014</t>
+          <t>19284.63707386364</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>7444.0</t>
+          <t>18772.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>17049.8</v>
+        <v>17429.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>17620.3</t>
+          <t>17380.2</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>12079.36</v>
+        <v>12316.72</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-570</t>
+          <t>49</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>770.2277154491823</t>
+          <t>644.4213010847493</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-243.4898490144406</t>
+          <t>-47.51397791963245</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>7444.0</t>
+          <t>18772.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>11.69</t>
+          <t>11.62</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>25.98</t>
+          <t>26.23</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>30078</t>
+          <t>29886</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>95.1</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8198,7 +8198,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>8.58</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>6.99</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>88.89</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>94.14000000000001</t>
+          <t>94.36</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>91.92</v>
+        <v>92.23999999999999</v>
       </c>
       <c r="AN19" t="n">
-        <v>88.81999999999999</v>
+        <v>88.95</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>87.49</t>
+          <t>87.64</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-56.30</t>
+          <t>-55.73</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>19296.16856330014</t>
+          <t>19284.63707386364</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>11803.0</t>
+          <t>7444.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>20205.2</v>
+        <v>17049.8</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>19845.5</t>
+          <t>17620.3</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>12067.32</v>
+        <v>12079.36</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>-570</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>954.5399998971137</t>
+          <t>770.2277154491823</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>698.9549726006335</t>
+          <t>-243.4898490144406</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>11803.0</t>
+          <t>7444.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>11.69</t>
+          <t>11.62</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>25.98</t>
+          <t>26.23</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>30078</t>
+          <t>29886</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>334.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8718,12 +8718,12 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18.84</t>
+          <t>6.99</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,209 +8754,209 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>88.02</t>
+          <t>87.88</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>94.16</t>
+          <t>94.14000000000001</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>91.66</v>
+        <v>91.92</v>
       </c>
       <c r="AN20" t="n">
-        <v>88.69</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>87.34</t>
+          <t>87.49</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>-56.30</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>2025/10/15</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>19284.63707386364</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>11803.0</t>
+        </is>
+      </c>
+      <c r="AX20" t="n">
+        <v>20205.2</v>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>19845.5</t>
+        </is>
+      </c>
+      <c r="AZ20" t="n">
+        <v>12067.32</v>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>954.5399998971137</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>698.9549726006335</t>
+        </is>
+      </c>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>11803.0</t>
+        </is>
+      </c>
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="BG20" t="inlineStr">
+        <is>
+          <t>2025/10/23</t>
+        </is>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>5.83</t>
+        </is>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>元大期貨</t>
+        </is>
+      </c>
+      <c r="BJ20" t="inlineStr">
+        <is>
+          <t>元大期貨</t>
+        </is>
+      </c>
+      <c r="BK20" t="inlineStr">
+        <is>
+          <t>金融業</t>
+        </is>
+      </c>
+      <c r="BL20" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM20" t="inlineStr">
+        <is>
+          <t>0.27</t>
+        </is>
+      </c>
+      <c r="BN20" t="inlineStr">
+        <is>
+          <t>0.586310700095985</t>
+        </is>
+      </c>
+      <c r="BO20" t="inlineStr">
+        <is>
+          <t>8.007619922843494</t>
+        </is>
+      </c>
+      <c r="BP20" t="inlineStr">
+        <is>
+          <t>-12.34648294771329</t>
+        </is>
+      </c>
+      <c r="BQ20" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR20" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS20" t="inlineStr">
+        <is>
           <t>1.61</t>
         </is>
       </c>
-      <c r="AS20" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="AT20" t="inlineStr">
-        <is>
-          <t>-56.98</t>
-        </is>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>2025/10/15</t>
-        </is>
-      </c>
-      <c r="AV20" t="inlineStr">
-        <is>
-          <t>19296.16856330014</t>
-        </is>
-      </c>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>31270.0</t>
-        </is>
-      </c>
-      <c r="AX20" t="n">
-        <v>21373.2</v>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>19590.6</t>
-        </is>
-      </c>
-      <c r="AZ20" t="n">
-        <v>11958.24</v>
-      </c>
-      <c r="BA20" t="inlineStr">
-        <is>
-          <t>1782</t>
-        </is>
-      </c>
-      <c r="BB20" t="inlineStr">
-        <is>
-          <t>1001.01000486011</t>
-        </is>
-      </c>
-      <c r="BC20" t="inlineStr">
-        <is>
-          <t>1553.306325886435</t>
-        </is>
-      </c>
-      <c r="BD20" t="inlineStr">
-        <is>
-          <t>31270.0</t>
-        </is>
-      </c>
-      <c r="BE20" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="BF20" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="BG20" t="inlineStr">
-        <is>
-          <t>2025/10/23</t>
-        </is>
-      </c>
-      <c r="BH20" t="inlineStr">
-        <is>
-          <t>5.27</t>
-        </is>
-      </c>
-      <c r="BI20" t="inlineStr">
-        <is>
-          <t>元大期貨</t>
-        </is>
-      </c>
-      <c r="BJ20" t="inlineStr">
-        <is>
-          <t>元大期貨</t>
-        </is>
-      </c>
-      <c r="BK20" t="inlineStr">
-        <is>
-          <t>金融業</t>
-        </is>
-      </c>
-      <c r="BL20" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM20" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="BN20" t="inlineStr">
-        <is>
-          <t>0.586310700095985</t>
-        </is>
-      </c>
-      <c r="BO20" t="inlineStr">
-        <is>
-          <t>8.007619922843494</t>
-        </is>
-      </c>
-      <c r="BP20" t="inlineStr">
-        <is>
-          <t>-12.34648294771329</t>
-        </is>
-      </c>
-      <c r="BQ20" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
-        </is>
-      </c>
-      <c r="BR20" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS20" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>11.69</t>
+          <t>11.62</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>25.98</t>
+          <t>26.23</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>30078</t>
+          <t>29886</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>188.0</t>
+          <t>334.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>93.9</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9148,12 +9148,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10.60</t>
+          <t>18.84</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>96.97</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>90.22</t>
+          <t>88.02</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>94.18</t>
+          <t>94.16</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>91.42</v>
+        <v>91.66</v>
       </c>
       <c r="AN21" t="n">
-        <v>88.56999999999999</v>
+        <v>88.69</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.34</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>14.91</t>
+          <t>9.14</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-57.96</t>
+          <t>-56.98</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>19296.16856330014</t>
+          <t>19284.63707386364</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>17859.0</t>
+          <t>31270.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>17990.2</v>
+        <v>21373.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>17411.4</t>
+          <t>19590.6</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>11472.62</v>
+        <v>11958.24</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>900.5924919462329</t>
+          <t>1001.01000486011</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>632.5830332273472</t>
+          <t>1553.306325886435</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>17859.0</t>
+          <t>31270.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>11.69</t>
+          <t>11.62</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>25.98</t>
+          <t>26.23</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>30078</t>
+          <t>29886</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>93.9</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>188.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9518,7 +9518,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.60</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,73 +9614,73 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>92.11</t>
+          <t>96.97</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>91.23</t>
+          <t>90.22</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>94.18</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>91.08</v>
+        <v>91.42</v>
       </c>
       <c r="AN22" t="n">
-        <v>88.45</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>87.06</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>18.54</t>
+          <t>14.91</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-59.53</t>
+          <t>-57.96</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>19296.16856330014</t>
+          <t>19284.63707386364</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>16873.0</t>
+          <t>17859.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>17330.8</v>
+        <v>17990.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>17510.1</t>
+          <t>17411.4</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>11244.72</v>
+        <v>11472.62</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-179</t>
+          <t>578</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>949.3214844405758</t>
+          <t>900.5924919462329</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>731.5646496705303</t>
+          <t>632.5830332273472</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>16873.0</t>
+          <t>17859.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>11.69</t>
+          <t>11.62</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>25.98</t>
+          <t>26.23</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>30078</t>
+          <t>29886</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>8.04</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10008,12 +10008,12 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,73 +10044,73 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>81.58</t>
+          <t>92.11</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>93.86</t>
+          <t>91.23</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>93.82</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>90.70999999999999</v>
+        <v>91.08</v>
       </c>
       <c r="AN23" t="n">
-        <v>88.33</v>
+        <v>88.45</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>86.93</t>
+          <t>87.06</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>22.80</t>
+          <t>18.54</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-61.41</t>
+          <t>-59.53</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>19296.16856330014</t>
+          <t>19284.63707386364</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>23221.0</t>
+          <t>16873.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>18190.8</v>
+        <v>17330.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>16836.8</t>
+          <t>17510.1</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>11205.54</v>
+        <v>11244.72</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>-179</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>988.9136362169477</t>
+          <t>949.3214844405758</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>952.4825071011255</t>
+          <t>731.5646496705303</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>23221.0</t>
+          <t>16873.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>11.69</t>
+          <t>11.62</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>25.98</t>
+          <t>26.23</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>30078</t>
+          <t>29886</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
+          <t>93.9</t>
+        </is>
+      </c>
+      <c r="CE23" t="inlineStr">
+        <is>
           <t>94.7</t>
         </is>
       </c>
-      <c r="CE23" t="inlineStr">
-        <is>
-          <t>94.7</t>
-        </is>
-      </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/期貨業.xlsx
+++ b/Result/checksun_type/期貨業.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>157.681</t>
+          <t>123.862</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-10.92</t>
+          <t>-18.62</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-04 00:00:00</t>
+          <t>2025-12-05 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,94 +993,94 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
           <t>95.83</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>95.83</t>
-        </is>
-      </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>49.91</t>
+          <t>49.92</t>
         </is>
       </c>
       <c r="AM2" t="n">
         <v>49.63</v>
       </c>
       <c r="AN2" t="n">
-        <v>49.26</v>
+        <v>49.29</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>49.22</t>
+          <t>49.23</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>65.01</t>
+          <t>61.76</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-95.59</t>
+          <t>-94.79</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,48 +1100,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>26530695.73934659</t>
+          <t>26506233.49361702</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>7861566.0</t>
+          <t>6189875.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>10092497.6</v>
+        <v>9268258.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>11329482.1</t>
+          <t>11388964.0</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>11025025.48</v>
+        <v>10947465.56</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-1236984</t>
+          <t>-2120705</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-163897.1034673644</t>
+          <t>-299099.5241476176</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-808653.6582805868</t>
+          <t>-1042712.83788901</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>7861566.0</t>
+          <t>6189875.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>10.42</t>
+          <t>10.44</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.14</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>12472</t>
+          <t>12497</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>79.08</t>
+          <t>157.681</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-4.00</t>
+          <t>-10.92</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-12-04 00:00:00</t>
+          <t>2025-12-05 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,17 +1444,17 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>95.83</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1464,53 +1464,53 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>49.87</t>
+          <t>49.91</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>49.62</v>
+        <v>49.63</v>
       </c>
       <c r="AN3" t="n">
-        <v>49.24</v>
+        <v>49.26</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>49.21</t>
+          <t>49.22</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>71.91</t>
+          <t>65.01</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-96.31</t>
+          <t>-95.59</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,48 +1530,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>26530695.73934659</t>
+          <t>26506233.49361702</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>3943706.0</t>
+          <t>7861566.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>10703715</v>
+        <v>10092497.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>11150051.8</t>
+          <t>11329482.1</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>11217869</v>
+        <v>11025025.48</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-446336</t>
+          <t>-1236984</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-46668.63895586941</t>
+          <t>-163897.1034673644</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-624512.6639013886</t>
+          <t>-808653.6582805868</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>3943706.0</t>
+          <t>7861566.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>10.42</t>
+          <t>10.44</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.14</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>12472</t>
+          <t>12497</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1706,12 +1706,12 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>380.391</t>
+          <t>79.08</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,74 +1758,74 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>49.85</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-4.00</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-12-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>49.95</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-12.82</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-12-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>49.95</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>49.95</t>
-        </is>
-      </c>
       <c r="T4" t="inlineStr">
         <is>
           <t>49.7</t>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12.63</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>98.61</t>
+          <t>95.83</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>49.87</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>49.64</v>
+        <v>49.62</v>
       </c>
       <c r="AN4" t="n">
-        <v>49.21</v>
+        <v>49.24</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.21</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>78.29</t>
+          <t>71.91</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-96.97</t>
+          <t>-96.31</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,48 +1960,48 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>26530695.73934659</t>
+          <t>26506233.49361702</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>18990914.0</t>
+          <t>3943706.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>11532127.6</v>
+        <v>10703715</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>13227919.1</t>
+          <t>11150051.8</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>11457402.2</v>
+        <v>11217869</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-1695791</t>
+          <t>-446336</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>58393.91103422501</t>
+          <t>-46668.63895586941</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>80620.63749394566</t>
+          <t>-624512.6639013886</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>18990914.0</t>
+          <t>3943706.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>10.42</t>
+          <t>10.44</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.14</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>12472</t>
+          <t>12497</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>187.779</t>
+          <t>380.391</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,22 +2198,22 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-12.82</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-12-04 00:00:00</t>
+          <t>2025-12-05 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2283,96 +2283,96 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>12.63</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>95.83</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>90.61</t>
+          <t>98.61</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>49.56</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>49.63</v>
+        <v>49.64</v>
       </c>
       <c r="AN5" t="n">
-        <v>49.2</v>
+        <v>49.21</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>49.19</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>41.80</t>
+          <t>78.29</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
       <c r="AS5" t="inlineStr">
         <is>
           <t>1.55</t>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-97.56</t>
+          <t>-96.97</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,48 +2390,48 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>26530695.73934659</t>
+          <t>26506233.49361702</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>9355231.0</t>
+          <t>18990914.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>12002864.4</v>
+        <v>11532127.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>12720616.9</t>
+          <t>13227919.1</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>11280841.36</v>
+        <v>11457402.2</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-717752</t>
+          <t>-1695791</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>54352.68804154852</t>
+          <t>58393.91103422501</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-527126.2404232193</t>
+          <t>80620.63749394566</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>9355231.0</t>
+          <t>18990914.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>10.42</t>
+          <t>10.44</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.14</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>12472</t>
+          <t>12497</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
+          <t>49.85</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>50.2</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
           <t>49.95</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
-        <is>
-          <t>49.9</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2593,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>207.186</t>
+          <t>187.779</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,64 +2618,64 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-5.64</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-12-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>49.95</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>6.05</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-12-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>49.95</t>
-        </is>
-      </c>
       <c r="R6" t="inlineStr">
         <is>
           <t>0</t>
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.83</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>90.61</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.56</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>49.61</v>
+        <v>49.63</v>
       </c>
       <c r="AN6" t="n">
-        <v>49.18</v>
+        <v>49.2</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>49.18</t>
+          <t>49.19</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-42.74</t>
+          <t>41.80</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-97.82</t>
+          <t>-97.56</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>26530695.73934659</t>
+          <t>26506233.49361702</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>10311071.0</t>
+          <t>9355231.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>13509669.6</v>
+        <v>12002864.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>12738791.1</t>
+          <t>12720616.9</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>11218520</v>
+        <v>11280841.36</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>770878</t>
+          <t>-717752</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>160076.1295805972</t>
+          <t>54352.68804154852</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-344115.5217183363</t>
+          <t>-527126.2404232193</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>10311071.0</t>
+          <t>9355231.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>10.42</t>
+          <t>10.44</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.14</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>12472</t>
+          <t>12497</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>220.404</t>
+          <t>207.186</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,79 +3048,79 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>49.95</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>6.05</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-12-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>49.95</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
           <t>49.7</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.4</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>-1.78</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-12-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>49.95</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
       <c r="U7" t="inlineStr">
         <is>
           <t>49.55</t>
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>44.41</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
+          <t>49.33</t>
+        </is>
+      </c>
+      <c r="AM7" t="n">
+        <v>49.61</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>49.18</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
           <t>49.18</t>
         </is>
       </c>
-      <c r="AM7" t="n">
-        <v>49.58</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>49.16</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>49.17</t>
-        </is>
-      </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-179.21</t>
+          <t>-42.74</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-97.59</t>
+          <t>-97.82</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>26530695.73934659</t>
+          <t>26506233.49361702</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>10917653.0</t>
+          <t>10311071.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>12566466.6</v>
+        <v>13509669.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>12794356.8</t>
+          <t>12738791.1</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>11192472.92</v>
+        <v>11218520</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-227890</t>
+          <t>770878</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>251747.3389076761</t>
+          <t>160076.1295805972</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-172793.2263642792</t>
+          <t>-344115.5217183363</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>10917653.0</t>
+          <t>10311071.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>10.42</t>
+          <t>10.44</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.14</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>12472</t>
+          <t>12497</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>164.837</t>
+          <t>220.404</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-12.76</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-04 00:00:00</t>
+          <t>2025-12-05 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,37 +3594,37 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>44.41</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -3634,33 +3634,33 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.18</t>
         </is>
       </c>
       <c r="AM8" t="n">
         <v>49.58</v>
       </c>
       <c r="AN8" t="n">
-        <v>49.14</v>
+        <v>49.16</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>49.16</t>
+          <t>49.17</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-222.32</t>
+          <t>-179.21</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-96.50</t>
+          <t>-97.59</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>26530695.73934659</t>
+          <t>26506233.49361702</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>8085769.0</t>
+          <t>10917653.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>11596388.6</v>
+        <v>12566466.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>13292107.0</t>
+          <t>12794356.8</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>11264689.06</v>
+        <v>11192472.92</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-1695718</t>
+          <t>-227890</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>328936.5325934861</t>
+          <t>251747.3389076761</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>13133.16794023849</t>
+          <t>-172793.2263642792</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>8085769.0</t>
+          <t>10917653.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>10.42</t>
+          <t>10.44</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.14</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>12472</t>
+          <t>12497</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>437.14</t>
+          <t>164.837</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>-12.76</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-04 00:00:00</t>
+          <t>2025-12-05 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14.52</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,37 +4024,37 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -4064,23 +4064,23 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>49.6</v>
+        <v>49.58</v>
       </c>
       <c r="AN9" t="n">
         <v>49.14</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>49.16</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-178.57</t>
+          <t>-222.32</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-94.56</t>
+          <t>-96.50</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>26530695.73934659</t>
+          <t>26506233.49361702</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>21344598.0</t>
+          <t>8085769.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>14923710.6</v>
+        <v>11596388.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>13956611.9</t>
+          <t>13292107.0</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>11357891.38</v>
+        <v>11264689.06</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>967098</t>
+          <t>-1695718</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>386355.3261668038</t>
+          <t>328936.5325934861</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>581689.4038059711</t>
+          <t>13133.16794023849</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>21344598.0</t>
+          <t>8085769.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>10.42</t>
+          <t>10.44</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.14</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>12472</t>
+          <t>12497</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4281,17 +4281,17 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>346.337</t>
+          <t>437.14</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-04 00:00:00</t>
+          <t>2025-12-05 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11.50</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,54 +4454,54 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>11.49</t>
+          <t>16.09</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>49.01000000000001</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>49.63</v>
+        <v>49.6</v>
       </c>
       <c r="AN10" t="n">
-        <v>49.15</v>
+        <v>49.14</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4510,17 +4510,17 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-132.60</t>
+          <t>-178.57</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-92.13</t>
+          <t>-94.56</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>26530695.73934659</t>
+          <t>26506233.49361702</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>16889257.0</t>
+          <t>21344598.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>13438369.4</v>
+        <v>14923710.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>13466583.0</t>
+          <t>13956611.9</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>11395162.18</v>
+        <v>11357891.38</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-28213</t>
+          <t>967098</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>350840.0393233188</t>
+          <t>386355.3261668038</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-47450.8450931944</t>
+          <t>581689.4038059711</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>16889257.0</t>
+          <t>21344598.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>10.42</t>
+          <t>10.44</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.14</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>12472</t>
+          <t>12497</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,12 +4706,12 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>113.787</t>
+          <t>346.337</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-8.11</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-12-04 00:00:00</t>
+          <t>2025-12-05 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>11.50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,17 +4884,17 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -4904,17 +4904,17 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -4924,11 +4924,11 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>49.26000000000001</t>
+          <t>49.01000000000001</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>49.68</v>
+        <v>49.63</v>
       </c>
       <c r="AN11" t="n">
         <v>49.15</v>
@@ -4940,17 +4940,17 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-87.62</t>
+          <t>-132.60</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-89.52</t>
+          <t>-92.13</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>26530695.73934659</t>
+          <t>26506233.49361702</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>5595056.0</t>
+          <t>16889257.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>11967912.6</v>
+        <v>13438369.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>13023841.6</t>
+          <t>13466583.0</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>11508277.46</v>
+        <v>11395162.18</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-1055929</t>
+          <t>-28213</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>423256.5637626849</t>
+          <t>350840.0393233188</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-467169.9919101018</t>
+          <t>-47450.8450931944</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>5595056.0</t>
+          <t>16889257.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>10.42</t>
+          <t>10.44</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.14</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>12472</t>
+          <t>12497</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>48.75</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>124.255</t>
+          <t>113.787</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-8.11</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-12-04 00:00:00</t>
+          <t>2025-12-05 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,37 +5314,37 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>31.03</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>11.49</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -5354,11 +5354,11 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>49.26000000000001</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>49.69</v>
+        <v>49.68</v>
       </c>
       <c r="AN12" t="n">
         <v>49.15</v>
@@ -5370,17 +5370,17 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-74.56</t>
+          <t>-87.62</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-87.23</t>
+          <t>-89.52</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>26530695.73934659</t>
+          <t>26506233.49361702</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>6067263.0</t>
+          <t>5595056.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>13022247</v>
+        <v>11967912.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>13893145.0</t>
+          <t>13023841.6</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>11517867.76</v>
+        <v>11508277.46</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-870898</t>
+          <t>-1055929</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>585152.301157737</t>
+          <t>423256.5637626849</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>160008.8337768205</t>
+          <t>-467169.9919101018</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>6067263.0</t>
+          <t>5595056.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>10.42</t>
+          <t>10.44</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.14</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>12472</t>
+          <t>12497</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>48.95</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>93.4</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-31.93</t>
+          <t>-31.73</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>17.11</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>94.58</t>
+          <t>94.36</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>93.73</v>
+        <v>93.89</v>
       </c>
       <c r="AN13" t="n">
-        <v>89.86</v>
+        <v>90.02</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>88.52</t>
+          <t>88.64</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-16.89</t>
+          <t>-18.20</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-57.41</t>
+          <t>-59.26</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>19284.63707386364</t>
+          <t>19270.1</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>7452.0</t>
+          <t>6024.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>8993.6</v>
+        <v>8211.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>13211.6</t>
+          <t>12028.1</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>12445.02</v>
+        <v>12511.84</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-4218</t>
+          <t>-3816</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-419.459604698613</t>
+          <t>-630.9563780717992</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-1581.703733718965</t>
+          <t>-1794.188631624324</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>7452.0</t>
+          <t>6024.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>11.62</t>
+          <t>11.74</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>26.23</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>29886</t>
+          <t>30206</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>93.4</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-20.46</t>
+          <t>-31.93</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,12 +6153,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>95.02000000000001</t>
+          <t>94.58</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>93.56</v>
+        <v>93.73</v>
       </c>
       <c r="AN14" t="n">
-        <v>89.73</v>
+        <v>89.86</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>88.52</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-9.34</t>
+          <t>-16.89</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-55.61</t>
+          <t>-57.41</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>19284.63707386364</t>
+          <t>19270.1</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>8803.0</t>
+          <t>7452.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>11257.6</v>
+        <v>8993.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>14153.7</t>
+          <t>13211.6</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>12542.78</v>
+        <v>12445.02</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-2896</t>
+          <t>-4218</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-208.1424903312762</t>
+          <t>-419.459604698613</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-1374.664460507063</t>
+          <t>-1581.703733718965</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>8803.0</t>
+          <t>7452.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>11.62</t>
+          <t>11.74</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>26.23</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>29886</t>
+          <t>30206</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>118.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,72 +6488,72 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>-20.46</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2025-10-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>87.4</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
           <t>94.7</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>-1.39</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>-29.56</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2025-10-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2025-08-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>87.4</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>94.7</t>
-        </is>
-      </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>74.95</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>95.02000000000001</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>93.38</v>
+        <v>93.56</v>
       </c>
       <c r="AN15" t="n">
-        <v>89.58</v>
+        <v>89.73</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-9.34</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-54.57</t>
+          <t>-55.61</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,48 +6690,48 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>19284.63707386364</t>
+          <t>19270.1</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>11135.0</t>
+          <t>8803.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>10985.8</v>
+        <v>11257.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>15595.5</t>
+          <t>14153.7</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>12513.22</v>
+        <v>12542.78</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-4609</t>
+          <t>-2896</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>3.952413337048682</t>
+          <t>-208.1424903312762</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-1174.548910900525</t>
+          <t>-1374.664460507063</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>11135.0</t>
+          <t>8803.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>11.62</t>
+          <t>11.74</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>26.23</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>29886</t>
+          <t>30206</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>93.9</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>95.4</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6893,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-31.56</t>
+          <t>-29.56</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,37 +7034,37 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>92.59</t>
+          <t>74.95</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -7074,33 +7074,33 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>95.14000000000001</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>93.15000000000001</v>
+        <v>93.38</v>
       </c>
       <c r="AN16" t="n">
-        <v>89.43000000000001</v>
+        <v>89.58</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>88.12</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-54.27</t>
+          <t>-54.57</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>19284.63707386364</t>
+          <t>19270.1</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>7644.0</t>
+          <t>11135.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>11119.4</v>
+        <v>10985.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>16246.3</t>
+          <t>15595.5</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>12428.1</v>
+        <v>12513.22</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-5126</t>
+          <t>-4609</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>218.2253813802438</t>
+          <t>3.952413337048682</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-1096.578521787593</t>
+          <t>-1174.548910900525</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>7644.0</t>
+          <t>11135.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>11.62</t>
+          <t>11.74</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>26.23</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>29886</t>
+          <t>30206</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>95.4</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-31.56</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>9.27</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,37 +7464,37 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>98.15</t>
+          <t>92.59</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -7504,33 +7504,33 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>94.86</t>
+          <t>95.14000000000001</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>92.88</v>
+        <v>93.15000000000001</v>
       </c>
       <c r="AN17" t="n">
-        <v>89.27</v>
+        <v>89.43000000000001</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>87.97</t>
+          <t>88.12</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-54.52</t>
+          <t>-54.27</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>19284.63707386364</t>
+          <t>19270.1</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>9934.0</t>
+          <t>7644.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>15844.6</v>
+        <v>11119.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>16917.4</t>
+          <t>16246.3</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>12366.42</v>
+        <v>12428.1</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-1072</t>
+          <t>-5126</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>457.2806365016687</t>
+          <t>218.2253813802438</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-571.9930187052742</t>
+          <t>-1096.578521787593</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>9934.0</t>
+          <t>7644.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>11.62</t>
+          <t>11.74</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>26.23</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>29886</t>
+          <t>30206</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.27</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11.05</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,37 +7894,37 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>97.22</t>
+          <t>98.15</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -7934,23 +7934,23 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>94.64000000000001</t>
+          <t>94.86</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>92.58</v>
+        <v>92.88</v>
       </c>
       <c r="AN18" t="n">
-        <v>89.11</v>
+        <v>89.27</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>87.81</t>
+          <t>87.97</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
@@ -7960,7 +7960,7 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-55.07</t>
+          <t>-54.52</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>19284.63707386364</t>
+          <t>19270.1</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>18772.0</t>
+          <t>9934.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>17429.6</v>
+        <v>15844.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>17380.2</t>
+          <t>16917.4</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>12316.72</v>
+        <v>12366.42</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>-1072</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>644.4213010847493</t>
+          <t>457.2806365016687</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-47.51397791963245</t>
+          <t>-571.9930187052742</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>18772.0</t>
+          <t>9934.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>11.62</t>
+          <t>11.74</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>26.23</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>29886</t>
+          <t>30206</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>95.1</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>8.58</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,12 +8324,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8339,58 +8339,58 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>88.89</t>
+          <t>97.22</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>94.36</t>
+          <t>94.64000000000001</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>92.23999999999999</v>
+        <v>92.58</v>
       </c>
       <c r="AN19" t="n">
-        <v>88.95</v>
+        <v>89.11</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>87.64</t>
+          <t>87.81</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-55.73</t>
+          <t>-55.07</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>19284.63707386364</t>
+          <t>19270.1</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>7444.0</t>
+          <t>18772.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>17049.8</v>
+        <v>17429.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>17620.3</t>
+          <t>17380.2</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>12079.36</v>
+        <v>12316.72</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-570</t>
+          <t>49</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>770.2277154491823</t>
+          <t>644.4213010847493</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-243.4898490144406</t>
+          <t>-47.51397791963245</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>7444.0</t>
+          <t>18772.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8521,12 +8521,12 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>11.62</t>
+          <t>11.74</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>26.23</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>29886</t>
+          <t>30206</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>95.1</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>94.9</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8718,12 +8718,12 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>8.58</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>6.99</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>88.89</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>94.14000000000001</t>
+          <t>94.36</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>91.92</v>
+        <v>92.23999999999999</v>
       </c>
       <c r="AN20" t="n">
-        <v>88.81999999999999</v>
+        <v>88.95</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>87.49</t>
+          <t>87.64</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-56.30</t>
+          <t>-55.73</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>19284.63707386364</t>
+          <t>19270.1</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>11803.0</t>
+          <t>7444.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>20205.2</v>
+        <v>17049.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>19845.5</t>
+          <t>17620.3</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>12067.32</v>
+        <v>12079.36</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>-570</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>954.5399998971137</t>
+          <t>770.2277154491823</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>698.9549726006335</t>
+          <t>-243.4898490144406</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>11803.0</t>
+          <t>7444.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>11.62</t>
+          <t>11.74</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>26.23</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>29886</t>
+          <t>30206</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>94.9</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>334.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9148,12 +9148,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18.84</t>
+          <t>6.99</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,209 +9184,209 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>88.02</t>
+          <t>87.88</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>94.16</t>
+          <t>94.14000000000001</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>91.66</v>
+        <v>91.92</v>
       </c>
       <c r="AN21" t="n">
-        <v>88.69</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>87.34</t>
+          <t>87.49</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>-56.30</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>2025/10/15</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>19270.1</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>11803.0</t>
+        </is>
+      </c>
+      <c r="AX21" t="n">
+        <v>20205.2</v>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>19845.5</t>
+        </is>
+      </c>
+      <c r="AZ21" t="n">
+        <v>12067.32</v>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>954.5399998971137</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>698.9549726006335</t>
+        </is>
+      </c>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>11803.0</t>
+        </is>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>2025/10/23</t>
+        </is>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>5.83</t>
+        </is>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>元大期貨</t>
+        </is>
+      </c>
+      <c r="BJ21" t="inlineStr">
+        <is>
+          <t>元大期貨</t>
+        </is>
+      </c>
+      <c r="BK21" t="inlineStr">
+        <is>
+          <t>金融業</t>
+        </is>
+      </c>
+      <c r="BL21" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM21" t="inlineStr">
+        <is>
+          <t>0.27</t>
+        </is>
+      </c>
+      <c r="BN21" t="inlineStr">
+        <is>
+          <t>0.586310700095985</t>
+        </is>
+      </c>
+      <c r="BO21" t="inlineStr">
+        <is>
+          <t>8.007619922843494</t>
+        </is>
+      </c>
+      <c r="BP21" t="inlineStr">
+        <is>
+          <t>-12.34648294771329</t>
+        </is>
+      </c>
+      <c r="BQ21" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR21" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS21" t="inlineStr">
+        <is>
           <t>1.61</t>
         </is>
       </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="AT21" t="inlineStr">
-        <is>
-          <t>-56.98</t>
-        </is>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>2025/10/15</t>
-        </is>
-      </c>
-      <c r="AV21" t="inlineStr">
-        <is>
-          <t>19284.63707386364</t>
-        </is>
-      </c>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>31270.0</t>
-        </is>
-      </c>
-      <c r="AX21" t="n">
-        <v>21373.2</v>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>19590.6</t>
-        </is>
-      </c>
-      <c r="AZ21" t="n">
-        <v>11958.24</v>
-      </c>
-      <c r="BA21" t="inlineStr">
-        <is>
-          <t>1782</t>
-        </is>
-      </c>
-      <c r="BB21" t="inlineStr">
-        <is>
-          <t>1001.01000486011</t>
-        </is>
-      </c>
-      <c r="BC21" t="inlineStr">
-        <is>
-          <t>1553.306325886435</t>
-        </is>
-      </c>
-      <c r="BD21" t="inlineStr">
-        <is>
-          <t>31270.0</t>
-        </is>
-      </c>
-      <c r="BE21" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="BF21" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="BG21" t="inlineStr">
-        <is>
-          <t>2025/10/23</t>
-        </is>
-      </c>
-      <c r="BH21" t="inlineStr">
-        <is>
-          <t>5.27</t>
-        </is>
-      </c>
-      <c r="BI21" t="inlineStr">
-        <is>
-          <t>元大期貨</t>
-        </is>
-      </c>
-      <c r="BJ21" t="inlineStr">
-        <is>
-          <t>元大期貨</t>
-        </is>
-      </c>
-      <c r="BK21" t="inlineStr">
-        <is>
-          <t>金融業</t>
-        </is>
-      </c>
-      <c r="BL21" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM21" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="BN21" t="inlineStr">
-        <is>
-          <t>0.586310700095985</t>
-        </is>
-      </c>
-      <c r="BO21" t="inlineStr">
-        <is>
-          <t>8.007619922843494</t>
-        </is>
-      </c>
-      <c r="BP21" t="inlineStr">
-        <is>
-          <t>-12.34648294771329</t>
-        </is>
-      </c>
-      <c r="BQ21" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
-        </is>
-      </c>
-      <c r="BR21" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS21" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>11.62</t>
+          <t>11.74</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>26.23</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>29886</t>
+          <t>30206</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>188.0</t>
+          <t>334.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>93.9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9518,7 +9518,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10.60</t>
+          <t>18.84</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,73 +9614,73 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>96.97</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>90.22</t>
+          <t>88.02</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>94.18</t>
+          <t>94.16</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>91.42</v>
+        <v>91.66</v>
       </c>
       <c r="AN22" t="n">
-        <v>88.56999999999999</v>
+        <v>88.69</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.34</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>14.91</t>
+          <t>9.14</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-57.96</t>
+          <t>-56.98</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>19284.63707386364</t>
+          <t>19270.1</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>17859.0</t>
+          <t>31270.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>17990.2</v>
+        <v>21373.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>17411.4</t>
+          <t>19590.6</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>11472.62</v>
+        <v>11958.24</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>900.5924919462329</t>
+          <t>1001.01000486011</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>632.5830332273472</t>
+          <t>1553.306325886435</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>17859.0</t>
+          <t>31270.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>11.62</t>
+          <t>11.74</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>26.23</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>29886</t>
+          <t>30206</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>93.9</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>188.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10008,12 +10008,12 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>10.60</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,73 +10044,73 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>92.11</t>
+          <t>96.97</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>91.23</t>
+          <t>90.22</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>94.18</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>91.08</v>
+        <v>91.42</v>
       </c>
       <c r="AN23" t="n">
-        <v>88.45</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>87.06</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>18.54</t>
+          <t>14.91</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-59.53</t>
+          <t>-57.96</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>19284.63707386364</t>
+          <t>19270.1</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>16873.0</t>
+          <t>17859.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>17330.8</v>
+        <v>17990.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>17510.1</t>
+          <t>17411.4</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>11244.72</v>
+        <v>11472.62</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-179</t>
+          <t>578</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>949.3214844405758</t>
+          <t>900.5924919462329</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>731.5646496705303</t>
+          <t>632.5830332273472</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>16873.0</t>
+          <t>17859.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>11.62</t>
+          <t>11.74</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>26.23</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>29886</t>
+          <t>30206</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/期貨業.xlsx
+++ b/Result/checksun_type/期貨業.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>價_量;【b1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>123.862</t>
+          <t>168.466</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-18.62</t>
+          <t>-13.85</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-05 00:00:00</t>
+          <t>2025-12-08 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>5.60</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>168</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,59 +1029,51 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>95.83</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0.16</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0.59</t>
-        </is>
+          <t>98.61</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.63</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>49.92</t>
+          <t>49.95999999999999</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>49.63</v>
+        <v>49.65</v>
       </c>
       <c r="AN2" t="n">
-        <v>49.29</v>
+        <v>49.32</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>49.23</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>61.76</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0.13</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.08</t>
-        </is>
+          <t>59.41</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0.09</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1090,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-94.79</t>
+          <t>-93.88</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,48 +1092,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>26506233.49361702</t>
+          <t>26486585.34773371</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>6189875.0</t>
+          <t>8423095.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>9268258.4</v>
+        <v>9081831.199999999</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>11388964.0</t>
+          <t>10542347.8</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>10947465.56</v>
+        <v>11044509.76</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-2120705</t>
+          <t>-1460516</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-299099.5241476176</t>
+          <t>-408929.5885353198</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1042712.83788901</t>
+          <t>-1012994.942667682</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>6189875.0</t>
+          <t>8423095.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1156,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,12 +1193,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1216,7 +1208,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.65</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>10.44</t>
+          <t>10.46</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>17.14</t>
+          <t>17.13</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>12497</t>
+          <t>12522</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>50.1</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>49.9</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
+      <c r="CG2" t="inlineStr">
         <is>
           <t>50.1</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>49.9</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>50.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1303,7 +1295,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1313,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>157.681</t>
+          <t>123.862</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1348,7 +1340,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-10.92</t>
+          <t>-18.62</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1368,7 +1360,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-12-05 00:00:00</t>
+          <t>2025-12-08 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1408,7 +1400,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1423,95 +1415,87 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>168</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
           <t>95.83</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>95.83</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0.57</t>
-        </is>
+      <c r="AH3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.59</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>49.91</t>
+          <t>49.92</t>
         </is>
       </c>
       <c r="AM3" t="n">
         <v>49.63</v>
       </c>
       <c r="AN3" t="n">
-        <v>49.26</v>
+        <v>49.29</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>49.22</t>
+          <t>49.23</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>65.01</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>0.11</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.07</t>
-        </is>
+          <t>61.76</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0.08</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1520,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-95.59</t>
+          <t>-94.79</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,48 +1514,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>26506233.49361702</t>
+          <t>26486585.34773371</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>7861566.0</t>
+          <t>6189875.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>10092497.6</v>
+        <v>9268258.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>11329482.1</t>
+          <t>11388964.0</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>11025025.48</v>
+        <v>10947465.56</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-1236984</t>
+          <t>-2120705</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-163897.1034673644</t>
+          <t>-299099.5241476176</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-808653.6582805868</t>
+          <t>-1042712.83788901</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>7861566.0</t>
+          <t>6189875.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1586,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1646,7 +1630,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.65</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>10.44</t>
+          <t>10.46</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>17.14</t>
+          <t>17.13</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>12497</t>
+          <t>12522</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1733,7 +1717,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1743,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>79.08</t>
+          <t>157.681</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,7 +1752,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1778,7 +1762,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-4.00</t>
+          <t>-10.92</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1798,7 +1782,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-05 00:00:00</t>
+          <t>2025-12-08 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1838,7 +1822,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1853,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,17 +1858,17 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>168</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>95.83</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1892,56 +1876,48 @@
           <t>95.83</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0.50</t>
-        </is>
+      <c r="AH4" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.57</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>49.87</t>
+          <t>49.91</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>49.62</v>
+        <v>49.63</v>
       </c>
       <c r="AN4" t="n">
-        <v>49.24</v>
+        <v>49.26</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>49.21</t>
+          <t>49.22</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>71.91</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>0.10</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
+          <t>65.01</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.07000000000000001</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1950,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-96.31</t>
+          <t>-95.59</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,48 +1936,48 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>26506233.49361702</t>
+          <t>26486585.34773371</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>3943706.0</t>
+          <t>7861566.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>10703715</v>
+        <v>10092497.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>11150051.8</t>
+          <t>11329482.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>11217869</v>
+        <v>11025025.48</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-446336</t>
+          <t>-1236984</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-46668.63895586941</t>
+          <t>-163897.1034673644</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-624512.6639013886</t>
+          <t>-808653.6582805868</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>3943706.0</t>
+          <t>7861566.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -2016,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2047,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.65</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>10.44</t>
+          <t>10.46</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>17.14</t>
+          <t>17.13</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>12497</t>
+          <t>12522</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2136,12 +2112,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2163,7 +2139,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2173,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>380.391</t>
+          <t>79.08</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,74 +2164,74 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>49.85</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-4.00</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>49.95</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-12.82</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-12-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>49.95</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>49.95</t>
-        </is>
-      </c>
       <c r="T5" t="inlineStr">
         <is>
           <t>49.7</t>
@@ -2268,7 +2244,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2283,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.63</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,74 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>168</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>98.61</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0.21</t>
-        </is>
+          <t>95.83</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.5</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>49.87</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>49.64</v>
+        <v>49.62</v>
       </c>
       <c r="AN5" t="n">
-        <v>49.21</v>
+        <v>49.24</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.21</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>78.29</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>0.08</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
+          <t>71.91</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.06</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2380,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-96.97</t>
+          <t>-96.31</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,48 +2358,48 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>26506233.49361702</t>
+          <t>26486585.34773371</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>18990914.0</t>
+          <t>3943706.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>11532127.6</v>
+        <v>10703715</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>13227919.1</t>
+          <t>11150051.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>11457402.2</v>
+        <v>11217869</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-1695791</t>
+          <t>-446336</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>58393.91103422501</t>
+          <t>-46668.63895586941</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>80620.63749394566</t>
+          <t>-624512.6639013886</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>18990914.0</t>
+          <t>3943706.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
@@ -2446,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2459,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.65</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>10.44</t>
+          <t>10.46</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>17.14</t>
+          <t>17.13</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>12497</t>
+          <t>12522</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2561,17 +2529,17 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2593,7 +2561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2603,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>187.779</t>
+          <t>380.391</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,7 +2596,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2638,12 +2606,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-12.82</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -2658,7 +2626,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-12-05 00:00:00</t>
+          <t>2025-12-08 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2683,7 +2651,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -2698,7 +2666,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2713,95 +2681,87 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>12.63</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>168</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>95.83</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>90.61</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>0.69</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
+          <t>98.61</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.21</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>49.56</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>49.63</v>
+        <v>49.64</v>
       </c>
       <c r="AN6" t="n">
-        <v>49.2</v>
+        <v>49.21</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>49.19</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>41.80</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
+          <t>78.29</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.05</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2810,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-97.56</t>
+          <t>-96.97</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,48 +2780,48 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>26506233.49361702</t>
+          <t>26486585.34773371</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>9355231.0</t>
+          <t>18990914.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>12002864.4</v>
+        <v>11532127.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>12720616.9</t>
+          <t>13227919.1</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>11280841.36</v>
+        <v>11457402.2</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-717752</t>
+          <t>-1695791</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>54352.68804154852</t>
+          <t>58393.91103422501</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-527126.2404232193</t>
+          <t>80620.63749394566</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>9355231.0</t>
+          <t>18990914.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
@@ -2876,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,12 +2881,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2936,7 +2896,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.65</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>10.44</t>
+          <t>10.46</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>17.14</t>
+          <t>17.13</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>12497</t>
+          <t>12522</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
+          <t>49.85</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>50.2</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
           <t>49.95</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
-      <c r="CG6" t="inlineStr">
-        <is>
-          <t>49.9</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3023,7 +2983,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b2】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3033,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>207.186</t>
+          <t>187.779</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,64 +3008,64 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-5.64</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>49.95</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>6.05</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-12-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>49.95</t>
-        </is>
-      </c>
       <c r="R7" t="inlineStr">
         <is>
           <t>0</t>
@@ -3143,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,74 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>168</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.83</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>1.26</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>-0.57</t>
-        </is>
+          <t>90.61</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-0.15</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.56</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>49.61</v>
+        <v>49.63</v>
       </c>
       <c r="AN7" t="n">
-        <v>49.18</v>
+        <v>49.2</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>49.18</t>
+          <t>49.19</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-42.74</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
+          <t>41.80</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0.04</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3240,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-97.82</t>
+          <t>-97.56</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>26506233.49361702</t>
+          <t>26486585.34773371</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>10311071.0</t>
+          <t>9355231.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>13509669.6</v>
+        <v>12002864.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>12738791.1</t>
+          <t>12720616.9</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>11218520</v>
+        <v>11280841.36</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>770878</t>
+          <t>-717752</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>160076.1295805972</t>
+          <t>54352.68804154852</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-344115.5217183363</t>
+          <t>-527126.2404232193</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>10311071.0</t>
+          <t>9355231.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3366,7 +3318,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.65</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>10.44</t>
+          <t>10.46</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>17.14</t>
+          <t>17.13</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>12497</t>
+          <t>12522</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>220.404</t>
+          <t>207.186</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,79 +3430,79 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>49.95</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>6.05</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-11-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>49.95</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
           <t>49.7</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>-1.78</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-12-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-11-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>49.95</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>49.7</t>
-        </is>
-      </c>
       <c r="U8" t="inlineStr">
         <is>
           <t>49.55</t>
@@ -3573,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,74 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>168</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>44.41</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>1.06</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>-0.82</t>
-        </is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-0.57</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
+          <t>49.33</t>
+        </is>
+      </c>
+      <c r="AM8" t="n">
+        <v>49.61</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>49.18</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
           <t>49.18</t>
         </is>
       </c>
-      <c r="AM8" t="n">
-        <v>49.58</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>49.16</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>49.17</t>
-        </is>
-      </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-179.21</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
+          <t>-42.74</t>
+        </is>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0.03</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3670,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-97.59</t>
+          <t>-97.82</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>26506233.49361702</t>
+          <t>26486585.34773371</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>10917653.0</t>
+          <t>10311071.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>12566466.6</v>
+        <v>13509669.6</v>
    